--- a/storage/app/pdfs/emissions_asia_download.xlsx
+++ b/storage/app/pdfs/emissions_asia_download.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://faro90mx-my.sharepoint.com/personal/rfavela_hcx_mx/Documents/F90/Operacion/Proyectos/Proyectos en curso/US Grains 013 (Analisis Global)/Entregables/Asia/1. Informacion AsiaAfrica/3. Emissions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://faro90mx-my.sharepoint.com/personal/ssantos_faro90_com/Documents/Escritorio/Archivos faltantes emisioens y GHG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="8_{6BCD11FE-E5C6-CB4B-9E36-7FC8DFF0380F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D40F6B0-0EAF-6C44-8CA7-8A7B364A2BD6}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="8_{6BCD11FE-E5C6-CB4B-9E36-7FC8DFF0380F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E130908-BDD6-4325-B6D8-F96F58E51903}"/>
   <bookViews>
-    <workbookView xWindow="5520" yWindow="1260" windowWidth="23280" windowHeight="12480" tabRatio="853" activeTab="6" xr2:uid="{AD60D5F5-4EC3-4F16-A51A-8F435208B142}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="853" activeTab="6" xr2:uid="{AD60D5F5-4EC3-4F16-A51A-8F435208B142}"/>
   </bookViews>
   <sheets>
     <sheet name="Content" sheetId="7" r:id="rId1"/>
@@ -303,7 +303,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -379,6 +379,57 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -391,7 +442,7 @@
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -443,7 +494,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -461,9 +511,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -483,6 +530,15 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Hipervínculo" xfId="4" builtinId="8"/>
@@ -883,135 +939,135 @@
     <tabColor rgb="FF002F60"/>
   </sheetPr>
   <dimension ref="A1:A35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="80.83203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="10.83203125" style="6"/>
+    <col min="1" max="1" width="80.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="10.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="5"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
     </row>
-    <row r="4" spans="1:1" ht="18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="30" t="s">
+    <row r="5" spans="1:1" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="35" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="30"/>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="35"/>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="10"/>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="10"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="10"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="10"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="10"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="10"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="10"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="10"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="10"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="10"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="10"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="10"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="10"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="10"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="10"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="10"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="10"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="10"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="10"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="10"/>
     </row>
   </sheetData>
@@ -1037,59 +1093,59 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:W82"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.33203125" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" style="6" customWidth="1"/>
-    <col min="3" max="8" width="10.83203125" style="6"/>
+    <col min="3" max="8" width="10.77734375" style="6"/>
     <col min="9" max="9" width="16" style="6" customWidth="1"/>
-    <col min="10" max="10" width="14.1640625" style="6" customWidth="1"/>
+    <col min="10" max="10" width="14.109375" style="6" customWidth="1"/>
     <col min="11" max="14" width="12" style="6" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="3.33203125" style="6" customWidth="1"/>
-    <col min="16" max="16" width="31.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="31.44140625" style="6" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14" style="6" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="10.83203125" style="6"/>
+    <col min="18" max="16384" width="10.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="11"/>
     </row>
-    <row r="3" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="28" x14ac:dyDescent="0.2">
-      <c r="A4" s="34" t="s">
+    <row r="4" spans="1:22" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="E4" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="F4" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="G4" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="H4" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="33" t="s">
+      <c r="I4" s="31" t="s">
         <v>17</v>
       </c>
       <c r="J4" s="17"/>
@@ -1098,7 +1154,7 @@
       <c r="M4" s="17"/>
       <c r="N4" s="17"/>
     </row>
-    <row r="5" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
         <v>18</v>
       </c>
@@ -1108,23 +1164,23 @@
       <c r="C5" s="20">
         <v>3.5</v>
       </c>
-      <c r="D5" s="21">
-        <v>4.4462806032113864</v>
-      </c>
-      <c r="E5" s="21">
-        <v>3.6938465282731987</v>
-      </c>
-      <c r="F5" s="21">
-        <v>3.3788393370444827</v>
-      </c>
-      <c r="G5" s="21">
-        <v>3.0587490643613866</v>
-      </c>
-      <c r="H5" s="21">
-        <v>2.8116858501595843</v>
-      </c>
-      <c r="I5" s="22">
-        <v>2.5492512923927002</v>
+      <c r="D5" s="36">
+        <v>3.8012767084341772</v>
+      </c>
+      <c r="E5" s="37">
+        <v>3.3102425058992004</v>
+      </c>
+      <c r="F5" s="37">
+        <v>3.1181654912479235</v>
+      </c>
+      <c r="G5" s="37">
+        <v>2.9290689012484181</v>
+      </c>
+      <c r="H5" s="37">
+        <v>2.7849303769867841</v>
+      </c>
+      <c r="I5" s="38">
+        <v>2.6143736660003589</v>
       </c>
       <c r="J5" s="17"/>
       <c r="K5" s="17"/>
@@ -1132,33 +1188,33 @@
       <c r="M5" s="17"/>
       <c r="N5" s="17"/>
     </row>
-    <row r="6" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="20">
         <v>95</v>
       </c>
-      <c r="C6" s="23">
+      <c r="C6" s="22">
         <v>255.38399999999999</v>
       </c>
-      <c r="D6" s="21">
-        <v>208.98283350496689</v>
-      </c>
-      <c r="E6" s="21">
-        <v>198.53369182971855</v>
-      </c>
-      <c r="F6" s="21">
-        <v>194.54211970977363</v>
-      </c>
-      <c r="G6" s="21">
-        <v>192.56693338624666</v>
-      </c>
-      <c r="H6" s="21">
-        <v>191.57879861045109</v>
-      </c>
-      <c r="I6" s="22">
-        <v>188.04745051238581</v>
+      <c r="D6" s="39">
+        <v>210.76083474783283</v>
+      </c>
+      <c r="E6" s="40">
+        <v>200.22279301044125</v>
+      </c>
+      <c r="F6" s="40">
+        <v>196.19726106675759</v>
+      </c>
+      <c r="G6" s="40">
+        <v>194.20527009148381</v>
+      </c>
+      <c r="H6" s="40">
+        <v>193.21171993209731</v>
+      </c>
+      <c r="I6" s="21">
+        <v>189.65027239899379</v>
       </c>
       <c r="J6" s="17"/>
       <c r="K6" s="17"/>
@@ -1167,7 +1223,7 @@
       <c r="N6" s="17"/>
       <c r="O6" s="9"/>
     </row>
-    <row r="7" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>20</v>
       </c>
@@ -1177,23 +1233,23 @@
       <c r="C7" s="20">
         <v>0.27300000000000002</v>
       </c>
-      <c r="D7" s="21">
-        <v>0.94671773608015397</v>
-      </c>
-      <c r="E7" s="21">
-        <v>0.79234546505305881</v>
-      </c>
-      <c r="F7" s="21">
-        <v>0.72823490259706936</v>
-      </c>
-      <c r="G7" s="21">
-        <v>0.66332298743713292</v>
-      </c>
-      <c r="H7" s="21">
-        <v>0.61329007960578508</v>
-      </c>
-      <c r="I7" s="22">
-        <v>0.54694473452713177</v>
+      <c r="D7" s="39">
+        <v>0.46270138666255173</v>
+      </c>
+      <c r="E7" s="40">
+        <v>0.41738990512621571</v>
+      </c>
+      <c r="F7" s="40">
+        <v>0.40134441754733274</v>
+      </c>
+      <c r="G7" s="40">
+        <v>0.38635745612214034</v>
+      </c>
+      <c r="H7" s="40">
+        <v>0.37518333375145113</v>
+      </c>
+      <c r="I7" s="21">
+        <v>0.35903635081011492</v>
       </c>
       <c r="J7" s="17"/>
       <c r="K7" s="17"/>
@@ -1208,7 +1264,7 @@
       <c r="U7" s="12"/>
       <c r="V7" s="12"/>
     </row>
-    <row r="8" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
         <v>21</v>
       </c>
@@ -1218,23 +1274,23 @@
       <c r="C8" s="20">
         <v>0.20300000000000001</v>
       </c>
-      <c r="D8" s="21">
-        <v>0.29415627168249292</v>
-      </c>
-      <c r="E8" s="21">
-        <v>0.25618468734015404</v>
-      </c>
-      <c r="F8" s="21">
-        <v>0.24835747496097815</v>
-      </c>
-      <c r="G8" s="21">
-        <v>0.23571686344328829</v>
-      </c>
-      <c r="H8" s="21">
-        <v>0.22582344620620667</v>
-      </c>
-      <c r="I8" s="22">
-        <v>0.21416513477310045</v>
+      <c r="D8" s="39">
+        <v>0.33163120454124417</v>
+      </c>
+      <c r="E8" s="40">
+        <v>0.28899062651261226</v>
+      </c>
+      <c r="F8" s="40">
+        <v>0.28033980974608258</v>
+      </c>
+      <c r="G8" s="40">
+        <v>0.2662709703196795</v>
+      </c>
+      <c r="H8" s="40">
+        <v>0.25530470472153055</v>
+      </c>
+      <c r="I8" s="21">
+        <v>0.24235426175253522</v>
       </c>
       <c r="J8" s="17"/>
       <c r="K8" s="17"/>
@@ -1249,29 +1305,29 @@
       <c r="U8" s="12"/>
       <c r="V8" s="12"/>
     </row>
-    <row r="9" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>22</v>
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="20"/>
-      <c r="D9" s="21">
-        <v>2.368362950951598E-3</v>
-      </c>
-      <c r="E9" s="21">
-        <v>2.01048766879683E-3</v>
-      </c>
-      <c r="F9" s="21">
-        <v>1.859023278135236E-3</v>
-      </c>
-      <c r="G9" s="21">
-        <v>1.7137590449478161E-3</v>
-      </c>
-      <c r="H9" s="21">
-        <v>1.5562005313162967E-3</v>
-      </c>
-      <c r="I9" s="22">
-        <v>1.3905476502193499E-3</v>
+      <c r="D9" s="39">
+        <v>2.3872899412951771E-3</v>
+      </c>
+      <c r="E9" s="40">
+        <v>2.0265546659088683E-3</v>
+      </c>
+      <c r="F9" s="40">
+        <v>1.8738798336389495E-3</v>
+      </c>
+      <c r="G9" s="40">
+        <v>1.7274547079718947E-3</v>
+      </c>
+      <c r="H9" s="40">
+        <v>1.5686370509878527E-3</v>
+      </c>
+      <c r="I9" s="21">
+        <v>1.4016603396563357E-3</v>
       </c>
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
@@ -1286,29 +1342,29 @@
       <c r="U9" s="12"/>
       <c r="V9" s="12"/>
     </row>
-    <row r="10" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>23</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
-      <c r="D10" s="21">
-        <v>8.1294193069346682E-2</v>
-      </c>
-      <c r="E10" s="21">
-        <v>7.9684407067973501E-2</v>
-      </c>
-      <c r="F10" s="21">
-        <v>8.0062706778296175E-2</v>
-      </c>
-      <c r="G10" s="21">
-        <v>8.0963382046064472E-2</v>
-      </c>
-      <c r="H10" s="21">
-        <v>8.1596832837604813E-2</v>
-      </c>
-      <c r="I10" s="22">
-        <v>8.2123232860053838E-2</v>
+      <c r="D10" s="39">
+        <v>7.3970323534015905E-2</v>
+      </c>
+      <c r="E10" s="40">
+        <v>7.2505564652154186E-2</v>
+      </c>
+      <c r="F10" s="40">
+        <v>7.2849782989391695E-2</v>
+      </c>
+      <c r="G10" s="40">
+        <v>7.3669315583793304E-2</v>
+      </c>
+      <c r="H10" s="40">
+        <v>7.4245698203805915E-2</v>
+      </c>
+      <c r="I10" s="21">
+        <v>7.4724674358174689E-2</v>
       </c>
       <c r="J10" s="17"/>
       <c r="K10" s="17"/>
@@ -1323,29 +1379,29 @@
       <c r="U10" s="12"/>
       <c r="V10" s="12"/>
     </row>
-    <row r="11" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>24</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
-      <c r="D11" s="21">
-        <v>4.0642178399329931E-3</v>
-      </c>
-      <c r="E11" s="21">
-        <v>4.025971114346702E-3</v>
-      </c>
-      <c r="F11" s="21">
-        <v>4.0454970742512817E-3</v>
-      </c>
-      <c r="G11" s="21">
-        <v>4.1290077930761756E-3</v>
-      </c>
-      <c r="H11" s="21">
-        <v>4.1748998378086126E-3</v>
-      </c>
-      <c r="I11" s="22">
-        <v>4.2222814918533606E-3</v>
+      <c r="D11" s="39">
+        <v>4.567243998991952E-3</v>
+      </c>
+      <c r="E11" s="40">
+        <v>4.5242634957820211E-3</v>
+      </c>
+      <c r="F11" s="40">
+        <v>4.5462061737365621E-3</v>
+      </c>
+      <c r="G11" s="40">
+        <v>4.6400529714295683E-3</v>
+      </c>
+      <c r="H11" s="40">
+        <v>4.6916250510179889E-3</v>
+      </c>
+      <c r="I11" s="21">
+        <v>4.7448711080998497E-3</v>
       </c>
       <c r="J11" s="17"/>
       <c r="K11" s="17"/>
@@ -1360,29 +1416,29 @@
       <c r="U11" s="12"/>
       <c r="V11" s="12"/>
     </row>
-    <row r="12" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
         <v>32</v>
       </c>
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
-      <c r="D12" s="21">
-        <v>0.19212088530545968</v>
-      </c>
-      <c r="E12" s="21">
-        <v>0.19212088530545968</v>
-      </c>
-      <c r="F12" s="21">
-        <v>0.19500269858504152</v>
-      </c>
-      <c r="G12" s="21">
-        <v>0.19922935806176165</v>
-      </c>
-      <c r="H12" s="21">
-        <v>0.2028796548825654</v>
-      </c>
-      <c r="I12" s="22">
-        <v>0.20633783081806364</v>
+      <c r="D12" s="39">
+        <v>0.10427451920379208</v>
+      </c>
+      <c r="E12" s="40">
+        <v>0.10427451920379208</v>
+      </c>
+      <c r="F12" s="40">
+        <v>0.10583863699184895</v>
+      </c>
+      <c r="G12" s="40">
+        <v>0.10813267641433237</v>
+      </c>
+      <c r="H12" s="40">
+        <v>0.11011389227920443</v>
+      </c>
+      <c r="I12" s="21">
+        <v>0.11199083362487269</v>
       </c>
       <c r="J12" s="17"/>
       <c r="K12" s="17"/>
@@ -1397,28 +1453,28 @@
       <c r="U12" s="12"/>
       <c r="V12" s="12"/>
     </row>
-    <row r="13" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>25</v>
       </c>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
-      <c r="D13" s="21">
+      <c r="D13" s="39">
         <v>0</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="40">
         <v>0</v>
       </c>
-      <c r="F13" s="21">
+      <c r="F13" s="40">
         <v>0</v>
       </c>
-      <c r="G13" s="21">
+      <c r="G13" s="40">
         <v>0</v>
       </c>
-      <c r="H13" s="21">
+      <c r="H13" s="40">
         <v>0</v>
       </c>
-      <c r="I13" s="22">
+      <c r="I13" s="21">
         <v>0</v>
       </c>
       <c r="J13" s="17"/>
@@ -1434,29 +1490,29 @@
       <c r="U13" s="12"/>
       <c r="V13" s="12"/>
     </row>
-    <row r="14" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
-      <c r="D14" s="21">
-        <v>3.6437979593193061E-3</v>
-      </c>
-      <c r="E14" s="21">
-        <v>3.2835818559431456E-3</v>
-      </c>
-      <c r="F14" s="21">
-        <v>3.1555052203028097E-3</v>
-      </c>
-      <c r="G14" s="21">
-        <v>3.0356016107438571E-3</v>
-      </c>
-      <c r="H14" s="21">
-        <v>2.9461129379737606E-3</v>
-      </c>
-      <c r="I14" s="22">
-        <v>2.8171257145022995E-3</v>
+      <c r="D14" s="39">
+        <v>3.3009878200121598E-3</v>
+      </c>
+      <c r="E14" s="40">
+        <v>3.0401202448667865E-3</v>
+      </c>
+      <c r="F14" s="40">
+        <v>2.9572998556201277E-3</v>
+      </c>
+      <c r="G14" s="40">
+        <v>2.8850334618299935E-3</v>
+      </c>
+      <c r="H14" s="40">
+        <v>2.8328070108550236E-3</v>
+      </c>
+      <c r="I14" s="21">
+        <v>2.7513136523868529E-3</v>
       </c>
       <c r="J14" s="17"/>
       <c r="K14" s="17"/>
@@ -1471,29 +1527,29 @@
       <c r="U14" s="12"/>
       <c r="V14" s="12"/>
     </row>
-    <row r="15" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>33</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
-      <c r="D15" s="21">
-        <v>1.3145895340290249E-2</v>
-      </c>
-      <c r="E15" s="21">
-        <v>2.2137942395089268E-2</v>
-      </c>
-      <c r="F15" s="21">
-        <v>3.3713094223745202E-2</v>
-      </c>
-      <c r="G15" s="21">
-        <v>4.5930596514664412E-2</v>
-      </c>
-      <c r="H15" s="21">
-        <v>5.2484627464226628E-2</v>
-      </c>
-      <c r="I15" s="22">
-        <v>6.2016267368874729E-2</v>
+      <c r="D15" s="39">
+        <v>7.5152237651330955E-3</v>
+      </c>
+      <c r="E15" s="40">
+        <v>1.2655782393825825E-2</v>
+      </c>
+      <c r="F15" s="40">
+        <v>1.9273046099031792E-2</v>
+      </c>
+      <c r="G15" s="40">
+        <v>2.6257527657003545E-2</v>
+      </c>
+      <c r="H15" s="40">
+        <v>3.0004325259948741E-2</v>
+      </c>
+      <c r="I15" s="21">
+        <v>3.5453357439031996E-2</v>
       </c>
       <c r="J15" s="17"/>
       <c r="K15" s="17"/>
@@ -1508,29 +1564,29 @@
       <c r="U15" s="12"/>
       <c r="V15" s="12"/>
     </row>
-    <row r="16" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
         <v>34</v>
       </c>
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
-      <c r="D16" s="21">
-        <v>5.064743433992127E-2</v>
-      </c>
-      <c r="E16" s="21">
-        <v>5.7400425585244101E-2</v>
-      </c>
-      <c r="F16" s="21">
-        <v>6.7400480121026327E-2</v>
-      </c>
-      <c r="G16" s="21">
-        <v>7.0612090207447784E-2</v>
-      </c>
-      <c r="H16" s="21">
-        <v>7.8115901529396417E-2</v>
-      </c>
-      <c r="I16" s="22">
-        <v>8.5038055205414617E-2</v>
+      <c r="D16" s="39">
+        <v>2.5689915428884422E-2</v>
+      </c>
+      <c r="E16" s="40">
+        <v>2.911523748606901E-2</v>
+      </c>
+      <c r="F16" s="40">
+        <v>3.4187568565749844E-2</v>
+      </c>
+      <c r="G16" s="40">
+        <v>3.5816594647445889E-2</v>
+      </c>
+      <c r="H16" s="40">
+        <v>3.9622755428688448E-2</v>
+      </c>
+      <c r="I16" s="21">
+        <v>4.3133881803405529E-2</v>
       </c>
       <c r="J16" s="17"/>
       <c r="K16" s="17"/>
@@ -1544,29 +1600,29 @@
       <c r="U16" s="12"/>
       <c r="V16" s="12"/>
     </row>
-    <row r="17" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
         <v>27</v>
       </c>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
-      <c r="D17" s="21">
-        <v>1.060670862089595E-2</v>
-      </c>
-      <c r="E17" s="21">
-        <v>9.6581643939145454E-3</v>
-      </c>
-      <c r="F17" s="21">
-        <v>9.5052946081688513E-3</v>
-      </c>
-      <c r="G17" s="21">
-        <v>9.426368448460596E-3</v>
-      </c>
-      <c r="H17" s="21">
-        <v>9.0149643332313126E-3</v>
-      </c>
-      <c r="I17" s="22">
-        <v>8.7240331858343088E-3</v>
+      <c r="D17" s="39">
+        <v>7.7385377184061022E-3</v>
+      </c>
+      <c r="E17" s="40">
+        <v>7.0464903038470767E-3</v>
+      </c>
+      <c r="F17" s="40">
+        <v>6.9349581928709074E-3</v>
+      </c>
+      <c r="G17" s="40">
+        <v>6.8773745365547463E-3</v>
+      </c>
+      <c r="H17" s="40">
+        <v>6.5772186279689972E-3</v>
+      </c>
+      <c r="I17" s="21">
+        <v>6.3649584690394423E-3</v>
       </c>
       <c r="J17" s="17"/>
       <c r="K17" s="17"/>
@@ -1580,29 +1636,29 @@
       <c r="U17" s="16"/>
       <c r="V17" s="16"/>
     </row>
-    <row r="18" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="18" t="s">
         <v>28</v>
       </c>
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
-      <c r="D18" s="21">
-        <v>1.2375461558990416E-2</v>
-      </c>
-      <c r="E18" s="21">
-        <v>1.0125377639173979E-2</v>
-      </c>
-      <c r="F18" s="21">
-        <v>9.1353407144547424E-3</v>
-      </c>
-      <c r="G18" s="21">
-        <v>8.1666795869737661E-3</v>
-      </c>
-      <c r="H18" s="21">
-        <v>7.1282658579784799E-3</v>
-      </c>
-      <c r="I18" s="22">
-        <v>6.0414753247071424E-3</v>
+      <c r="D18" s="39">
+        <v>1.2283961366313904E-2</v>
+      </c>
+      <c r="E18" s="40">
+        <v>1.0050513845165917E-2</v>
+      </c>
+      <c r="F18" s="40">
+        <v>9.0677969358608067E-3</v>
+      </c>
+      <c r="G18" s="40">
+        <v>8.106297778006602E-3</v>
+      </c>
+      <c r="H18" s="40">
+        <v>7.0755617469968049E-3</v>
+      </c>
+      <c r="I18" s="21">
+        <v>5.996806594282332E-3</v>
       </c>
       <c r="J18" s="17"/>
       <c r="K18" s="17"/>
@@ -1616,29 +1672,29 @@
       <c r="U18" s="15"/>
       <c r="V18" s="15"/>
     </row>
-    <row r="19" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
         <v>29</v>
       </c>
       <c r="B19" s="20"/>
       <c r="C19" s="20"/>
-      <c r="D19" s="21">
-        <v>3.113582950923616E-2</v>
-      </c>
-      <c r="E19" s="21">
-        <v>2.5474769598465952E-2</v>
-      </c>
-      <c r="F19" s="21">
-        <v>2.298390323772705E-2</v>
-      </c>
-      <c r="G19" s="21">
-        <v>2.0546816946140474E-2</v>
-      </c>
-      <c r="H19" s="21">
-        <v>1.7934237797320021E-2</v>
-      </c>
-      <c r="I19" s="22">
-        <v>1.5199945860418016E-2</v>
+      <c r="D19" s="39">
+        <v>1.5029013922523595E-2</v>
+      </c>
+      <c r="E19" s="40">
+        <v>1.2296465936610216E-2</v>
+      </c>
+      <c r="F19" s="40">
+        <v>1.1094144822808322E-2</v>
+      </c>
+      <c r="G19" s="40">
+        <v>9.9177829148726134E-3</v>
+      </c>
+      <c r="H19" s="40">
+        <v>8.65671201937359E-3</v>
+      </c>
+      <c r="I19" s="21">
+        <v>7.3368913421774252E-3</v>
       </c>
       <c r="J19" s="17"/>
       <c r="K19" s="17"/>
@@ -1646,33 +1702,33 @@
       <c r="M19" s="17"/>
       <c r="N19" s="17"/>
     </row>
-    <row r="20" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A20" s="24" t="s">
+    <row r="20" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="24">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="24">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="D20" s="26">
-        <v>4.3511291068226578E-2</v>
-      </c>
-      <c r="E20" s="26">
-        <v>3.5600147237639934E-2</v>
-      </c>
-      <c r="F20" s="26">
-        <v>3.211924395218179E-2</v>
-      </c>
-      <c r="G20" s="26">
-        <v>2.8713496533114238E-2</v>
-      </c>
-      <c r="H20" s="26">
-        <v>2.5062503655298503E-2</v>
-      </c>
-      <c r="I20" s="27">
-        <v>2.1241421185125158E-2</v>
+      <c r="D20" s="41">
+        <v>2.7312975288837499E-2</v>
+      </c>
+      <c r="E20" s="25">
+        <v>2.2346979781776133E-2</v>
+      </c>
+      <c r="F20" s="25">
+        <v>2.016194175866913E-2</v>
+      </c>
+      <c r="G20" s="25">
+        <v>1.8024080692879217E-2</v>
+      </c>
+      <c r="H20" s="25">
+        <v>1.5732273766370396E-2</v>
+      </c>
+      <c r="I20" s="26">
+        <v>1.3333697936459757E-2</v>
       </c>
       <c r="J20" s="17"/>
       <c r="K20" s="17"/>
@@ -1680,7 +1736,7 @@
       <c r="M20" s="17"/>
       <c r="N20" s="17"/>
     </row>
-    <row r="21" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
@@ -1696,7 +1752,7 @@
       <c r="M21" s="17"/>
       <c r="N21" s="17"/>
     </row>
-    <row r="22" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
@@ -1712,7 +1768,7 @@
       <c r="M22" s="17"/>
       <c r="N22" s="17"/>
     </row>
-    <row r="23" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="17"/>
@@ -1735,7 +1791,7 @@
       <c r="V23" s="12"/>
       <c r="W23" s="12"/>
     </row>
-    <row r="24" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
@@ -1751,7 +1807,7 @@
       <c r="M24" s="17"/>
       <c r="N24" s="17"/>
     </row>
-    <row r="25" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="17"/>
@@ -1767,7 +1823,7 @@
       <c r="M25" s="17"/>
       <c r="N25" s="17"/>
     </row>
-    <row r="26" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -1783,7 +1839,7 @@
       <c r="M26" s="17"/>
       <c r="N26" s="17"/>
     </row>
-    <row r="27" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
@@ -1799,7 +1855,7 @@
       <c r="M27" s="17"/>
       <c r="N27" s="17"/>
     </row>
-    <row r="28" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:23" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -1815,7 +1871,7 @@
       <c r="M28" s="17"/>
       <c r="N28" s="17"/>
     </row>
-    <row r="29" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="17"/>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
@@ -1831,7 +1887,7 @@
       <c r="M29" s="17"/>
       <c r="N29" s="17"/>
     </row>
-    <row r="30" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="17"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -1854,7 +1910,7 @@
       <c r="V30" s="12"/>
       <c r="W30" s="12"/>
     </row>
-    <row r="31" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="17"/>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
@@ -1877,7 +1933,7 @@
       <c r="V31" s="12"/>
       <c r="W31" s="12"/>
     </row>
-    <row r="32" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="17"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -1900,7 +1956,7 @@
       <c r="V32" s="12"/>
       <c r="W32" s="12"/>
     </row>
-    <row r="33" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="17"/>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
@@ -1923,7 +1979,7 @@
       <c r="V33" s="12"/>
       <c r="W33" s="12"/>
     </row>
-    <row r="34" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="17"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
@@ -1946,7 +2002,7 @@
       <c r="V34" s="12"/>
       <c r="W34" s="12"/>
     </row>
-    <row r="35" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="17"/>
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
@@ -1969,7 +2025,7 @@
       <c r="V35" s="12"/>
       <c r="W35" s="12"/>
     </row>
-    <row r="36" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="17"/>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
@@ -1992,7 +2048,7 @@
       <c r="V36" s="12"/>
       <c r="W36" s="12"/>
     </row>
-    <row r="37" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="17"/>
       <c r="B37" s="17"/>
       <c r="C37" s="17"/>
@@ -2015,7 +2071,7 @@
       <c r="V37" s="12"/>
       <c r="W37" s="12"/>
     </row>
-    <row r="38" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="17"/>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
@@ -2038,7 +2094,7 @@
       <c r="V38" s="12"/>
       <c r="W38" s="12"/>
     </row>
-    <row r="39" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="17"/>
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>
@@ -2061,7 +2117,7 @@
       <c r="V39" s="12"/>
       <c r="W39" s="12"/>
     </row>
-    <row r="40" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="17"/>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
@@ -2084,7 +2140,7 @@
       <c r="V40" s="12"/>
       <c r="W40" s="12"/>
     </row>
-    <row r="41" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="17"/>
       <c r="B41" s="17"/>
       <c r="C41" s="17"/>
@@ -2107,7 +2163,7 @@
       <c r="V41" s="12"/>
       <c r="W41" s="12"/>
     </row>
-    <row r="42" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="17"/>
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
@@ -2130,7 +2186,7 @@
       <c r="V42" s="12"/>
       <c r="W42" s="12"/>
     </row>
-    <row r="43" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="17"/>
       <c r="B43" s="17"/>
       <c r="C43" s="17"/>
@@ -2153,7 +2209,7 @@
       <c r="V43" s="12"/>
       <c r="W43" s="12"/>
     </row>
-    <row r="44" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="17"/>
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
@@ -2176,7 +2232,7 @@
       <c r="V44" s="12"/>
       <c r="W44" s="12"/>
     </row>
-    <row r="45" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="17"/>
       <c r="B45" s="17"/>
       <c r="C45" s="17"/>
@@ -2199,7 +2255,7 @@
       <c r="V45" s="12"/>
       <c r="W45" s="12"/>
     </row>
-    <row r="46" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="17"/>
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
@@ -2222,7 +2278,7 @@
       <c r="V46" s="12"/>
       <c r="W46" s="12"/>
     </row>
-    <row r="47" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="17"/>
       <c r="B47" s="17"/>
       <c r="C47" s="17"/>
@@ -2245,7 +2301,7 @@
       <c r="V47" s="12"/>
       <c r="W47" s="12"/>
     </row>
-    <row r="48" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="17"/>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
@@ -2268,7 +2324,7 @@
       <c r="V48" s="13"/>
       <c r="W48" s="13"/>
     </row>
-    <row r="49" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="17"/>
       <c r="B49" s="17"/>
       <c r="C49" s="17"/>
@@ -2291,7 +2347,7 @@
       <c r="V49" s="14"/>
       <c r="W49" s="14"/>
     </row>
-    <row r="50" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="17"/>
       <c r="B50" s="17"/>
       <c r="C50" s="17"/>
@@ -2307,7 +2363,7 @@
       <c r="M50" s="17"/>
       <c r="N50" s="17"/>
     </row>
-    <row r="51" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="17"/>
       <c r="B51" s="17"/>
       <c r="C51" s="17"/>
@@ -2323,7 +2379,7 @@
       <c r="M51" s="17"/>
       <c r="N51" s="17"/>
     </row>
-    <row r="52" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:23" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="17"/>
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
@@ -2339,7 +2395,7 @@
       <c r="M52" s="17"/>
       <c r="N52" s="17"/>
     </row>
-    <row r="53" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="17"/>
       <c r="B53" s="17"/>
       <c r="C53" s="17"/>
@@ -2355,7 +2411,7 @@
       <c r="M53" s="17"/>
       <c r="N53" s="17"/>
     </row>
-    <row r="54" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="17"/>
       <c r="B54" s="17"/>
       <c r="C54" s="17"/>
@@ -2372,7 +2428,7 @@
       <c r="N54" s="17"/>
       <c r="O54" s="9"/>
     </row>
-    <row r="55" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="17"/>
       <c r="B55" s="17"/>
       <c r="C55" s="17"/>
@@ -2395,7 +2451,7 @@
       <c r="U55" s="12"/>
       <c r="V55" s="12"/>
     </row>
-    <row r="56" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="17"/>
       <c r="B56" s="17"/>
       <c r="C56" s="17"/>
@@ -2418,7 +2474,7 @@
       <c r="U56" s="12"/>
       <c r="V56" s="12"/>
     </row>
-    <row r="57" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="17"/>
       <c r="B57" s="17"/>
       <c r="C57" s="17"/>
@@ -2441,7 +2497,7 @@
       <c r="U57" s="12"/>
       <c r="V57" s="12"/>
     </row>
-    <row r="58" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="17"/>
       <c r="B58" s="17"/>
       <c r="C58" s="17"/>
@@ -2464,7 +2520,7 @@
       <c r="U58" s="12"/>
       <c r="V58" s="12"/>
     </row>
-    <row r="59" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="17"/>
       <c r="B59" s="17"/>
       <c r="C59" s="17"/>
@@ -2487,7 +2543,7 @@
       <c r="U59" s="12"/>
       <c r="V59" s="12"/>
     </row>
-    <row r="60" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="17"/>
       <c r="B60" s="17"/>
       <c r="C60" s="17"/>
@@ -2510,7 +2566,7 @@
       <c r="U60" s="12"/>
       <c r="V60" s="12"/>
     </row>
-    <row r="61" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="17"/>
       <c r="B61" s="17"/>
       <c r="C61" s="17"/>
@@ -2533,7 +2589,7 @@
       <c r="U61" s="12"/>
       <c r="V61" s="12"/>
     </row>
-    <row r="62" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="17"/>
       <c r="B62" s="17"/>
       <c r="C62" s="17"/>
@@ -2556,7 +2612,7 @@
       <c r="U62" s="12"/>
       <c r="V62" s="12"/>
     </row>
-    <row r="63" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="17"/>
       <c r="B63" s="17"/>
       <c r="C63" s="17"/>
@@ -2579,7 +2635,7 @@
       <c r="U63" s="12"/>
       <c r="V63" s="12"/>
     </row>
-    <row r="64" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="17"/>
       <c r="B64" s="17"/>
       <c r="C64" s="17"/>
@@ -2601,7 +2657,7 @@
       <c r="U64" s="12"/>
       <c r="V64" s="12"/>
     </row>
-    <row r="65" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="17"/>
       <c r="B65" s="17"/>
       <c r="C65" s="17"/>
@@ -2623,7 +2679,7 @@
       <c r="U65" s="16"/>
       <c r="V65" s="16"/>
     </row>
-    <row r="66" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="17"/>
       <c r="B66" s="17"/>
       <c r="C66" s="17"/>
@@ -2645,7 +2701,7 @@
       <c r="U66" s="15"/>
       <c r="V66" s="15"/>
     </row>
-    <row r="67" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="17"/>
       <c r="B67" s="17"/>
       <c r="C67" s="17"/>
@@ -2661,7 +2717,7 @@
       <c r="M67" s="17"/>
       <c r="N67" s="17"/>
     </row>
-    <row r="68" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="17"/>
       <c r="B68" s="17"/>
       <c r="C68" s="17"/>
@@ -2677,7 +2733,7 @@
       <c r="M68" s="17"/>
       <c r="N68" s="17"/>
     </row>
-    <row r="69" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="17"/>
       <c r="B69" s="17"/>
       <c r="C69" s="17"/>
@@ -2693,7 +2749,7 @@
       <c r="M69" s="17"/>
       <c r="N69" s="17"/>
     </row>
-    <row r="70" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="17"/>
       <c r="B70" s="17"/>
       <c r="C70" s="17"/>
@@ -2709,7 +2765,7 @@
       <c r="M70" s="17"/>
       <c r="N70" s="17"/>
     </row>
-    <row r="71" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="17"/>
       <c r="B71" s="17"/>
       <c r="C71" s="17"/>
@@ -2732,7 +2788,7 @@
       <c r="V71" s="12"/>
       <c r="W71" s="12"/>
     </row>
-    <row r="72" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="17"/>
       <c r="B72" s="17"/>
       <c r="C72" s="17"/>
@@ -2748,7 +2804,7 @@
       <c r="M72" s="17"/>
       <c r="N72" s="17"/>
     </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
       <c r="D73" s="8"/>
@@ -2763,7 +2819,7 @@
       <c r="M73" s="8"/>
       <c r="N73" s="8"/>
     </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B74" s="8"/>
       <c r="C74" s="8"/>
       <c r="D74" s="8"/>
@@ -2778,7 +2834,7 @@
       <c r="M74" s="8"/>
       <c r="N74" s="8"/>
     </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B75" s="8"/>
       <c r="C75" s="8"/>
       <c r="D75" s="8"/>
@@ -2793,7 +2849,7 @@
       <c r="M75" s="8"/>
       <c r="N75" s="8"/>
     </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B76" s="8"/>
       <c r="C76" s="8"/>
       <c r="D76" s="8"/>
@@ -2808,7 +2864,7 @@
       <c r="M76" s="8"/>
       <c r="N76" s="8"/>
     </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B77" s="8"/>
       <c r="C77" s="8"/>
       <c r="D77" s="8"/>
@@ -2823,7 +2879,7 @@
       <c r="M77" s="8"/>
       <c r="N77" s="8"/>
     </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B78" s="8"/>
       <c r="C78" s="8"/>
       <c r="D78" s="8"/>
@@ -2838,7 +2894,7 @@
       <c r="M78" s="8"/>
       <c r="N78" s="8"/>
     </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B79" s="8"/>
       <c r="C79" s="8"/>
       <c r="D79" s="8"/>
@@ -2853,7 +2909,7 @@
       <c r="M79" s="8"/>
       <c r="N79" s="8"/>
     </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
       <c r="D80" s="8"/>
@@ -2868,7 +2924,7 @@
       <c r="M80" s="8"/>
       <c r="N80" s="8"/>
     </row>
-    <row r="81" spans="2:14" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B81" s="8"/>
       <c r="C81" s="8"/>
       <c r="D81" s="8"/>
@@ -2883,7 +2939,7 @@
       <c r="M81" s="8"/>
       <c r="N81" s="8"/>
     </row>
-    <row r="82" spans="2:14" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B82" s="8"/>
       <c r="C82" s="8"/>
       <c r="D82" s="8"/>
@@ -2912,63 +2968,63 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:W95"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.33203125" style="8" customWidth="1"/>
-    <col min="2" max="2" width="17.1640625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="17.109375" style="6" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5" style="6" customWidth="1"/>
-    <col min="9" max="9" width="18.83203125" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="6"/>
+    <col min="8" max="8" width="12.44140625" style="6" customWidth="1"/>
+    <col min="9" max="9" width="18.77734375" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="10.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:23" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
       <c r="K4" s="17"/>
       <c r="L4" s="17"/>
       <c r="M4" s="17"/>
       <c r="N4" s="17"/>
     </row>
-    <row r="5" spans="1:23" ht="28" x14ac:dyDescent="0.2">
-      <c r="A5" s="34" t="s">
+    <row r="5" spans="1:23" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="33" t="s">
+      <c r="F5" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="33" t="s">
+      <c r="G5" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="33" t="s">
+      <c r="H5" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="33" t="s">
+      <c r="I5" s="31" t="s">
         <v>17</v>
       </c>
       <c r="K5" s="17"/>
@@ -2976,7 +3032,7 @@
       <c r="M5" s="17"/>
       <c r="N5" s="17"/>
     </row>
-    <row r="6" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
         <v>18</v>
       </c>
@@ -2986,23 +3042,23 @@
       <c r="C6" s="20">
         <v>3.5</v>
       </c>
-      <c r="D6" s="21">
-        <v>3.8809270710085282</v>
-      </c>
-      <c r="E6" s="21">
-        <v>3.2381882184885531</v>
-      </c>
-      <c r="F6" s="21">
-        <v>2.9703478851315919</v>
-      </c>
-      <c r="G6" s="21">
-        <v>2.698745517741711</v>
-      </c>
-      <c r="H6" s="21">
-        <v>2.4892752306167449</v>
-      </c>
-      <c r="I6" s="22">
-        <v>2.2534288797021027</v>
+      <c r="D6" s="36">
+        <v>2.9641125009238176</v>
+      </c>
+      <c r="E6" s="37">
+        <v>2.595106344346894</v>
+      </c>
+      <c r="F6" s="37">
+        <v>2.4523753310413809</v>
+      </c>
+      <c r="G6" s="37">
+        <v>2.3126365692065076</v>
+      </c>
+      <c r="H6" s="37">
+        <v>2.2063607405658745</v>
+      </c>
+      <c r="I6" s="38">
+        <v>2.0786285211236715</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="17"/>
@@ -3017,33 +3073,33 @@
       <c r="V6" s="12"/>
       <c r="W6" s="12"/>
     </row>
-    <row r="7" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="20">
         <v>95</v>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="22">
         <v>255.38399999999999</v>
       </c>
-      <c r="D7" s="21">
-        <v>147.63862037572957</v>
-      </c>
-      <c r="E7" s="21">
-        <v>140.25668935694313</v>
-      </c>
-      <c r="F7" s="21">
-        <v>137.43679170776673</v>
-      </c>
-      <c r="G7" s="21">
-        <v>136.0413958329012</v>
-      </c>
-      <c r="H7" s="21">
-        <v>135.40912299943639</v>
-      </c>
-      <c r="I7" s="22">
-        <v>132.91314352554355</v>
+      <c r="D7" s="39">
+        <v>159.44025646393922</v>
+      </c>
+      <c r="E7" s="40">
+        <v>151.46824364074226</v>
+      </c>
+      <c r="F7" s="40">
+        <v>148.422934742281</v>
+      </c>
+      <c r="G7" s="40">
+        <v>146.91599654690179</v>
+      </c>
+      <c r="H7" s="40">
+        <v>146.20457439050364</v>
+      </c>
+      <c r="I7" s="21">
+        <v>143.50960370769775</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="17"/>
@@ -3058,7 +3114,7 @@
       <c r="V7" s="12"/>
       <c r="W7" s="12"/>
     </row>
-    <row r="8" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
         <v>20</v>
       </c>
@@ -3068,23 +3124,23 @@
       <c r="C8" s="20">
         <v>0.27300000000000002</v>
       </c>
-      <c r="D8" s="21">
-        <v>1.0753629680849102</v>
-      </c>
-      <c r="E8" s="21">
-        <v>0.92530182150630125</v>
-      </c>
-      <c r="F8" s="21">
-        <v>0.86530792280067437</v>
-      </c>
-      <c r="G8" s="21">
-        <v>0.8056206388537176</v>
-      </c>
-      <c r="H8" s="21">
-        <v>0.7599315869824077</v>
-      </c>
-      <c r="I8" s="22">
-        <v>0.69823056809800832</v>
+      <c r="D8" s="39">
+        <v>0.61004150337592256</v>
+      </c>
+      <c r="E8" s="40">
+        <v>0.55019089779286423</v>
+      </c>
+      <c r="F8" s="40">
+        <v>0.52897997676196107</v>
+      </c>
+      <c r="G8" s="40">
+        <v>0.50915934163725973</v>
+      </c>
+      <c r="H8" s="40">
+        <v>0.49437835519094897</v>
+      </c>
+      <c r="I8" s="21">
+        <v>0.47302999039671434</v>
       </c>
       <c r="J8" s="6"/>
       <c r="K8" s="17"/>
@@ -3099,7 +3155,7 @@
       <c r="V8" s="12"/>
       <c r="W8" s="12"/>
     </row>
-    <row r="9" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>21</v>
       </c>
@@ -3109,23 +3165,23 @@
       <c r="C9" s="20">
         <v>0.20300000000000001</v>
       </c>
-      <c r="D9" s="21">
-        <v>0.2436069795387662</v>
-      </c>
-      <c r="E9" s="21">
-        <v>0.21202374551099037</v>
-      </c>
-      <c r="F9" s="21">
-        <v>0.20540061673632906</v>
-      </c>
-      <c r="G9" s="21">
-        <v>0.19478426676636201</v>
-      </c>
-      <c r="H9" s="21">
-        <v>0.18643863932189345</v>
-      </c>
-      <c r="I9" s="22">
-        <v>0.17662688901011064</v>
+      <c r="D9" s="39">
+        <v>0.22687495586963952</v>
+      </c>
+      <c r="E9" s="40">
+        <v>0.19746518135179755</v>
+      </c>
+      <c r="F9" s="40">
+        <v>0.19130126515515641</v>
+      </c>
+      <c r="G9" s="40">
+        <v>0.18141861338970033</v>
+      </c>
+      <c r="H9" s="40">
+        <v>0.17365085449523732</v>
+      </c>
+      <c r="I9" s="21">
+        <v>0.16451781061847232</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="17"/>
@@ -3140,29 +3196,29 @@
       <c r="V9" s="12"/>
       <c r="W9" s="12"/>
     </row>
-    <row r="10" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>22</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
-      <c r="D10" s="21">
-        <v>1.6929643169091347E-3</v>
-      </c>
-      <c r="E10" s="21">
-        <v>1.4371462285758508E-3</v>
-      </c>
-      <c r="F10" s="21">
-        <v>1.3288757421753468E-3</v>
-      </c>
-      <c r="G10" s="21">
-        <v>1.2250372814315413E-3</v>
-      </c>
-      <c r="H10" s="21">
-        <v>1.1124105654561763E-3</v>
-      </c>
-      <c r="I10" s="22">
-        <v>9.9399779575056976E-4</v>
+      <c r="D10" s="39">
+        <v>1.8332814431135814E-3</v>
+      </c>
+      <c r="E10" s="40">
+        <v>1.5562605103803771E-3</v>
+      </c>
+      <c r="F10" s="40">
+        <v>1.4390162946739814E-3</v>
+      </c>
+      <c r="G10" s="40">
+        <v>1.3265714420201183E-3</v>
+      </c>
+      <c r="H10" s="40">
+        <v>1.2046099415122828E-3</v>
+      </c>
+      <c r="I10" s="21">
+        <v>1.0763828246376026E-3</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="17"/>
@@ -3177,29 +3233,29 @@
       <c r="V10" s="12"/>
       <c r="W10" s="12"/>
     </row>
-    <row r="11" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>23</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
-      <c r="D11" s="21">
-        <v>6.5432372201373268E-2</v>
-      </c>
-      <c r="E11" s="21">
-        <v>6.413668166273219E-2</v>
-      </c>
-      <c r="F11" s="21">
-        <v>6.4441168939312829E-2</v>
-      </c>
-      <c r="G11" s="21">
-        <v>6.5166107795682493E-2</v>
-      </c>
-      <c r="H11" s="21">
-        <v>6.5675962022637771E-2</v>
-      </c>
-      <c r="I11" s="22">
-        <v>6.6099652828773406E-2</v>
+      <c r="D11" s="39">
+        <v>6.0386443255951883E-2</v>
+      </c>
+      <c r="E11" s="40">
+        <v>5.9190672102368662E-2</v>
+      </c>
+      <c r="F11" s="40">
+        <v>5.947167832346071E-2</v>
+      </c>
+      <c r="G11" s="40">
+        <v>6.0140712283890521E-2</v>
+      </c>
+      <c r="H11" s="40">
+        <v>6.0611248232825508E-2</v>
+      </c>
+      <c r="I11" s="21">
+        <v>6.1002265400047218E-2</v>
       </c>
       <c r="J11" s="6"/>
       <c r="K11" s="17"/>
@@ -3214,29 +3270,29 @@
       <c r="V11" s="12"/>
       <c r="W11" s="12"/>
     </row>
-    <row r="12" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
         <v>24</v>
       </c>
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
-      <c r="D12" s="21">
-        <v>1.8962240994336798E-3</v>
-      </c>
-      <c r="E12" s="21">
-        <v>1.8783794942384144E-3</v>
-      </c>
-      <c r="F12" s="21">
-        <v>1.8874896347854707E-3</v>
-      </c>
-      <c r="G12" s="21">
-        <v>1.9264528606344575E-3</v>
-      </c>
-      <c r="H12" s="21">
-        <v>1.9478645084892816E-3</v>
-      </c>
-      <c r="I12" s="22">
-        <v>1.9699711567569742E-3</v>
+      <c r="D12" s="39">
+        <v>2.0955254558132322E-3</v>
+      </c>
+      <c r="E12" s="40">
+        <v>2.0758053054118195E-3</v>
+      </c>
+      <c r="F12" s="40">
+        <v>2.0858729611430665E-3</v>
+      </c>
+      <c r="G12" s="40">
+        <v>2.1289313905932246E-3</v>
+      </c>
+      <c r="H12" s="40">
+        <v>2.1525934952696148E-3</v>
+      </c>
+      <c r="I12" s="21">
+        <v>2.1770236479090061E-3</v>
       </c>
       <c r="J12" s="6"/>
       <c r="K12" s="17"/>
@@ -3251,29 +3307,29 @@
       <c r="V12" s="12"/>
       <c r="W12" s="12"/>
     </row>
-    <row r="13" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>32</v>
       </c>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
-      <c r="D13" s="21">
-        <v>0.23858387382720853</v>
-      </c>
-      <c r="E13" s="21">
-        <v>0.23858387382720853</v>
-      </c>
-      <c r="F13" s="21">
-        <v>0.24216263193461662</v>
-      </c>
-      <c r="G13" s="21">
-        <v>0.24741147715881523</v>
-      </c>
-      <c r="H13" s="21">
-        <v>0.2519445707615322</v>
-      </c>
-      <c r="I13" s="22">
-        <v>0.25623908049042199</v>
+      <c r="D13" s="39">
+        <v>0.14591128106802229</v>
+      </c>
+      <c r="E13" s="40">
+        <v>0.14591128106802229</v>
+      </c>
+      <c r="F13" s="40">
+        <v>0.1480999502840426</v>
+      </c>
+      <c r="G13" s="40">
+        <v>0.15130999846753909</v>
+      </c>
+      <c r="H13" s="40">
+        <v>0.15408231280783155</v>
+      </c>
+      <c r="I13" s="21">
+        <v>0.15670871586705595</v>
       </c>
       <c r="J13" s="6"/>
       <c r="K13" s="17"/>
@@ -3288,28 +3344,28 @@
       <c r="V13" s="12"/>
       <c r="W13" s="12"/>
     </row>
-    <row r="14" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
         <v>25</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
-      <c r="D14" s="21">
+      <c r="D14" s="39">
         <v>0</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="40">
         <v>0</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="40">
         <v>0</v>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="40">
         <v>0</v>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="40">
         <v>0</v>
       </c>
-      <c r="I14" s="22">
+      <c r="I14" s="21">
         <v>0</v>
       </c>
       <c r="J14" s="6"/>
@@ -3325,29 +3381,29 @@
       <c r="V14" s="12"/>
       <c r="W14" s="12"/>
     </row>
-    <row r="15" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>26</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
-      <c r="D15" s="21">
-        <v>5.0243652820669716E-3</v>
-      </c>
-      <c r="E15" s="21">
-        <v>4.4830412785429041E-3</v>
-      </c>
-      <c r="F15" s="21">
-        <v>4.2837991382750143E-3</v>
-      </c>
-      <c r="G15" s="21">
-        <v>4.093679102931908E-3</v>
-      </c>
-      <c r="H15" s="21">
-        <v>3.9506202323650848E-3</v>
-      </c>
-      <c r="I15" s="22">
-        <v>3.7486553457022052E-3</v>
+      <c r="D15" s="39">
+        <v>3.5214917516320715E-3</v>
+      </c>
+      <c r="E15" s="40">
+        <v>3.2269425825402881E-3</v>
+      </c>
+      <c r="F15" s="40">
+        <v>3.1303434559383039E-3</v>
+      </c>
+      <c r="G15" s="40">
+        <v>3.0442210976844995E-3</v>
+      </c>
+      <c r="H15" s="40">
+        <v>2.9813432117180099E-3</v>
+      </c>
+      <c r="I15" s="21">
+        <v>2.8856253567603155E-3</v>
       </c>
       <c r="K15" s="17"/>
       <c r="L15" s="17"/>
@@ -3361,29 +3417,29 @@
       <c r="V15" s="12"/>
       <c r="W15" s="12"/>
     </row>
-    <row r="16" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
         <v>33</v>
       </c>
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
-      <c r="D16" s="21">
-        <v>1.8592397439458876E-2</v>
-      </c>
-      <c r="E16" s="21">
-        <v>3.1309957431340553E-2</v>
-      </c>
-      <c r="F16" s="21">
-        <v>4.7680833484252942E-2</v>
-      </c>
-      <c r="G16" s="21">
-        <v>6.4960193499700447E-2</v>
-      </c>
-      <c r="H16" s="21">
-        <v>7.4229638074639906E-2</v>
-      </c>
-      <c r="I16" s="22">
-        <v>8.7710350705439727E-2</v>
+      <c r="D16" s="39">
+        <v>1.083784990620164E-2</v>
+      </c>
+      <c r="E16" s="40">
+        <v>1.8251149176182178E-2</v>
+      </c>
+      <c r="F16" s="40">
+        <v>2.7794033469196691E-2</v>
+      </c>
+      <c r="G16" s="40">
+        <v>3.7866489747761072E-2</v>
+      </c>
+      <c r="H16" s="40">
+        <v>4.326981921853925E-2</v>
+      </c>
+      <c r="I16" s="21">
+        <v>5.1127974176606743E-2</v>
       </c>
       <c r="K16" s="17"/>
       <c r="L16" s="17"/>
@@ -3397,29 +3453,29 @@
       <c r="V16" s="12"/>
       <c r="W16" s="12"/>
     </row>
-    <row r="17" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
         <v>34</v>
       </c>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
-      <c r="D17" s="21">
-        <v>7.7653111913584039E-2</v>
-      </c>
-      <c r="E17" s="21">
-        <v>8.8006860168728579E-2</v>
-      </c>
-      <c r="F17" s="21">
-        <v>0.10333903570988845</v>
-      </c>
-      <c r="G17" s="21">
-        <v>0.10826310581756424</v>
-      </c>
-      <c r="H17" s="21">
-        <v>0.11976801831620994</v>
-      </c>
-      <c r="I17" s="22">
-        <v>0.13038112796514584</v>
+      <c r="D17" s="39">
+        <v>4.3538030286300135E-2</v>
+      </c>
+      <c r="E17" s="40">
+        <v>4.934310099114015E-2</v>
+      </c>
+      <c r="F17" s="40">
+        <v>5.7939443193224069E-2</v>
+      </c>
+      <c r="G17" s="40">
+        <v>6.0700238069267581E-2</v>
+      </c>
+      <c r="H17" s="40">
+        <v>6.7150735885307386E-2</v>
+      </c>
+      <c r="I17" s="21">
+        <v>7.3101223611303667E-2</v>
       </c>
       <c r="K17" s="17"/>
       <c r="L17" s="17"/>
@@ -3433,29 +3489,29 @@
       <c r="V17" s="12"/>
       <c r="W17" s="12"/>
     </row>
-    <row r="18" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="18" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
-      <c r="D18" s="21">
-        <v>1.2618859832078139E-2</v>
-      </c>
-      <c r="E18" s="21">
-        <v>1.1490371525986231E-2</v>
-      </c>
-      <c r="F18" s="21">
-        <v>1.1308501497513472E-2</v>
-      </c>
-      <c r="G18" s="21">
-        <v>1.1214602609362563E-2</v>
-      </c>
-      <c r="H18" s="21">
-        <v>1.0725152861097499E-2</v>
-      </c>
-      <c r="I18" s="22">
-        <v>1.0379030468090878E-2</v>
+      <c r="D18" s="39">
+        <v>8.3181014684816767E-3</v>
+      </c>
+      <c r="E18" s="40">
+        <v>7.5742244177036564E-3</v>
+      </c>
+      <c r="F18" s="40">
+        <v>7.4543393115178817E-3</v>
+      </c>
+      <c r="G18" s="40">
+        <v>7.3924430316787675E-3</v>
+      </c>
+      <c r="H18" s="40">
+        <v>7.069807490594297E-3</v>
+      </c>
+      <c r="I18" s="21">
+        <v>6.8416504919545408E-3</v>
       </c>
       <c r="K18" s="17"/>
       <c r="L18" s="17"/>
@@ -3469,29 +3525,29 @@
       <c r="V18" s="12"/>
       <c r="W18" s="12"/>
     </row>
-    <row r="19" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
         <v>28</v>
       </c>
       <c r="B19" s="20"/>
       <c r="C19" s="20"/>
-      <c r="D19" s="21">
-        <v>9.8577044175359035E-3</v>
-      </c>
-      <c r="E19" s="21">
-        <v>8.0653945234384662E-3</v>
-      </c>
-      <c r="F19" s="21">
-        <v>7.2767781700355917E-3</v>
-      </c>
-      <c r="G19" s="21">
-        <v>6.5051887606266453E-3</v>
-      </c>
-      <c r="H19" s="21">
-        <v>5.6780377445006767E-3</v>
-      </c>
-      <c r="I19" s="22">
-        <v>4.812352065651615E-3</v>
+      <c r="D19" s="39">
+        <v>1.0326697636983477E-2</v>
+      </c>
+      <c r="E19" s="40">
+        <v>8.4491162484410225E-3</v>
+      </c>
+      <c r="F19" s="40">
+        <v>7.6229804374823452E-3</v>
+      </c>
+      <c r="G19" s="40">
+        <v>6.8146816497148197E-3</v>
+      </c>
+      <c r="H19" s="40">
+        <v>5.9481778389024794E-3</v>
+      </c>
+      <c r="I19" s="21">
+        <v>5.0413060282364797E-3</v>
       </c>
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
@@ -3505,29 +3561,29 @@
       <c r="V19" s="12"/>
       <c r="W19" s="12"/>
     </row>
-    <row r="20" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
         <v>29</v>
       </c>
       <c r="B20" s="20"/>
       <c r="C20" s="20"/>
-      <c r="D20" s="21">
-        <v>5.1189236643329604E-2</v>
-      </c>
-      <c r="E20" s="21">
-        <v>4.1882102708178749E-2</v>
-      </c>
-      <c r="F20" s="21">
-        <v>3.7786963776712389E-2</v>
-      </c>
-      <c r="G20" s="21">
-        <v>3.3780242617629949E-2</v>
-      </c>
-      <c r="H20" s="21">
-        <v>2.9485000306557835E-2</v>
-      </c>
-      <c r="I20" s="22">
-        <v>2.4989654615879993E-2</v>
+      <c r="D20" s="39">
+        <v>2.9369331995899497E-2</v>
+      </c>
+      <c r="E20" s="40">
+        <v>2.4029453451190497E-2</v>
+      </c>
+      <c r="F20" s="40">
+        <v>2.1679906891518535E-2</v>
+      </c>
+      <c r="G20" s="40">
+        <v>1.9381089178021307E-2</v>
+      </c>
+      <c r="H20" s="40">
+        <v>1.6916735229638102E-2</v>
+      </c>
+      <c r="I20" s="21">
+        <v>1.433757389254366E-2</v>
       </c>
       <c r="K20" s="17"/>
       <c r="L20" s="17"/>
@@ -3541,33 +3597,33 @@
       <c r="V20" s="12"/>
       <c r="W20" s="12"/>
     </row>
-    <row r="21" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A21" s="24" t="s">
+    <row r="21" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="24">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="24">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="D21" s="26">
-        <v>6.1046941060865507E-2</v>
-      </c>
-      <c r="E21" s="26">
-        <v>4.9947497231617219E-2</v>
-      </c>
-      <c r="F21" s="26">
-        <v>4.5063741946747983E-2</v>
-      </c>
-      <c r="G21" s="26">
-        <v>4.0285431378256596E-2</v>
-      </c>
-      <c r="H21" s="26">
-        <v>3.5163038051058512E-2</v>
-      </c>
-      <c r="I21" s="27">
-        <v>2.9802006681531608E-2</v>
+      <c r="D21" s="41">
+        <v>3.9696029632882976E-2</v>
+      </c>
+      <c r="E21" s="25">
+        <v>3.2478569699631518E-2</v>
+      </c>
+      <c r="F21" s="25">
+        <v>2.9302887329000882E-2</v>
+      </c>
+      <c r="G21" s="25">
+        <v>2.6195770827736126E-2</v>
+      </c>
+      <c r="H21" s="25">
+        <v>2.2864913068540584E-2</v>
+      </c>
+      <c r="I21" s="26">
+        <v>1.9378879920780141E-2</v>
       </c>
       <c r="K21" s="17"/>
       <c r="L21" s="17"/>
@@ -3581,7 +3637,7 @@
       <c r="V21" s="12"/>
       <c r="W21" s="12"/>
     </row>
-    <row r="22" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
       <c r="K22" s="17"/>
       <c r="L22" s="17"/>
@@ -3595,7 +3651,7 @@
       <c r="V22" s="12"/>
       <c r="W22" s="12"/>
     </row>
-    <row r="23" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="6"/>
       <c r="K23" s="17"/>
       <c r="L23" s="17"/>
@@ -3609,7 +3665,7 @@
       <c r="V23" s="13"/>
       <c r="W23" s="13"/>
     </row>
-    <row r="24" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="K24" s="17"/>
       <c r="L24" s="17"/>
@@ -3623,21 +3679,21 @@
       <c r="V24" s="14"/>
       <c r="W24" s="14"/>
     </row>
-    <row r="25" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="6"/>
       <c r="K25" s="17"/>
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
       <c r="N25" s="17"/>
     </row>
-    <row r="26" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="K26" s="17"/>
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
       <c r="N26" s="17"/>
     </row>
-    <row r="27" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:23" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
@@ -3653,7 +3709,7 @@
       <c r="M27" s="17"/>
       <c r="N27" s="17"/>
     </row>
-    <row r="28" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -3669,7 +3725,7 @@
       <c r="M28" s="17"/>
       <c r="N28" s="17"/>
     </row>
-    <row r="29" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="17"/>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
@@ -3686,7 +3742,7 @@
       <c r="N29" s="17"/>
       <c r="O29" s="9"/>
     </row>
-    <row r="30" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="17"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -3709,7 +3765,7 @@
       <c r="U30" s="12"/>
       <c r="V30" s="12"/>
     </row>
-    <row r="31" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="17"/>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
@@ -3732,7 +3788,7 @@
       <c r="U31" s="12"/>
       <c r="V31" s="12"/>
     </row>
-    <row r="32" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="17"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -3755,7 +3811,7 @@
       <c r="U32" s="12"/>
       <c r="V32" s="12"/>
     </row>
-    <row r="33" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="17"/>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
@@ -3778,7 +3834,7 @@
       <c r="U33" s="12"/>
       <c r="V33" s="12"/>
     </row>
-    <row r="34" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="17"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
@@ -3801,7 +3857,7 @@
       <c r="U34" s="12"/>
       <c r="V34" s="12"/>
     </row>
-    <row r="35" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="17"/>
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
@@ -3824,7 +3880,7 @@
       <c r="U35" s="12"/>
       <c r="V35" s="12"/>
     </row>
-    <row r="36" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="17"/>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
@@ -3847,7 +3903,7 @@
       <c r="U36" s="12"/>
       <c r="V36" s="12"/>
     </row>
-    <row r="37" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="17"/>
       <c r="B37" s="17"/>
       <c r="C37" s="17"/>
@@ -3870,7 +3926,7 @@
       <c r="U37" s="12"/>
       <c r="V37" s="12"/>
     </row>
-    <row r="38" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="17"/>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
@@ -3893,7 +3949,7 @@
       <c r="U38" s="12"/>
       <c r="V38" s="12"/>
     </row>
-    <row r="39" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="17"/>
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>
@@ -3915,7 +3971,7 @@
       <c r="U39" s="12"/>
       <c r="V39" s="12"/>
     </row>
-    <row r="40" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="17"/>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
@@ -3937,7 +3993,7 @@
       <c r="U40" s="16"/>
       <c r="V40" s="16"/>
     </row>
-    <row r="41" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="17"/>
       <c r="B41" s="17"/>
       <c r="C41" s="17"/>
@@ -3959,7 +4015,7 @@
       <c r="U41" s="15"/>
       <c r="V41" s="15"/>
     </row>
-    <row r="42" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="17"/>
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
@@ -3975,7 +4031,7 @@
       <c r="M42" s="17"/>
       <c r="N42" s="17"/>
     </row>
-    <row r="43" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="17"/>
       <c r="B43" s="17"/>
       <c r="C43" s="17"/>
@@ -3991,7 +4047,7 @@
       <c r="M43" s="17"/>
       <c r="N43" s="17"/>
     </row>
-    <row r="44" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="17"/>
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
@@ -4007,7 +4063,7 @@
       <c r="M44" s="17"/>
       <c r="N44" s="17"/>
     </row>
-    <row r="45" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="17"/>
       <c r="B45" s="17"/>
       <c r="C45" s="17"/>
@@ -4023,7 +4079,7 @@
       <c r="M45" s="17"/>
       <c r="N45" s="17"/>
     </row>
-    <row r="46" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="17"/>
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
@@ -4046,7 +4102,7 @@
       <c r="V46" s="12"/>
       <c r="W46" s="12"/>
     </row>
-    <row r="47" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="17"/>
       <c r="B47" s="17"/>
       <c r="C47" s="17"/>
@@ -4062,7 +4118,7 @@
       <c r="M47" s="17"/>
       <c r="N47" s="17"/>
     </row>
-    <row r="48" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="17"/>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
@@ -4078,7 +4134,7 @@
       <c r="M48" s="17"/>
       <c r="N48" s="17"/>
     </row>
-    <row r="49" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="17"/>
       <c r="B49" s="17"/>
       <c r="C49" s="17"/>
@@ -4094,7 +4150,7 @@
       <c r="M49" s="17"/>
       <c r="N49" s="17"/>
     </row>
-    <row r="50" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="17"/>
       <c r="B50" s="17"/>
       <c r="C50" s="17"/>
@@ -4110,7 +4166,7 @@
       <c r="M50" s="17"/>
       <c r="N50" s="17"/>
     </row>
-    <row r="51" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="17"/>
       <c r="B51" s="17"/>
       <c r="C51" s="17"/>
@@ -4126,7 +4182,7 @@
       <c r="M51" s="17"/>
       <c r="N51" s="17"/>
     </row>
-    <row r="52" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="17"/>
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
@@ -4142,7 +4198,7 @@
       <c r="M52" s="17"/>
       <c r="N52" s="17"/>
     </row>
-    <row r="53" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="17"/>
       <c r="B53" s="17"/>
       <c r="C53" s="17"/>
@@ -4158,7 +4214,7 @@
       <c r="M53" s="17"/>
       <c r="N53" s="17"/>
     </row>
-    <row r="54" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="17"/>
       <c r="B54" s="17"/>
       <c r="C54" s="17"/>
@@ -4174,7 +4230,7 @@
       <c r="M54" s="17"/>
       <c r="N54" s="17"/>
     </row>
-    <row r="55" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="17"/>
       <c r="B55" s="17"/>
       <c r="C55" s="17"/>
@@ -4190,7 +4246,7 @@
       <c r="M55" s="17"/>
       <c r="N55" s="17"/>
     </row>
-    <row r="56" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="17"/>
       <c r="B56" s="17"/>
       <c r="C56" s="17"/>
@@ -4206,7 +4262,7 @@
       <c r="M56" s="17"/>
       <c r="N56" s="17"/>
     </row>
-    <row r="57" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="17"/>
       <c r="B57" s="17"/>
       <c r="C57" s="17"/>
@@ -4222,7 +4278,7 @@
       <c r="M57" s="17"/>
       <c r="N57" s="17"/>
     </row>
-    <row r="58" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="17"/>
       <c r="B58" s="17"/>
       <c r="C58" s="17"/>
@@ -4238,7 +4294,7 @@
       <c r="M58" s="17"/>
       <c r="N58" s="17"/>
     </row>
-    <row r="59" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="17"/>
       <c r="B59" s="17"/>
       <c r="C59" s="17"/>
@@ -4254,7 +4310,7 @@
       <c r="M59" s="17"/>
       <c r="N59" s="17"/>
     </row>
-    <row r="60" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="17"/>
       <c r="B60" s="17"/>
       <c r="C60" s="17"/>
@@ -4270,7 +4326,7 @@
       <c r="M60" s="17"/>
       <c r="N60" s="17"/>
     </row>
-    <row r="61" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="17"/>
       <c r="B61" s="17"/>
       <c r="C61" s="17"/>
@@ -4286,7 +4342,7 @@
       <c r="M61" s="17"/>
       <c r="N61" s="17"/>
     </row>
-    <row r="62" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="17"/>
       <c r="B62" s="17"/>
       <c r="C62" s="17"/>
@@ -4302,7 +4358,7 @@
       <c r="M62" s="17"/>
       <c r="N62" s="17"/>
     </row>
-    <row r="63" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="17"/>
       <c r="B63" s="17"/>
       <c r="C63" s="17"/>
@@ -4318,7 +4374,7 @@
       <c r="M63" s="17"/>
       <c r="N63" s="17"/>
     </row>
-    <row r="64" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="17"/>
       <c r="B64" s="17"/>
       <c r="C64" s="17"/>
@@ -4334,7 +4390,7 @@
       <c r="M64" s="17"/>
       <c r="N64" s="17"/>
     </row>
-    <row r="65" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="17"/>
       <c r="B65" s="17"/>
       <c r="C65" s="17"/>
@@ -4350,7 +4406,7 @@
       <c r="M65" s="17"/>
       <c r="N65" s="17"/>
     </row>
-    <row r="66" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="17"/>
       <c r="B66" s="17"/>
       <c r="C66" s="17"/>
@@ -4366,7 +4422,7 @@
       <c r="M66" s="17"/>
       <c r="N66" s="17"/>
     </row>
-    <row r="67" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="17"/>
       <c r="B67" s="17"/>
       <c r="C67" s="17"/>
@@ -4382,7 +4438,7 @@
       <c r="M67" s="17"/>
       <c r="N67" s="17"/>
     </row>
-    <row r="68" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="17"/>
       <c r="B68" s="17"/>
       <c r="C68" s="17"/>
@@ -4398,7 +4454,7 @@
       <c r="M68" s="17"/>
       <c r="N68" s="17"/>
     </row>
-    <row r="69" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="17"/>
       <c r="B69" s="17"/>
       <c r="C69" s="17"/>
@@ -4414,7 +4470,7 @@
       <c r="M69" s="17"/>
       <c r="N69" s="17"/>
     </row>
-    <row r="70" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="17"/>
       <c r="B70" s="17"/>
       <c r="C70" s="17"/>
@@ -4430,7 +4486,7 @@
       <c r="M70" s="17"/>
       <c r="N70" s="17"/>
     </row>
-    <row r="71" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="17"/>
       <c r="B71" s="17"/>
       <c r="C71" s="17"/>
@@ -4446,7 +4502,7 @@
       <c r="M71" s="17"/>
       <c r="N71" s="17"/>
     </row>
-    <row r="72" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="17"/>
       <c r="B72" s="17"/>
       <c r="C72" s="17"/>
@@ -4462,7 +4518,7 @@
       <c r="M72" s="17"/>
       <c r="N72" s="17"/>
     </row>
-    <row r="73" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="17"/>
       <c r="B73" s="17"/>
       <c r="C73" s="17"/>
@@ -4478,7 +4534,7 @@
       <c r="M73" s="17"/>
       <c r="N73" s="17"/>
     </row>
-    <row r="74" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="17"/>
       <c r="B74" s="17"/>
       <c r="C74" s="17"/>
@@ -4494,7 +4550,7 @@
       <c r="M74" s="17"/>
       <c r="N74" s="17"/>
     </row>
-    <row r="75" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="17"/>
       <c r="B75" s="17"/>
       <c r="C75" s="17"/>
@@ -4510,7 +4566,7 @@
       <c r="M75" s="17"/>
       <c r="N75" s="17"/>
     </row>
-    <row r="76" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="17"/>
       <c r="B76" s="17"/>
       <c r="C76" s="17"/>
@@ -4526,7 +4582,7 @@
       <c r="M76" s="17"/>
       <c r="N76" s="17"/>
     </row>
-    <row r="77" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="17"/>
       <c r="B77" s="17"/>
       <c r="C77" s="17"/>
@@ -4542,7 +4598,7 @@
       <c r="M77" s="17"/>
       <c r="N77" s="17"/>
     </row>
-    <row r="78" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="17"/>
       <c r="B78" s="17"/>
       <c r="C78" s="17"/>
@@ -4558,7 +4614,7 @@
       <c r="M78" s="17"/>
       <c r="N78" s="17"/>
     </row>
-    <row r="79" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="17"/>
       <c r="B79" s="17"/>
       <c r="C79" s="17"/>
@@ -4574,7 +4630,7 @@
       <c r="M79" s="17"/>
       <c r="N79" s="17"/>
     </row>
-    <row r="80" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="17"/>
       <c r="B80" s="17"/>
       <c r="C80" s="17"/>
@@ -4590,7 +4646,7 @@
       <c r="M80" s="17"/>
       <c r="N80" s="17"/>
     </row>
-    <row r="81" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="17"/>
       <c r="B81" s="17"/>
       <c r="C81" s="17"/>
@@ -4606,7 +4662,7 @@
       <c r="M81" s="17"/>
       <c r="N81" s="17"/>
     </row>
-    <row r="82" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="17"/>
       <c r="B82" s="17"/>
       <c r="C82" s="17"/>
@@ -4622,7 +4678,7 @@
       <c r="M82" s="17"/>
       <c r="N82" s="17"/>
     </row>
-    <row r="83" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="17"/>
       <c r="B83" s="17"/>
       <c r="C83" s="17"/>
@@ -4638,7 +4694,7 @@
       <c r="M83" s="17"/>
       <c r="N83" s="17"/>
     </row>
-    <row r="84" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="17"/>
       <c r="B84" s="17"/>
       <c r="C84" s="17"/>
@@ -4654,7 +4710,7 @@
       <c r="M84" s="17"/>
       <c r="N84" s="17"/>
     </row>
-    <row r="85" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="17"/>
       <c r="B85" s="17"/>
       <c r="C85" s="17"/>
@@ -4670,7 +4726,7 @@
       <c r="M85" s="17"/>
       <c r="N85" s="17"/>
     </row>
-    <row r="86" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="17"/>
       <c r="B86" s="17"/>
       <c r="C86" s="17"/>
@@ -4686,7 +4742,7 @@
       <c r="M86" s="17"/>
       <c r="N86" s="17"/>
     </row>
-    <row r="87" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="17"/>
       <c r="B87" s="17"/>
       <c r="C87" s="17"/>
@@ -4702,7 +4758,7 @@
       <c r="M87" s="17"/>
       <c r="N87" s="17"/>
     </row>
-    <row r="88" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="17"/>
       <c r="B88" s="17"/>
       <c r="C88" s="17"/>
@@ -4718,7 +4774,7 @@
       <c r="M88" s="17"/>
       <c r="N88" s="17"/>
     </row>
-    <row r="89" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="17"/>
       <c r="B89" s="17"/>
       <c r="C89" s="17"/>
@@ -4734,7 +4790,7 @@
       <c r="M89" s="17"/>
       <c r="N89" s="17"/>
     </row>
-    <row r="90" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="17"/>
       <c r="B90" s="17"/>
       <c r="C90" s="17"/>
@@ -4750,7 +4806,7 @@
       <c r="M90" s="17"/>
       <c r="N90" s="17"/>
     </row>
-    <row r="91" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91" s="17"/>
       <c r="B91" s="17"/>
       <c r="C91" s="17"/>
@@ -4766,7 +4822,7 @@
       <c r="M91" s="17"/>
       <c r="N91" s="17"/>
     </row>
-    <row r="92" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="17"/>
       <c r="B92" s="17"/>
       <c r="C92" s="17"/>
@@ -4782,7 +4838,7 @@
       <c r="M92" s="17"/>
       <c r="N92" s="17"/>
     </row>
-    <row r="93" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93" s="17"/>
       <c r="B93" s="17"/>
       <c r="C93" s="17"/>
@@ -4798,7 +4854,7 @@
       <c r="M93" s="17"/>
       <c r="N93" s="17"/>
     </row>
-    <row r="94" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A94" s="17"/>
       <c r="B94" s="17"/>
       <c r="C94" s="17"/>
@@ -4814,7 +4870,7 @@
       <c r="M94" s="17"/>
       <c r="N94" s="17"/>
     </row>
-    <row r="95" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A95" s="17"/>
       <c r="B95" s="17"/>
       <c r="C95" s="17"/>
@@ -4845,7 +4901,7 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:W57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.6640625" style="6" customWidth="1"/>
@@ -4853,23 +4909,23 @@
     <col min="4" max="7" width="12" style="6" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.33203125" style="6" customWidth="1"/>
     <col min="9" max="9" width="15.33203125" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="6"/>
+    <col min="10" max="16384" width="10.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:23" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -4885,32 +4941,32 @@
       <c r="M4" s="17"/>
       <c r="N4" s="17"/>
     </row>
-    <row r="5" spans="1:23" ht="28" x14ac:dyDescent="0.2">
-      <c r="A5" s="29" t="s">
+    <row r="5" spans="1:23" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="28" t="s">
+      <c r="G5" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="28" t="s">
+      <c r="I5" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J5" s="17"/>
@@ -4919,7 +4975,7 @@
       <c r="M5" s="17"/>
       <c r="N5" s="17"/>
     </row>
-    <row r="6" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
         <v>18</v>
       </c>
@@ -4929,23 +4985,23 @@
       <c r="C6" s="20">
         <v>3.5</v>
       </c>
-      <c r="D6" s="21">
-        <v>4.360983185911782</v>
-      </c>
-      <c r="E6" s="21">
-        <v>3.5818852639327883</v>
-      </c>
-      <c r="F6" s="21">
-        <v>3.2520723397202684</v>
-      </c>
-      <c r="G6" s="21">
-        <v>2.9152961907188062</v>
-      </c>
-      <c r="H6" s="21">
-        <v>2.6548635225774988</v>
-      </c>
-      <c r="I6" s="22">
-        <v>2.3803711562910252</v>
+      <c r="D6" s="36">
+        <v>4.2241743934784219</v>
+      </c>
+      <c r="E6" s="37">
+        <v>3.4755999948608971</v>
+      </c>
+      <c r="F6" s="37">
+        <v>3.1592191811646622</v>
+      </c>
+      <c r="G6" s="37">
+        <v>2.836386269749791</v>
+      </c>
+      <c r="H6" s="37">
+        <v>2.5868037140148745</v>
+      </c>
+      <c r="I6" s="38">
+        <v>2.3233400285324723</v>
       </c>
       <c r="J6" s="17"/>
       <c r="K6" s="17"/>
@@ -4953,33 +5009,33 @@
       <c r="M6" s="17"/>
       <c r="N6" s="17"/>
     </row>
-    <row r="7" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="20">
         <v>95</v>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="22">
         <v>255.38399999999999</v>
       </c>
-      <c r="D7" s="21">
-        <v>219.24972638383446</v>
-      </c>
-      <c r="E7" s="21">
-        <v>208.28724006464276</v>
-      </c>
-      <c r="F7" s="21">
-        <v>204.09957029071154</v>
-      </c>
-      <c r="G7" s="21">
-        <v>202.02734716248946</v>
-      </c>
-      <c r="H7" s="21">
-        <v>201.04025249921401</v>
-      </c>
-      <c r="I7" s="22">
-        <v>197.33450260179848</v>
+      <c r="D7" s="39">
+        <v>219.04441629608655</v>
+      </c>
+      <c r="E7" s="40">
+        <v>208.0921954812822</v>
+      </c>
+      <c r="F7" s="40">
+        <v>203.90844713002696</v>
+      </c>
+      <c r="G7" s="40">
+        <v>201.83816447543418</v>
+      </c>
+      <c r="H7" s="40">
+        <v>200.85351990327493</v>
+      </c>
+      <c r="I7" s="21">
+        <v>197.1512120245082</v>
       </c>
       <c r="J7" s="17"/>
       <c r="K7" s="17"/>
@@ -4987,7 +5043,7 @@
       <c r="M7" s="17"/>
       <c r="N7" s="17"/>
     </row>
-    <row r="8" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
         <v>20</v>
       </c>
@@ -4997,23 +5053,23 @@
       <c r="C8" s="20">
         <v>0.27300000000000002</v>
       </c>
-      <c r="D8" s="21">
-        <v>0.82374095757109045</v>
-      </c>
-      <c r="E8" s="21">
-        <v>0.69805476340583328</v>
-      </c>
-      <c r="F8" s="21">
-        <v>0.64665167559305992</v>
-      </c>
-      <c r="G8" s="21">
-        <v>0.59496676851881947</v>
-      </c>
-      <c r="H8" s="21">
-        <v>0.55523715336535773</v>
-      </c>
-      <c r="I8" s="22">
-        <v>0.50217339760076396</v>
+      <c r="D8" s="39">
+        <v>0.79479945188345769</v>
+      </c>
+      <c r="E8" s="40">
+        <v>0.67457977698315363</v>
+      </c>
+      <c r="F8" s="40">
+        <v>0.62551567073807013</v>
+      </c>
+      <c r="G8" s="40">
+        <v>0.57623020300292993</v>
+      </c>
+      <c r="H8" s="40">
+        <v>0.53835939360199037</v>
+      </c>
+      <c r="I8" s="21">
+        <v>0.4877275048469652</v>
       </c>
       <c r="J8" s="17"/>
       <c r="K8" s="17"/>
@@ -5028,7 +5084,7 @@
       <c r="V8" s="12"/>
       <c r="W8" s="12"/>
     </row>
-    <row r="9" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>21</v>
       </c>
@@ -5038,23 +5094,23 @@
       <c r="C9" s="20">
         <v>0.20300000000000001</v>
       </c>
-      <c r="D9" s="21">
-        <v>0.3029344361918489</v>
-      </c>
-      <c r="E9" s="21">
-        <v>0.26402046693887932</v>
-      </c>
-      <c r="F9" s="21">
-        <v>0.25615615589732377</v>
-      </c>
-      <c r="G9" s="21">
-        <v>0.24334453363791048</v>
-      </c>
-      <c r="H9" s="21">
-        <v>0.23336819121790645</v>
-      </c>
-      <c r="I9" s="22">
-        <v>0.22158058189358057</v>
+      <c r="D9" s="39">
+        <v>0.29673301052998635</v>
+      </c>
+      <c r="E9" s="40">
+        <v>0.25860816656743169</v>
+      </c>
+      <c r="F9" s="40">
+        <v>0.25089713295586447</v>
+      </c>
+      <c r="G9" s="40">
+        <v>0.23833968345922379</v>
+      </c>
+      <c r="H9" s="40">
+        <v>0.22855923260762018</v>
+      </c>
+      <c r="I9" s="21">
+        <v>0.21700434646693012</v>
       </c>
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
@@ -5062,29 +5118,29 @@
       <c r="M9" s="17"/>
       <c r="N9" s="17"/>
     </row>
-    <row r="10" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>22</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
-      <c r="D10" s="21">
-        <v>2.5581962313850431E-3</v>
-      </c>
-      <c r="E10" s="21">
-        <v>2.1716358869300952E-3</v>
-      </c>
-      <c r="F10" s="21">
-        <v>2.0080310504231582E-3</v>
-      </c>
-      <c r="G10" s="21">
-        <v>1.851123337546725E-3</v>
-      </c>
-      <c r="H10" s="21">
-        <v>1.6809359109815395E-3</v>
-      </c>
-      <c r="I10" s="22">
-        <v>1.5020053226736906E-3</v>
+      <c r="D10" s="39">
+        <v>2.5645777759405377E-3</v>
+      </c>
+      <c r="E10" s="40">
+        <v>2.1770531379606186E-3</v>
+      </c>
+      <c r="F10" s="40">
+        <v>2.013040181255219E-3</v>
+      </c>
+      <c r="G10" s="40">
+        <v>1.8557410544799847E-3</v>
+      </c>
+      <c r="H10" s="40">
+        <v>1.6851290871262214E-3</v>
+      </c>
+      <c r="I10" s="21">
+        <v>1.5057521477888382E-3</v>
       </c>
       <c r="J10" s="17"/>
       <c r="K10" s="17"/>
@@ -5092,29 +5148,29 @@
       <c r="M10" s="17"/>
       <c r="N10" s="17"/>
     </row>
-    <row r="11" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>23</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
-      <c r="D11" s="21">
-        <v>7.891371089949889E-2</v>
-      </c>
-      <c r="E11" s="21">
-        <v>7.7351063158914754E-2</v>
-      </c>
-      <c r="F11" s="21">
-        <v>7.7718285377952015E-2</v>
-      </c>
-      <c r="G11" s="21">
-        <v>7.8592586788808816E-2</v>
-      </c>
-      <c r="H11" s="21">
-        <v>7.9207488674728682E-2</v>
-      </c>
-      <c r="I11" s="22">
-        <v>7.9718474485899735E-2</v>
+      <c r="D11" s="39">
+        <v>7.8621509449242358E-2</v>
+      </c>
+      <c r="E11" s="40">
+        <v>7.7064647875990031E-2</v>
+      </c>
+      <c r="F11" s="40">
+        <v>7.743051034570432E-2</v>
+      </c>
+      <c r="G11" s="40">
+        <v>7.8301574395939003E-2</v>
+      </c>
+      <c r="H11" s="40">
+        <v>7.8914199425013792E-2</v>
+      </c>
+      <c r="I11" s="21">
+        <v>7.9423293159467293E-2</v>
       </c>
       <c r="J11" s="17"/>
       <c r="K11" s="17"/>
@@ -5122,29 +5178,29 @@
       <c r="M11" s="17"/>
       <c r="N11" s="17"/>
     </row>
-    <row r="12" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
         <v>24</v>
       </c>
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
-      <c r="D12" s="21">
-        <v>4.584410076699616E-3</v>
-      </c>
-      <c r="E12" s="21">
-        <v>4.541268030410715E-3</v>
-      </c>
-      <c r="F12" s="21">
-        <v>4.5632931803582062E-3</v>
-      </c>
-      <c r="G12" s="21">
-        <v>4.6574927031130158E-3</v>
-      </c>
-      <c r="H12" s="21">
-        <v>4.7092586173916673E-3</v>
-      </c>
-      <c r="I12" s="22">
-        <v>4.7627048008415714E-3</v>
+      <c r="D12" s="39">
+        <v>4.5372294806964534E-3</v>
+      </c>
+      <c r="E12" s="40">
+        <v>4.4945314320915834E-3</v>
+      </c>
+      <c r="F12" s="40">
+        <v>4.5163299095372263E-3</v>
+      </c>
+      <c r="G12" s="40">
+        <v>4.6095599750331029E-3</v>
+      </c>
+      <c r="H12" s="40">
+        <v>4.6607931388275145E-3</v>
+      </c>
+      <c r="I12" s="21">
+        <v>4.7136892792518014E-3</v>
       </c>
       <c r="J12" s="17"/>
       <c r="K12" s="17"/>
@@ -5152,29 +5208,29 @@
       <c r="M12" s="17"/>
       <c r="N12" s="17"/>
     </row>
-    <row r="13" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>32</v>
       </c>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
-      <c r="D13" s="21">
-        <v>0.17014806056324897</v>
-      </c>
-      <c r="E13" s="21">
-        <v>0.17014806056324897</v>
-      </c>
-      <c r="F13" s="21">
-        <v>0.17270028147169769</v>
-      </c>
-      <c r="G13" s="21">
-        <v>0.17644353880408914</v>
-      </c>
-      <c r="H13" s="21">
-        <v>0.1796763519547909</v>
-      </c>
-      <c r="I13" s="22">
-        <v>0.1827390170449294</v>
+      <c r="D13" s="39">
+        <v>0.16441019680915883</v>
+      </c>
+      <c r="E13" s="40">
+        <v>0.16441019680915883</v>
+      </c>
+      <c r="F13" s="40">
+        <v>0.1668763497612962</v>
+      </c>
+      <c r="G13" s="40">
+        <v>0.17049337409109774</v>
+      </c>
+      <c r="H13" s="40">
+        <v>0.17361716783047174</v>
+      </c>
+      <c r="I13" s="21">
+        <v>0.17657655137303663</v>
       </c>
       <c r="J13" s="17"/>
       <c r="K13" s="17"/>
@@ -5182,28 +5238,28 @@
       <c r="M13" s="17"/>
       <c r="N13" s="17"/>
     </row>
-    <row r="14" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
         <v>25</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
-      <c r="D14" s="21">
+      <c r="D14" s="39">
         <v>0</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="40">
         <v>0</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="40">
         <v>0</v>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="40">
         <v>0</v>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="40">
         <v>0</v>
       </c>
-      <c r="I14" s="22">
+      <c r="I14" s="21">
         <v>0</v>
       </c>
       <c r="J14" s="17"/>
@@ -5212,29 +5268,29 @@
       <c r="M14" s="17"/>
       <c r="N14" s="17"/>
     </row>
-    <row r="15" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>26</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
-      <c r="D15" s="21">
-        <v>3.3745811654783322E-3</v>
-      </c>
-      <c r="E15" s="21">
-        <v>3.0043321441419724E-3</v>
-      </c>
-      <c r="F15" s="21">
-        <v>2.8671276693971806E-3</v>
-      </c>
-      <c r="G15" s="21">
-        <v>2.7357289202581485E-3</v>
-      </c>
-      <c r="H15" s="21">
-        <v>2.6367043568428289E-3</v>
-      </c>
-      <c r="I15" s="22">
-        <v>2.4974518151246539E-3</v>
+      <c r="D15" s="39">
+        <v>3.2864537123932233E-3</v>
+      </c>
+      <c r="E15" s="40">
+        <v>2.9314379368366363E-3</v>
+      </c>
+      <c r="F15" s="40">
+        <v>2.8006392056989715E-3</v>
+      </c>
+      <c r="G15" s="40">
+        <v>2.6757623301220941E-3</v>
+      </c>
+      <c r="H15" s="40">
+        <v>2.5817755199620462E-3</v>
+      </c>
+      <c r="I15" s="21">
+        <v>2.4491651272583177E-3</v>
       </c>
       <c r="J15" s="17"/>
       <c r="K15" s="17"/>
@@ -5242,29 +5298,29 @@
       <c r="M15" s="17"/>
       <c r="N15" s="17"/>
     </row>
-    <row r="16" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
         <v>33</v>
       </c>
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
-      <c r="D16" s="21">
-        <v>1.1076434621920222E-2</v>
-      </c>
-      <c r="E16" s="21">
-        <v>1.8652930458947978E-2</v>
-      </c>
-      <c r="F16" s="21">
-        <v>2.8405892060274478E-2</v>
-      </c>
-      <c r="G16" s="21">
-        <v>3.870008365890764E-2</v>
-      </c>
-      <c r="H16" s="21">
-        <v>4.4222362168183024E-2</v>
-      </c>
-      <c r="I16" s="22">
-        <v>5.2253506758231864E-2</v>
+      <c r="D16" s="39">
+        <v>1.0704238746839252E-2</v>
+      </c>
+      <c r="E16" s="40">
+        <v>1.8026145395706291E-2</v>
+      </c>
+      <c r="F16" s="40">
+        <v>2.7451383121819998E-2</v>
+      </c>
+      <c r="G16" s="40">
+        <v>3.7399664165199041E-2</v>
+      </c>
+      <c r="H16" s="40">
+        <v>4.2736380320489757E-2</v>
+      </c>
+      <c r="I16" s="21">
+        <v>5.0497658388446796E-2</v>
       </c>
       <c r="J16" s="17"/>
       <c r="K16" s="17"/>
@@ -5272,29 +5328,29 @@
       <c r="M16" s="17"/>
       <c r="N16" s="17"/>
     </row>
-    <row r="17" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
         <v>34</v>
       </c>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
-      <c r="D17" s="21">
-        <v>4.234894698048669E-2</v>
-      </c>
-      <c r="E17" s="21">
-        <v>4.7995473244551577E-2</v>
-      </c>
-      <c r="F17" s="21">
-        <v>5.6357037553921019E-2</v>
-      </c>
-      <c r="G17" s="21">
-        <v>5.9042431336339185E-2</v>
-      </c>
-      <c r="H17" s="21">
-        <v>6.5316757212197041E-2</v>
-      </c>
-      <c r="I17" s="22">
-        <v>7.1104728959176786E-2</v>
+      <c r="D17" s="39">
+        <v>4.0819677151294809E-2</v>
+      </c>
+      <c r="E17" s="40">
+        <v>4.6262300771467438E-2</v>
+      </c>
+      <c r="F17" s="40">
+        <v>5.4321919249006416E-2</v>
+      </c>
+      <c r="G17" s="40">
+        <v>5.6910340332366867E-2</v>
+      </c>
+      <c r="H17" s="40">
+        <v>6.2958092988709038E-2</v>
+      </c>
+      <c r="I17" s="21">
+        <v>6.8537054330567004E-2</v>
       </c>
       <c r="J17" s="17"/>
       <c r="K17" s="17"/>
@@ -5302,29 +5358,29 @@
       <c r="M17" s="17"/>
       <c r="N17" s="17"/>
     </row>
-    <row r="18" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="18" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
-      <c r="D18" s="21">
-        <v>1.0008449102626455E-2</v>
-      </c>
-      <c r="E18" s="21">
-        <v>9.1134064502214653E-3</v>
-      </c>
-      <c r="F18" s="21">
-        <v>8.969159113498092E-3</v>
-      </c>
-      <c r="G18" s="21">
-        <v>8.8946846954161465E-3</v>
-      </c>
-      <c r="H18" s="21">
-        <v>8.5064853684570264E-3</v>
-      </c>
-      <c r="I18" s="22">
-        <v>8.231963866531803E-3</v>
+      <c r="D18" s="39">
+        <v>9.7405992367162932E-3</v>
+      </c>
+      <c r="E18" s="40">
+        <v>8.8695100512243344E-3</v>
+      </c>
+      <c r="F18" s="40">
+        <v>8.7291231157882246E-3</v>
+      </c>
+      <c r="G18" s="40">
+        <v>8.6566418099949544E-3</v>
+      </c>
+      <c r="H18" s="40">
+        <v>8.2788316189155459E-3</v>
+      </c>
+      <c r="I18" s="21">
+        <v>8.0116569643116347E-3</v>
       </c>
       <c r="J18" s="17"/>
       <c r="K18" s="17"/>
@@ -5332,29 +5388,29 @@
       <c r="M18" s="17"/>
       <c r="N18" s="17"/>
     </row>
-    <row r="19" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
         <v>28</v>
       </c>
       <c r="B19" s="20"/>
       <c r="C19" s="20"/>
-      <c r="D19" s="21">
-        <v>1.2325258857988956E-2</v>
-      </c>
-      <c r="E19" s="21">
-        <v>1.0084302701990963E-2</v>
-      </c>
-      <c r="F19" s="21">
-        <v>9.098281993351845E-3</v>
-      </c>
-      <c r="G19" s="21">
-        <v>8.1335503681947106E-3</v>
-      </c>
-      <c r="H19" s="21">
-        <v>7.0993491022016365E-3</v>
-      </c>
-      <c r="I19" s="22">
-        <v>6.0169672788546093E-3</v>
+      <c r="D19" s="39">
+        <v>1.2333585197823444E-2</v>
+      </c>
+      <c r="E19" s="40">
+        <v>1.0091115161855544E-2</v>
+      </c>
+      <c r="F19" s="40">
+        <v>9.1044283460296662E-3</v>
+      </c>
+      <c r="G19" s="40">
+        <v>8.1390449955454861E-3</v>
+      </c>
+      <c r="H19" s="40">
+        <v>7.1041450739462997E-3</v>
+      </c>
+      <c r="I19" s="21">
+        <v>6.0210320465738073E-3</v>
       </c>
       <c r="J19" s="17"/>
       <c r="K19" s="17"/>
@@ -5362,29 +5418,29 @@
       <c r="M19" s="17"/>
       <c r="N19" s="17"/>
     </row>
-    <row r="20" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
         <v>29</v>
       </c>
       <c r="B20" s="20"/>
       <c r="C20" s="20"/>
-      <c r="D20" s="21">
-        <v>2.6840385706558046E-2</v>
-      </c>
-      <c r="E20" s="21">
-        <v>2.1960315578092953E-2</v>
-      </c>
-      <c r="F20" s="21">
-        <v>1.981308472156831E-2</v>
-      </c>
-      <c r="G20" s="21">
-        <v>1.7712214531264078E-2</v>
-      </c>
-      <c r="H20" s="21">
-        <v>1.5460062166977432E-2</v>
-      </c>
-      <c r="I20" s="22">
-        <v>1.3102988294928794E-2</v>
+      <c r="D20" s="39">
+        <v>2.5943779940930289E-2</v>
+      </c>
+      <c r="E20" s="40">
+        <v>2.1226729042579329E-2</v>
+      </c>
+      <c r="F20" s="40">
+        <v>1.9151226647304901E-2</v>
+      </c>
+      <c r="G20" s="40">
+        <v>1.7120536235564809E-2</v>
+      </c>
+      <c r="H20" s="40">
+        <v>1.4943617245975843E-2</v>
+      </c>
+      <c r="I20" s="21">
+        <v>1.266528166207233E-2</v>
       </c>
       <c r="J20" s="17"/>
       <c r="K20" s="17"/>
@@ -5392,33 +5448,33 @@
       <c r="M20" s="17"/>
       <c r="N20" s="17"/>
     </row>
-    <row r="21" spans="1:14" ht="15" x14ac:dyDescent="0.2">
-      <c r="A21" s="24" t="s">
+    <row r="21" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="24">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="24">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="D21" s="26">
-        <v>3.9165644564547006E-2</v>
-      </c>
-      <c r="E21" s="26">
-        <v>3.2044618280083918E-2</v>
-      </c>
-      <c r="F21" s="26">
-        <v>2.8911366714920155E-2</v>
-      </c>
-      <c r="G21" s="26">
-        <v>2.5845764899458789E-2</v>
-      </c>
-      <c r="H21" s="26">
-        <v>2.2559411269179069E-2</v>
-      </c>
-      <c r="I21" s="27">
-        <v>1.9119955573783404E-2</v>
+      <c r="D21" s="41">
+        <v>3.8277365138753731E-2</v>
+      </c>
+      <c r="E21" s="25">
+        <v>3.1317844204434869E-2</v>
+      </c>
+      <c r="F21" s="25">
+        <v>2.8255654993334565E-2</v>
+      </c>
+      <c r="G21" s="25">
+        <v>2.5259581231110294E-2</v>
+      </c>
+      <c r="H21" s="25">
+        <v>2.2047762319922143E-2</v>
+      </c>
+      <c r="I21" s="26">
+        <v>1.8686313708646138E-2</v>
       </c>
       <c r="J21" s="17"/>
       <c r="K21" s="17"/>
@@ -5426,7 +5482,7 @@
       <c r="M21" s="17"/>
       <c r="N21" s="17"/>
     </row>
-    <row r="22" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
@@ -5442,7 +5498,7 @@
       <c r="M22" s="17"/>
       <c r="N22" s="17"/>
     </row>
-    <row r="23" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="17"/>
@@ -5458,7 +5514,7 @@
       <c r="M23" s="17"/>
       <c r="N23" s="17"/>
     </row>
-    <row r="24" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
@@ -5474,7 +5530,7 @@
       <c r="M24" s="17"/>
       <c r="N24" s="17"/>
     </row>
-    <row r="25" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="17"/>
@@ -5490,7 +5546,7 @@
       <c r="M25" s="17"/>
       <c r="N25" s="17"/>
     </row>
-    <row r="26" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -5506,7 +5562,7 @@
       <c r="M26" s="17"/>
       <c r="N26" s="17"/>
     </row>
-    <row r="27" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
@@ -5522,7 +5578,7 @@
       <c r="M27" s="17"/>
       <c r="N27" s="17"/>
     </row>
-    <row r="28" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -5538,7 +5594,7 @@
       <c r="M28" s="17"/>
       <c r="N28" s="17"/>
     </row>
-    <row r="29" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="17"/>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
@@ -5554,7 +5610,7 @@
       <c r="M29" s="17"/>
       <c r="N29" s="17"/>
     </row>
-    <row r="30" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="17"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -5570,7 +5626,7 @@
       <c r="M30" s="17"/>
       <c r="N30" s="17"/>
     </row>
-    <row r="31" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="17"/>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
@@ -5586,7 +5642,7 @@
       <c r="M31" s="17"/>
       <c r="N31" s="17"/>
     </row>
-    <row r="32" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="17"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -5602,7 +5658,7 @@
       <c r="M32" s="17"/>
       <c r="N32" s="17"/>
     </row>
-    <row r="33" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="17"/>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
@@ -5618,7 +5674,7 @@
       <c r="M33" s="17"/>
       <c r="N33" s="17"/>
     </row>
-    <row r="34" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="17"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
@@ -5634,7 +5690,7 @@
       <c r="M34" s="17"/>
       <c r="N34" s="17"/>
     </row>
-    <row r="35" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="17"/>
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
@@ -5650,7 +5706,7 @@
       <c r="M35" s="17"/>
       <c r="N35" s="17"/>
     </row>
-    <row r="36" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="17"/>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
@@ -5666,7 +5722,7 @@
       <c r="M36" s="17"/>
       <c r="N36" s="17"/>
     </row>
-    <row r="37" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="17"/>
       <c r="B37" s="17"/>
       <c r="C37" s="17"/>
@@ -5682,7 +5738,7 @@
       <c r="M37" s="17"/>
       <c r="N37" s="17"/>
     </row>
-    <row r="38" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="17"/>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
@@ -5698,7 +5754,7 @@
       <c r="M38" s="17"/>
       <c r="N38" s="17"/>
     </row>
-    <row r="39" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="17"/>
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>
@@ -5714,7 +5770,7 @@
       <c r="M39" s="17"/>
       <c r="N39" s="17"/>
     </row>
-    <row r="40" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="17"/>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
@@ -5730,7 +5786,7 @@
       <c r="M40" s="17"/>
       <c r="N40" s="17"/>
     </row>
-    <row r="41" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="17"/>
       <c r="B41" s="17"/>
       <c r="C41" s="17"/>
@@ -5746,7 +5802,7 @@
       <c r="M41" s="17"/>
       <c r="N41" s="17"/>
     </row>
-    <row r="42" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="17"/>
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
@@ -5762,7 +5818,7 @@
       <c r="M42" s="17"/>
       <c r="N42" s="17"/>
     </row>
-    <row r="43" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="17"/>
       <c r="B43" s="17"/>
       <c r="C43" s="17"/>
@@ -5778,7 +5834,7 @@
       <c r="M43" s="17"/>
       <c r="N43" s="17"/>
     </row>
-    <row r="44" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="17"/>
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
@@ -5794,7 +5850,7 @@
       <c r="M44" s="17"/>
       <c r="N44" s="17"/>
     </row>
-    <row r="45" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="17"/>
       <c r="B45" s="17"/>
       <c r="C45" s="17"/>
@@ -5810,7 +5866,7 @@
       <c r="M45" s="17"/>
       <c r="N45" s="17"/>
     </row>
-    <row r="46" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="17"/>
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
@@ -5826,7 +5882,7 @@
       <c r="M46" s="17"/>
       <c r="N46" s="17"/>
     </row>
-    <row r="47" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="17"/>
       <c r="B47" s="17"/>
       <c r="C47" s="17"/>
@@ -5842,7 +5898,7 @@
       <c r="M47" s="17"/>
       <c r="N47" s="17"/>
     </row>
-    <row r="48" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="17"/>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
@@ -5858,7 +5914,7 @@
       <c r="M48" s="17"/>
       <c r="N48" s="17"/>
     </row>
-    <row r="49" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="17"/>
       <c r="B49" s="17"/>
       <c r="C49" s="17"/>
@@ -5874,7 +5930,7 @@
       <c r="M49" s="17"/>
       <c r="N49" s="17"/>
     </row>
-    <row r="50" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="17"/>
       <c r="B50" s="17"/>
       <c r="C50" s="17"/>
@@ -5890,7 +5946,7 @@
       <c r="M50" s="17"/>
       <c r="N50" s="17"/>
     </row>
-    <row r="51" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="17"/>
       <c r="B51" s="17"/>
       <c r="C51" s="17"/>
@@ -5906,7 +5962,7 @@
       <c r="M51" s="17"/>
       <c r="N51" s="17"/>
     </row>
-    <row r="52" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="17"/>
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
@@ -5922,7 +5978,7 @@
       <c r="M52" s="17"/>
       <c r="N52" s="17"/>
     </row>
-    <row r="53" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="17"/>
       <c r="B53" s="17"/>
       <c r="C53" s="17"/>
@@ -5938,7 +5994,7 @@
       <c r="M53" s="17"/>
       <c r="N53" s="17"/>
     </row>
-    <row r="54" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="17"/>
       <c r="B54" s="17"/>
       <c r="C54" s="17"/>
@@ -5954,7 +6010,7 @@
       <c r="M54" s="17"/>
       <c r="N54" s="17"/>
     </row>
-    <row r="55" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="17"/>
       <c r="B55" s="17"/>
       <c r="C55" s="17"/>
@@ -5970,7 +6026,7 @@
       <c r="M55" s="17"/>
       <c r="N55" s="17"/>
     </row>
-    <row r="56" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="17"/>
       <c r="B56" s="17"/>
       <c r="C56" s="17"/>
@@ -5986,7 +6042,7 @@
       <c r="M56" s="17"/>
       <c r="N56" s="17"/>
     </row>
-    <row r="57" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="17"/>
       <c r="B57" s="17"/>
       <c r="C57" s="17"/>
@@ -6016,31 +6072,31 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:W77"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="15.77734375" style="6" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" style="6" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.33203125" style="6" customWidth="1"/>
     <col min="9" max="9" width="17.6640625" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="6"/>
+    <col min="10" max="16384" width="10.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:23" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -6056,32 +6112,32 @@
       <c r="M4" s="17"/>
       <c r="N4" s="17"/>
     </row>
-    <row r="5" spans="1:23" ht="28" x14ac:dyDescent="0.2">
-      <c r="A5" s="29" t="s">
+    <row r="5" spans="1:23" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="28" t="s">
+      <c r="G5" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="28" t="s">
+      <c r="I5" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J5" s="17"/>
@@ -6097,7 +6153,7 @@
       <c r="V5" s="13"/>
       <c r="W5" s="13"/>
     </row>
-    <row r="6" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
         <v>18</v>
       </c>
@@ -6107,23 +6163,23 @@
       <c r="C6" s="20">
         <v>3.5</v>
       </c>
-      <c r="D6" s="21">
-        <v>4.543098876856047</v>
-      </c>
-      <c r="E6" s="21">
-        <v>3.5938560970482727</v>
-      </c>
-      <c r="F6" s="21">
-        <v>3.1804623226242428</v>
-      </c>
-      <c r="G6" s="21">
-        <v>2.7531927812335586</v>
-      </c>
-      <c r="H6" s="21">
-        <v>2.4212499434831565</v>
-      </c>
-      <c r="I6" s="22">
-        <v>2.0659342906510161</v>
+      <c r="D6" s="36">
+        <v>3.6562396584325163</v>
+      </c>
+      <c r="E6" s="37">
+        <v>2.8641379198030101</v>
+      </c>
+      <c r="F6" s="37">
+        <v>2.5171571517657432</v>
+      </c>
+      <c r="G6" s="37">
+        <v>2.1576542120072655</v>
+      </c>
+      <c r="H6" s="37">
+        <v>1.8781015879867551</v>
+      </c>
+      <c r="I6" s="38">
+        <v>1.5827666642678129</v>
       </c>
       <c r="J6" s="17"/>
       <c r="K6" s="17"/>
@@ -6138,33 +6194,33 @@
       <c r="V6" s="14"/>
       <c r="W6" s="14"/>
     </row>
-    <row r="7" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="20">
         <v>95</v>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="22">
         <v>255.38399999999999</v>
       </c>
-      <c r="D7" s="21">
-        <v>177.50307872830982</v>
-      </c>
-      <c r="E7" s="21">
-        <v>168.62792479189429</v>
-      </c>
-      <c r="F7" s="21">
-        <v>165.23761598818356</v>
-      </c>
-      <c r="G7" s="21">
-        <v>163.55995831837427</v>
-      </c>
-      <c r="H7" s="21">
-        <v>162.8108983656918</v>
-      </c>
-      <c r="I7" s="22">
-        <v>159.80982538445318</v>
+      <c r="D7" s="39">
+        <v>134.2976320612687</v>
+      </c>
+      <c r="E7" s="40">
+        <v>127.58275045820523</v>
+      </c>
+      <c r="F7" s="40">
+        <v>125.01766568583501</v>
+      </c>
+      <c r="G7" s="40">
+        <v>123.74836120909593</v>
+      </c>
+      <c r="H7" s="40">
+        <v>123.17835029553839</v>
+      </c>
+      <c r="I7" s="21">
+        <v>120.90781912928209</v>
       </c>
       <c r="J7" s="17"/>
       <c r="K7" s="17"/>
@@ -6172,7 +6228,7 @@
       <c r="M7" s="17"/>
       <c r="N7" s="17"/>
     </row>
-    <row r="8" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
         <v>20</v>
       </c>
@@ -6182,23 +6238,23 @@
       <c r="C8" s="20">
         <v>0.27300000000000002</v>
       </c>
-      <c r="D8" s="21">
-        <v>0.82472728007698859</v>
-      </c>
-      <c r="E8" s="21">
-        <v>0.6973610138095061</v>
-      </c>
-      <c r="F8" s="21">
-        <v>0.6451204390260602</v>
-      </c>
-      <c r="G8" s="21">
-        <v>0.59252410435224334</v>
-      </c>
-      <c r="H8" s="21">
-        <v>0.55207294469519241</v>
-      </c>
-      <c r="I8" s="22">
-        <v>0.49811942912931462</v>
+      <c r="D8" s="39">
+        <v>0.68759061720994008</v>
+      </c>
+      <c r="E8" s="40">
+        <v>0.57616121272789333</v>
+      </c>
+      <c r="F8" s="40">
+        <v>0.5299481799439576</v>
+      </c>
+      <c r="G8" s="40">
+        <v>0.48318631068170953</v>
+      </c>
+      <c r="H8" s="40">
+        <v>0.44715176129482426</v>
+      </c>
+      <c r="I8" s="21">
+        <v>0.39933829664296555</v>
       </c>
       <c r="J8" s="17"/>
       <c r="K8" s="17"/>
@@ -6206,7 +6262,7 @@
       <c r="M8" s="17"/>
       <c r="N8" s="17"/>
     </row>
-    <row r="9" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>21</v>
       </c>
@@ -6216,23 +6272,23 @@
       <c r="C9" s="20">
         <v>0.20300000000000001</v>
       </c>
-      <c r="D9" s="21">
-        <v>0.35228599810460942</v>
-      </c>
-      <c r="E9" s="21">
-        <v>0.30687543412440083</v>
-      </c>
-      <c r="F9" s="21">
-        <v>0.29756816912321132</v>
-      </c>
-      <c r="G9" s="21">
-        <v>0.28249960829756804</v>
-      </c>
-      <c r="H9" s="21">
-        <v>0.27072320181902709</v>
-      </c>
-      <c r="I9" s="22">
-        <v>0.25683526909243748</v>
+      <c r="D9" s="39">
+        <v>0.27185320708025812</v>
+      </c>
+      <c r="E9" s="40">
+        <v>0.23685980016057984</v>
+      </c>
+      <c r="F9" s="40">
+        <v>0.22972817960629671</v>
+      </c>
+      <c r="G9" s="40">
+        <v>0.21815317093386508</v>
+      </c>
+      <c r="H9" s="40">
+        <v>0.20912023593937487</v>
+      </c>
+      <c r="I9" s="21">
+        <v>0.19845949393621559</v>
       </c>
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
@@ -6240,29 +6296,29 @@
       <c r="M9" s="17"/>
       <c r="N9" s="17"/>
     </row>
-    <row r="10" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>22</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
-      <c r="D10" s="21">
-        <v>1.9433508580068328E-3</v>
-      </c>
-      <c r="E10" s="21">
-        <v>1.6496977098035698E-3</v>
-      </c>
-      <c r="F10" s="21">
-        <v>1.5254142027374665E-3</v>
-      </c>
-      <c r="G10" s="21">
-        <v>1.4062182103795164E-3</v>
-      </c>
-      <c r="H10" s="21">
-        <v>1.2769341947986002E-3</v>
-      </c>
-      <c r="I10" s="22">
-        <v>1.1410083779884233E-3</v>
+      <c r="D10" s="39">
+        <v>1.4680106547375312E-3</v>
+      </c>
+      <c r="E10" s="40">
+        <v>1.2461845503140888E-3</v>
+      </c>
+      <c r="F10" s="40">
+        <v>1.1523005705739028E-3</v>
+      </c>
+      <c r="G10" s="40">
+        <v>1.0622597083885996E-3</v>
+      </c>
+      <c r="H10" s="40">
+        <v>9.645983357249448E-4</v>
+      </c>
+      <c r="I10" s="21">
+        <v>8.6191973473577694E-4</v>
       </c>
       <c r="J10" s="17"/>
       <c r="K10" s="17"/>
@@ -6270,29 +6326,29 @@
       <c r="M10" s="17"/>
       <c r="N10" s="17"/>
     </row>
-    <row r="11" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>23</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
-      <c r="D11" s="21">
-        <v>7.4355079909860872E-2</v>
-      </c>
-      <c r="E11" s="21">
-        <v>7.2882702089863624E-2</v>
-      </c>
-      <c r="F11" s="21">
-        <v>7.3228710877562955E-2</v>
-      </c>
-      <c r="G11" s="21">
-        <v>7.4052506267851426E-2</v>
-      </c>
-      <c r="H11" s="21">
-        <v>7.4631886940020334E-2</v>
-      </c>
-      <c r="I11" s="22">
-        <v>7.5113354487159431E-2</v>
+      <c r="D11" s="39">
+        <v>5.7166895693836282E-2</v>
+      </c>
+      <c r="E11" s="40">
+        <v>5.6034877957324689E-2</v>
+      </c>
+      <c r="F11" s="40">
+        <v>5.6300902125404888E-2</v>
+      </c>
+      <c r="G11" s="40">
+        <v>5.6934266048983134E-2</v>
+      </c>
+      <c r="H11" s="40">
+        <v>5.7379715028300471E-2</v>
+      </c>
+      <c r="I11" s="21">
+        <v>5.7749884828139766E-2</v>
       </c>
       <c r="J11" s="17"/>
       <c r="K11" s="17"/>
@@ -6301,29 +6357,29 @@
       <c r="N11" s="17"/>
       <c r="O11" s="9"/>
     </row>
-    <row r="12" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
         <v>24</v>
       </c>
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
-      <c r="D12" s="21">
-        <v>2.1720505021974273E-3</v>
-      </c>
-      <c r="E12" s="21">
-        <v>2.1516102052475754E-3</v>
-      </c>
-      <c r="F12" s="21">
-        <v>2.162045514743026E-3</v>
-      </c>
-      <c r="G12" s="21">
-        <v>2.2066763652304768E-3</v>
-      </c>
-      <c r="H12" s="21">
-        <v>2.2312025699600942E-3</v>
-      </c>
-      <c r="I12" s="22">
-        <v>2.2565248704656538E-3</v>
+      <c r="D12" s="39">
+        <v>1.8193955200215455E-3</v>
+      </c>
+      <c r="E12" s="40">
+        <v>1.8022739178024222E-3</v>
+      </c>
+      <c r="F12" s="40">
+        <v>1.811014946303764E-3</v>
+      </c>
+      <c r="G12" s="40">
+        <v>1.8483995141807391E-3</v>
+      </c>
+      <c r="H12" s="40">
+        <v>1.8689436345697699E-3</v>
+      </c>
+      <c r="I12" s="21">
+        <v>1.890154596308387E-3</v>
       </c>
       <c r="J12" s="17"/>
       <c r="K12" s="17"/>
@@ -6338,29 +6394,29 @@
       <c r="U12" s="12"/>
       <c r="V12" s="12"/>
     </row>
-    <row r="13" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>32</v>
       </c>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
-      <c r="D13" s="21">
-        <v>0.22665705656481611</v>
-      </c>
-      <c r="E13" s="21">
-        <v>0.22665705656481611</v>
-      </c>
-      <c r="F13" s="21">
-        <v>0.23005691241328835</v>
-      </c>
-      <c r="G13" s="21">
-        <v>0.23504336765771425</v>
-      </c>
-      <c r="H13" s="21">
-        <v>0.23934985173244583</v>
-      </c>
-      <c r="I13" s="22">
-        <v>0.2434296787506125</v>
+      <c r="D13" s="39">
+        <v>0.18125649312159778</v>
+      </c>
+      <c r="E13" s="40">
+        <v>0.18125649312159778</v>
+      </c>
+      <c r="F13" s="40">
+        <v>0.18397534051842174</v>
+      </c>
+      <c r="G13" s="40">
+        <v>0.18796298336709685</v>
+      </c>
+      <c r="H13" s="40">
+        <v>0.19140685673640725</v>
+      </c>
+      <c r="I13" s="21">
+        <v>0.19466947361259601</v>
       </c>
       <c r="J13" s="17"/>
       <c r="K13" s="17"/>
@@ -6375,28 +6431,28 @@
       <c r="U13" s="12"/>
       <c r="V13" s="12"/>
     </row>
-    <row r="14" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
         <v>25</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
-      <c r="D14" s="21">
+      <c r="D14" s="39">
         <v>0</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="40">
         <v>0</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="40">
         <v>0</v>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="40">
         <v>0</v>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="40">
         <v>0</v>
       </c>
-      <c r="I14" s="22">
+      <c r="I14" s="21">
         <v>0</v>
       </c>
       <c r="J14" s="17"/>
@@ -6412,29 +6468,29 @@
       <c r="U14" s="12"/>
       <c r="V14" s="12"/>
     </row>
-    <row r="15" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>26</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
-      <c r="D15" s="21">
-        <v>5.839419655513706E-3</v>
-      </c>
-      <c r="E15" s="21">
-        <v>5.0258559577307385E-3</v>
-      </c>
-      <c r="F15" s="21">
-        <v>4.7007354775368947E-3</v>
-      </c>
-      <c r="G15" s="21">
-        <v>4.3773423384661225E-3</v>
-      </c>
-      <c r="H15" s="21">
-        <v>4.1298134220885034E-3</v>
-      </c>
-      <c r="I15" s="22">
-        <v>3.795465571395938E-3</v>
+      <c r="D15" s="39">
+        <v>4.5007819660873522E-3</v>
+      </c>
+      <c r="E15" s="40">
+        <v>3.8621858410549351E-3</v>
+      </c>
+      <c r="F15" s="40">
+        <v>3.6057448904974446E-3</v>
+      </c>
+      <c r="G15" s="40">
+        <v>3.3500802377677621E-3</v>
+      </c>
+      <c r="H15" s="40">
+        <v>3.1542125900035538E-3</v>
+      </c>
+      <c r="I15" s="21">
+        <v>2.8902803552393755E-3</v>
       </c>
       <c r="J15" s="17"/>
       <c r="K15" s="17"/>
@@ -6449,29 +6505,29 @@
       <c r="U15" s="12"/>
       <c r="V15" s="12"/>
     </row>
-    <row r="16" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
         <v>33</v>
       </c>
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
-      <c r="D16" s="21">
-        <v>1.8169848757703097E-2</v>
-      </c>
-      <c r="E16" s="21">
-        <v>3.0598377266301463E-2</v>
-      </c>
-      <c r="F16" s="21">
-        <v>4.659719306620614E-2</v>
-      </c>
-      <c r="G16" s="21">
-        <v>6.3483845749536513E-2</v>
-      </c>
-      <c r="H16" s="21">
-        <v>7.2542624023989283E-2</v>
-      </c>
-      <c r="I16" s="22">
-        <v>8.5716961031644154E-2</v>
+      <c r="D16" s="39">
+        <v>1.4377016441439945E-2</v>
+      </c>
+      <c r="E16" s="40">
+        <v>2.4211174176807466E-2</v>
+      </c>
+      <c r="F16" s="40">
+        <v>3.6870346020562279E-2</v>
+      </c>
+      <c r="G16" s="40">
+        <v>5.0232024838400585E-2</v>
+      </c>
+      <c r="H16" s="40">
+        <v>5.7399844776139596E-2</v>
+      </c>
+      <c r="I16" s="21">
+        <v>6.7824128560220368E-2</v>
       </c>
       <c r="J16" s="17"/>
       <c r="K16" s="17"/>
@@ -6486,29 +6542,29 @@
       <c r="U16" s="12"/>
       <c r="V16" s="12"/>
     </row>
-    <row r="17" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
         <v>34</v>
       </c>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
-      <c r="D17" s="21">
-        <v>7.3209804299984971E-2</v>
-      </c>
-      <c r="E17" s="21">
-        <v>8.2971111539982989E-2</v>
-      </c>
-      <c r="F17" s="21">
-        <v>9.7425980677880011E-2</v>
-      </c>
-      <c r="G17" s="21">
-        <v>0.10206829571276907</v>
-      </c>
-      <c r="H17" s="21">
-        <v>0.11291489762940082</v>
-      </c>
-      <c r="I17" s="22">
-        <v>0.12292072561576077</v>
+      <c r="D17" s="39">
+        <v>5.8050750250570327E-2</v>
+      </c>
+      <c r="E17" s="40">
+        <v>6.5790850283979685E-2</v>
+      </c>
+      <c r="F17" s="40">
+        <v>7.7252648416786723E-2</v>
+      </c>
+      <c r="G17" s="40">
+        <v>8.0933710991009017E-2</v>
+      </c>
+      <c r="H17" s="40">
+        <v>8.9534381146466266E-2</v>
+      </c>
+      <c r="I17" s="21">
+        <v>9.7468370685712555E-2</v>
       </c>
       <c r="J17" s="17"/>
       <c r="K17" s="17"/>
@@ -6523,29 +6579,29 @@
       <c r="U17" s="12"/>
       <c r="V17" s="12"/>
     </row>
-    <row r="18" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="18" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
-      <c r="D18" s="21">
-        <v>9.7350158720821266E-3</v>
-      </c>
-      <c r="E18" s="21">
-        <v>8.864425999664579E-3</v>
-      </c>
-      <c r="F18" s="21">
-        <v>8.7241195347859089E-3</v>
-      </c>
-      <c r="G18" s="21">
-        <v>8.6516797756726327E-3</v>
-      </c>
-      <c r="H18" s="21">
-        <v>8.2740861474563509E-3</v>
-      </c>
-      <c r="I18" s="22">
-        <v>8.0070646388223556E-3</v>
+      <c r="D18" s="39">
+        <v>7.8236728697649392E-3</v>
+      </c>
+      <c r="E18" s="40">
+        <v>7.1240119287840076E-3</v>
+      </c>
+      <c r="F18" s="40">
+        <v>7.0112528026410404E-3</v>
+      </c>
+      <c r="G18" s="40">
+        <v>6.9530356424931895E-3</v>
+      </c>
+      <c r="H18" s="40">
+        <v>6.6495775830827603E-3</v>
+      </c>
+      <c r="I18" s="21">
+        <v>6.4349822542004954E-3</v>
       </c>
       <c r="J18" s="17"/>
       <c r="K18" s="17"/>
@@ -6560,29 +6616,29 @@
       <c r="U18" s="12"/>
       <c r="V18" s="12"/>
     </row>
-    <row r="19" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
         <v>28</v>
       </c>
       <c r="B19" s="20"/>
       <c r="C19" s="20"/>
-      <c r="D19" s="21">
-        <v>1.2424741541341639E-2</v>
-      </c>
-      <c r="E19" s="21">
-        <v>1.0165697624734066E-2</v>
-      </c>
-      <c r="F19" s="21">
-        <v>9.1717183014267348E-3</v>
-      </c>
-      <c r="G19" s="21">
-        <v>8.199199895327176E-3</v>
-      </c>
-      <c r="H19" s="21">
-        <v>7.1566511278127794E-3</v>
-      </c>
-      <c r="I19" s="22">
-        <v>6.0655329160913271E-3</v>
+      <c r="D19" s="39">
+        <v>9.367439162426593E-3</v>
+      </c>
+      <c r="E19" s="40">
+        <v>7.6642684056217611E-3</v>
+      </c>
+      <c r="F19" s="40">
+        <v>6.9148732726276325E-3</v>
+      </c>
+      <c r="G19" s="40">
+        <v>6.1816582618231487E-3</v>
+      </c>
+      <c r="H19" s="40">
+        <v>5.3956449575577178E-3</v>
+      </c>
+      <c r="I19" s="21">
+        <v>4.5730134820209847E-3</v>
       </c>
       <c r="J19" s="17"/>
       <c r="K19" s="17"/>
@@ -6597,29 +6653,29 @@
       <c r="U19" s="12"/>
       <c r="V19" s="12"/>
     </row>
-    <row r="20" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
         <v>29</v>
       </c>
       <c r="B20" s="20"/>
       <c r="C20" s="20"/>
-      <c r="D20" s="21">
-        <v>5.1302215080829411E-2</v>
-      </c>
-      <c r="E20" s="21">
-        <v>4.1974539611587695E-2</v>
-      </c>
-      <c r="F20" s="21">
-        <v>3.7870362405121344E-2</v>
-      </c>
-      <c r="G20" s="21">
-        <v>3.3854798115612789E-2</v>
-      </c>
-      <c r="H20" s="21">
-        <v>2.9550075886557739E-2</v>
-      </c>
-      <c r="I20" s="22">
-        <v>2.5044808634913991E-2</v>
+      <c r="D20" s="39">
+        <v>4.0372192368867764E-2</v>
+      </c>
+      <c r="E20" s="40">
+        <v>3.3031793756346357E-2</v>
+      </c>
+      <c r="F20" s="40">
+        <v>2.9802018366836922E-2</v>
+      </c>
+      <c r="G20" s="40">
+        <v>2.6641976764146456E-2</v>
+      </c>
+      <c r="H20" s="40">
+        <v>2.325438280446783E-2</v>
+      </c>
+      <c r="I20" s="21">
+        <v>1.9708970274619982E-2</v>
       </c>
       <c r="J20" s="17"/>
       <c r="K20" s="17"/>
@@ -6634,33 +6690,33 @@
       <c r="U20" s="12"/>
       <c r="V20" s="12"/>
     </row>
-    <row r="21" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A21" s="24" t="s">
+    <row r="21" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="24">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="24">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="D21" s="26">
-        <v>6.3726956622171052E-2</v>
-      </c>
-      <c r="E21" s="26">
-        <v>5.214023723632176E-2</v>
-      </c>
-      <c r="F21" s="26">
-        <v>4.7042080706548077E-2</v>
-      </c>
-      <c r="G21" s="26">
-        <v>4.2053998010939966E-2</v>
-      </c>
-      <c r="H21" s="26">
-        <v>3.670672701437052E-2</v>
-      </c>
-      <c r="I21" s="27">
-        <v>3.1110341551005317E-2</v>
+      <c r="D21" s="41">
+        <v>4.9739631531294355E-2</v>
+      </c>
+      <c r="E21" s="25">
+        <v>4.0696062161968118E-2</v>
+      </c>
+      <c r="F21" s="25">
+        <v>3.6716891639464552E-2</v>
+      </c>
+      <c r="G21" s="25">
+        <v>3.2823635025969605E-2</v>
+      </c>
+      <c r="H21" s="25">
+        <v>2.8650027762025548E-2</v>
+      </c>
+      <c r="I21" s="26">
+        <v>2.4281983756640965E-2</v>
       </c>
       <c r="J21" s="17"/>
       <c r="K21" s="17"/>
@@ -6674,7 +6730,7 @@
       <c r="U21" s="12"/>
       <c r="V21" s="12"/>
     </row>
-    <row r="22" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
@@ -6696,7 +6752,7 @@
       <c r="U22" s="16"/>
       <c r="V22" s="16"/>
     </row>
-    <row r="23" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="17"/>
@@ -6718,7 +6774,7 @@
       <c r="U23" s="15"/>
       <c r="V23" s="15"/>
     </row>
-    <row r="24" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
@@ -6734,7 +6790,7 @@
       <c r="M24" s="17"/>
       <c r="N24" s="17"/>
     </row>
-    <row r="25" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="17"/>
@@ -6750,7 +6806,7 @@
       <c r="M25" s="17"/>
       <c r="N25" s="17"/>
     </row>
-    <row r="26" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -6766,7 +6822,7 @@
       <c r="M26" s="17"/>
       <c r="N26" s="17"/>
     </row>
-    <row r="27" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
@@ -6782,7 +6838,7 @@
       <c r="M27" s="17"/>
       <c r="N27" s="17"/>
     </row>
-    <row r="28" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -6805,7 +6861,7 @@
       <c r="V28" s="12"/>
       <c r="W28" s="12"/>
     </row>
-    <row r="29" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="17"/>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
@@ -6821,7 +6877,7 @@
       <c r="M29" s="17"/>
       <c r="N29" s="17"/>
     </row>
-    <row r="30" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="17"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -6837,7 +6893,7 @@
       <c r="M30" s="17"/>
       <c r="N30" s="17"/>
     </row>
-    <row r="31" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="17"/>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
@@ -6853,7 +6909,7 @@
       <c r="M31" s="17"/>
       <c r="N31" s="17"/>
     </row>
-    <row r="32" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="17"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -6869,7 +6925,7 @@
       <c r="M32" s="17"/>
       <c r="N32" s="17"/>
     </row>
-    <row r="33" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="17"/>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
@@ -6885,7 +6941,7 @@
       <c r="M33" s="17"/>
       <c r="N33" s="17"/>
     </row>
-    <row r="34" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="17"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
@@ -6901,7 +6957,7 @@
       <c r="M34" s="17"/>
       <c r="N34" s="17"/>
     </row>
-    <row r="35" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="17"/>
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
@@ -6917,7 +6973,7 @@
       <c r="M35" s="17"/>
       <c r="N35" s="17"/>
     </row>
-    <row r="36" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="17"/>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
@@ -6933,7 +6989,7 @@
       <c r="M36" s="17"/>
       <c r="N36" s="17"/>
     </row>
-    <row r="37" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="17"/>
       <c r="B37" s="17"/>
       <c r="C37" s="17"/>
@@ -6949,7 +7005,7 @@
       <c r="M37" s="17"/>
       <c r="N37" s="17"/>
     </row>
-    <row r="38" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="17"/>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
@@ -6965,7 +7021,7 @@
       <c r="M38" s="17"/>
       <c r="N38" s="17"/>
     </row>
-    <row r="39" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="17"/>
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>
@@ -6981,7 +7037,7 @@
       <c r="M39" s="17"/>
       <c r="N39" s="17"/>
     </row>
-    <row r="40" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="17"/>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
@@ -6997,7 +7053,7 @@
       <c r="M40" s="17"/>
       <c r="N40" s="17"/>
     </row>
-    <row r="41" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="17"/>
       <c r="B41" s="17"/>
       <c r="C41" s="17"/>
@@ -7013,7 +7069,7 @@
       <c r="M41" s="17"/>
       <c r="N41" s="17"/>
     </row>
-    <row r="42" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="17"/>
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
@@ -7029,7 +7085,7 @@
       <c r="M42" s="17"/>
       <c r="N42" s="17"/>
     </row>
-    <row r="43" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="17"/>
       <c r="B43" s="17"/>
       <c r="C43" s="17"/>
@@ -7045,7 +7101,7 @@
       <c r="M43" s="17"/>
       <c r="N43" s="17"/>
     </row>
-    <row r="44" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="17"/>
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
@@ -7061,7 +7117,7 @@
       <c r="M44" s="17"/>
       <c r="N44" s="17"/>
     </row>
-    <row r="45" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="17"/>
       <c r="B45" s="17"/>
       <c r="C45" s="17"/>
@@ -7077,7 +7133,7 @@
       <c r="M45" s="17"/>
       <c r="N45" s="17"/>
     </row>
-    <row r="46" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="17"/>
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
@@ -7093,7 +7149,7 @@
       <c r="M46" s="17"/>
       <c r="N46" s="17"/>
     </row>
-    <row r="47" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="17"/>
       <c r="B47" s="17"/>
       <c r="C47" s="17"/>
@@ -7109,7 +7165,7 @@
       <c r="M47" s="17"/>
       <c r="N47" s="17"/>
     </row>
-    <row r="48" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="17"/>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
@@ -7125,7 +7181,7 @@
       <c r="M48" s="17"/>
       <c r="N48" s="17"/>
     </row>
-    <row r="49" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="17"/>
       <c r="B49" s="17"/>
       <c r="C49" s="17"/>
@@ -7141,7 +7197,7 @@
       <c r="M49" s="17"/>
       <c r="N49" s="17"/>
     </row>
-    <row r="50" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="17"/>
       <c r="B50" s="17"/>
       <c r="C50" s="17"/>
@@ -7157,7 +7213,7 @@
       <c r="M50" s="17"/>
       <c r="N50" s="17"/>
     </row>
-    <row r="51" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="17"/>
       <c r="B51" s="17"/>
       <c r="C51" s="17"/>
@@ -7173,7 +7229,7 @@
       <c r="M51" s="17"/>
       <c r="N51" s="17"/>
     </row>
-    <row r="52" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="17"/>
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
@@ -7189,7 +7245,7 @@
       <c r="M52" s="17"/>
       <c r="N52" s="17"/>
     </row>
-    <row r="53" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="17"/>
       <c r="B53" s="17"/>
       <c r="C53" s="17"/>
@@ -7205,7 +7261,7 @@
       <c r="M53" s="17"/>
       <c r="N53" s="17"/>
     </row>
-    <row r="54" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="17"/>
       <c r="B54" s="17"/>
       <c r="C54" s="17"/>
@@ -7221,7 +7277,7 @@
       <c r="M54" s="17"/>
       <c r="N54" s="17"/>
     </row>
-    <row r="55" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="17"/>
       <c r="B55" s="17"/>
       <c r="C55" s="17"/>
@@ -7237,7 +7293,7 @@
       <c r="M55" s="17"/>
       <c r="N55" s="17"/>
     </row>
-    <row r="56" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="17"/>
       <c r="B56" s="17"/>
       <c r="C56" s="17"/>
@@ -7253,7 +7309,7 @@
       <c r="M56" s="17"/>
       <c r="N56" s="17"/>
     </row>
-    <row r="57" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="17"/>
       <c r="B57" s="17"/>
       <c r="C57" s="17"/>
@@ -7269,7 +7325,7 @@
       <c r="M57" s="17"/>
       <c r="N57" s="17"/>
     </row>
-    <row r="58" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="17"/>
       <c r="B58" s="17"/>
       <c r="C58" s="17"/>
@@ -7285,7 +7341,7 @@
       <c r="M58" s="17"/>
       <c r="N58" s="17"/>
     </row>
-    <row r="59" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="17"/>
       <c r="B59" s="17"/>
       <c r="C59" s="17"/>
@@ -7301,7 +7357,7 @@
       <c r="M59" s="17"/>
       <c r="N59" s="17"/>
     </row>
-    <row r="60" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="17"/>
       <c r="B60" s="17"/>
       <c r="C60" s="17"/>
@@ -7317,7 +7373,7 @@
       <c r="M60" s="17"/>
       <c r="N60" s="17"/>
     </row>
-    <row r="61" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="17"/>
       <c r="B61" s="17"/>
       <c r="C61" s="17"/>
@@ -7333,7 +7389,7 @@
       <c r="M61" s="17"/>
       <c r="N61" s="17"/>
     </row>
-    <row r="62" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="17"/>
       <c r="B62" s="17"/>
       <c r="C62" s="17"/>
@@ -7349,7 +7405,7 @@
       <c r="M62" s="17"/>
       <c r="N62" s="17"/>
     </row>
-    <row r="63" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="17"/>
       <c r="B63" s="17"/>
       <c r="C63" s="17"/>
@@ -7365,7 +7421,7 @@
       <c r="M63" s="17"/>
       <c r="N63" s="17"/>
     </row>
-    <row r="64" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="17"/>
       <c r="B64" s="17"/>
       <c r="C64" s="17"/>
@@ -7381,7 +7437,7 @@
       <c r="M64" s="17"/>
       <c r="N64" s="17"/>
     </row>
-    <row r="65" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="17"/>
       <c r="B65" s="17"/>
       <c r="C65" s="17"/>
@@ -7397,7 +7453,7 @@
       <c r="M65" s="17"/>
       <c r="N65" s="17"/>
     </row>
-    <row r="66" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="17"/>
       <c r="B66" s="17"/>
       <c r="C66" s="17"/>
@@ -7413,7 +7469,7 @@
       <c r="M66" s="17"/>
       <c r="N66" s="17"/>
     </row>
-    <row r="67" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="17"/>
       <c r="B67" s="17"/>
       <c r="C67" s="17"/>
@@ -7429,7 +7485,7 @@
       <c r="M67" s="17"/>
       <c r="N67" s="17"/>
     </row>
-    <row r="68" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="17"/>
       <c r="B68" s="17"/>
       <c r="C68" s="17"/>
@@ -7445,7 +7501,7 @@
       <c r="M68" s="17"/>
       <c r="N68" s="17"/>
     </row>
-    <row r="69" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="17"/>
       <c r="B69" s="17"/>
       <c r="C69" s="17"/>
@@ -7461,7 +7517,7 @@
       <c r="M69" s="17"/>
       <c r="N69" s="17"/>
     </row>
-    <row r="70" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="17"/>
       <c r="B70" s="17"/>
       <c r="C70" s="17"/>
@@ -7477,7 +7533,7 @@
       <c r="M70" s="17"/>
       <c r="N70" s="17"/>
     </row>
-    <row r="71" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="17"/>
       <c r="B71" s="17"/>
       <c r="C71" s="17"/>
@@ -7493,7 +7549,7 @@
       <c r="M71" s="17"/>
       <c r="N71" s="17"/>
     </row>
-    <row r="72" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="17"/>
       <c r="B72" s="17"/>
       <c r="C72" s="17"/>
@@ -7509,7 +7565,7 @@
       <c r="M72" s="17"/>
       <c r="N72" s="17"/>
     </row>
-    <row r="73" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="17"/>
       <c r="B73" s="17"/>
       <c r="C73" s="17"/>
@@ -7525,7 +7581,7 @@
       <c r="M73" s="17"/>
       <c r="N73" s="17"/>
     </row>
-    <row r="74" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="17"/>
       <c r="B74" s="17"/>
       <c r="C74" s="17"/>
@@ -7541,7 +7597,7 @@
       <c r="M74" s="17"/>
       <c r="N74" s="17"/>
     </row>
-    <row r="75" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="17"/>
       <c r="B75" s="17"/>
       <c r="C75" s="17"/>
@@ -7557,7 +7613,7 @@
       <c r="M75" s="17"/>
       <c r="N75" s="17"/>
     </row>
-    <row r="76" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="17"/>
       <c r="B76" s="17"/>
       <c r="C76" s="17"/>
@@ -7573,7 +7629,7 @@
       <c r="M76" s="17"/>
       <c r="N76" s="17"/>
     </row>
-    <row r="77" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="17"/>
       <c r="B77" s="17"/>
       <c r="C77" s="17"/>
@@ -7603,31 +7659,31 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:W77"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.6640625" style="6" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.83203125" style="6" customWidth="1"/>
-    <col min="9" max="9" width="15.5" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="6"/>
+    <col min="8" max="8" width="8.77734375" style="6" customWidth="1"/>
+    <col min="9" max="9" width="15.44140625" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="10.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:23" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -7643,32 +7699,32 @@
       <c r="M4" s="17"/>
       <c r="N4" s="17"/>
     </row>
-    <row r="5" spans="1:23" ht="28" x14ac:dyDescent="0.2">
-      <c r="A5" s="29" t="s">
+    <row r="5" spans="1:23" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="28" t="s">
+      <c r="G5" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="28" t="s">
+      <c r="I5" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J5" s="17"/>
@@ -7684,7 +7740,7 @@
       <c r="V5" s="13"/>
       <c r="W5" s="13"/>
     </row>
-    <row r="6" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
         <v>18</v>
       </c>
@@ -7694,23 +7750,23 @@
       <c r="C6" s="20">
         <v>3.5</v>
       </c>
-      <c r="D6" s="21">
-        <v>3.0282419471792363</v>
-      </c>
-      <c r="E6" s="21">
-        <v>2.5514770171019618</v>
-      </c>
-      <c r="F6" s="21">
-        <v>2.3550431235381621</v>
-      </c>
-      <c r="G6" s="21">
-        <v>2.1568650471327784</v>
-      </c>
-      <c r="H6" s="21">
-        <v>2.0043262848845087</v>
-      </c>
-      <c r="I6" s="22">
-        <v>1.8386632263040665</v>
+      <c r="D6" s="36">
+        <v>2.5850358530745705</v>
+      </c>
+      <c r="E6" s="37">
+        <v>2.1359549975956811</v>
+      </c>
+      <c r="F6" s="37">
+        <v>1.9469168343869436</v>
+      </c>
+      <c r="G6" s="37">
+        <v>1.7543642003302249</v>
+      </c>
+      <c r="H6" s="37">
+        <v>1.605602864809784</v>
+      </c>
+      <c r="I6" s="38">
+        <v>1.4476569691254209</v>
       </c>
       <c r="J6" s="17"/>
       <c r="K6" s="17"/>
@@ -7725,33 +7781,33 @@
       <c r="V6" s="14"/>
       <c r="W6" s="14"/>
     </row>
-    <row r="7" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="20">
         <v>95</v>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="22">
         <v>255.38399999999999</v>
       </c>
-      <c r="D7" s="21">
-        <v>181.19841095929374</v>
-      </c>
-      <c r="E7" s="21">
-        <v>172.13849041132903</v>
-      </c>
-      <c r="F7" s="21">
-        <v>168.67760076200645</v>
-      </c>
-      <c r="G7" s="21">
-        <v>166.96501692356836</v>
-      </c>
-      <c r="H7" s="21">
-        <v>166.248976516482</v>
-      </c>
-      <c r="I7" s="22">
-        <v>163.18452986954114</v>
+      <c r="D7" s="39">
+        <v>192.51057373986595</v>
+      </c>
+      <c r="E7" s="40">
+        <v>182.88504505287256</v>
+      </c>
+      <c r="F7" s="40">
+        <v>179.20809309444113</v>
+      </c>
+      <c r="G7" s="40">
+        <v>177.38859315749406</v>
+      </c>
+      <c r="H7" s="40">
+        <v>176.56239830310795</v>
+      </c>
+      <c r="I7" s="21">
+        <v>173.30784563882634</v>
       </c>
       <c r="J7" s="17"/>
       <c r="K7" s="17"/>
@@ -7759,7 +7815,7 @@
       <c r="M7" s="17"/>
       <c r="N7" s="17"/>
     </row>
-    <row r="8" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
         <v>20</v>
       </c>
@@ -7769,23 +7825,23 @@
       <c r="C8" s="20">
         <v>0.27300000000000002</v>
       </c>
-      <c r="D8" s="21">
-        <v>0.50302717278223885</v>
-      </c>
-      <c r="E8" s="21">
-        <v>0.43774747469165998</v>
-      </c>
-      <c r="F8" s="21">
-        <v>0.41217722072477364</v>
-      </c>
-      <c r="G8" s="21">
-        <v>0.38698690501019761</v>
-      </c>
-      <c r="H8" s="21">
-        <v>0.36778044315075087</v>
-      </c>
-      <c r="I8" s="22">
-        <v>0.34157322286171293</v>
+      <c r="D8" s="39">
+        <v>0.45458837485205206</v>
+      </c>
+      <c r="E8" s="40">
+        <v>0.39303973391439145</v>
+      </c>
+      <c r="F8" s="40">
+        <v>0.3686356215901177</v>
+      </c>
+      <c r="G8" s="40">
+        <v>0.34445191399618702</v>
+      </c>
+      <c r="H8" s="40">
+        <v>0.32596911838805148</v>
+      </c>
+      <c r="I8" s="21">
+        <v>0.30090538058094196</v>
       </c>
       <c r="J8" s="17"/>
       <c r="K8" s="17"/>
@@ -7793,7 +7849,7 @@
       <c r="M8" s="17"/>
       <c r="N8" s="17"/>
     </row>
-    <row r="9" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>21</v>
       </c>
@@ -7803,23 +7859,23 @@
       <c r="C9" s="20">
         <v>0.20300000000000001</v>
       </c>
-      <c r="D9" s="21">
-        <v>0.25707110382477866</v>
-      </c>
-      <c r="E9" s="21">
-        <v>0.22378058031331624</v>
-      </c>
-      <c r="F9" s="21">
-        <v>0.2168308529882752</v>
-      </c>
-      <c r="G9" s="21">
-        <v>0.20566915356874335</v>
-      </c>
-      <c r="H9" s="21">
-        <v>0.19690490516536432</v>
-      </c>
-      <c r="I9" s="22">
-        <v>0.18659476576545198</v>
+      <c r="D9" s="39">
+        <v>0.22260889022111588</v>
+      </c>
+      <c r="E9" s="40">
+        <v>0.19385379532451832</v>
+      </c>
+      <c r="F9" s="40">
+        <v>0.18791050305603854</v>
+      </c>
+      <c r="G9" s="40">
+        <v>0.1783235860014698</v>
+      </c>
+      <c r="H9" s="40">
+        <v>0.17081504766148836</v>
+      </c>
+      <c r="I9" s="21">
+        <v>0.16197025172093449</v>
       </c>
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
@@ -7827,29 +7883,29 @@
       <c r="M9" s="17"/>
       <c r="N9" s="17"/>
     </row>
-    <row r="10" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>22</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
-      <c r="D10" s="21">
-        <v>2.0547182418996848E-3</v>
-      </c>
-      <c r="E10" s="21">
-        <v>1.744236746538956E-3</v>
-      </c>
-      <c r="F10" s="21">
-        <v>1.6128309388414698E-3</v>
-      </c>
-      <c r="G10" s="21">
-        <v>1.4868041954718201E-3</v>
-      </c>
-      <c r="H10" s="21">
-        <v>1.3501113156937424E-3</v>
-      </c>
-      <c r="I10" s="22">
-        <v>1.2063960137479921E-3</v>
+      <c r="D10" s="39">
+        <v>2.2029820519688533E-3</v>
+      </c>
+      <c r="E10" s="40">
+        <v>1.8700969157976963E-3</v>
+      </c>
+      <c r="F10" s="40">
+        <v>1.7292091629277997E-3</v>
+      </c>
+      <c r="G10" s="40">
+        <v>1.5940886154727212E-3</v>
+      </c>
+      <c r="H10" s="40">
+        <v>1.4475322873872543E-3</v>
+      </c>
+      <c r="I10" s="21">
+        <v>1.2934468150710805E-3</v>
       </c>
       <c r="J10" s="17"/>
       <c r="K10" s="17"/>
@@ -7857,29 +7913,29 @@
       <c r="M10" s="17"/>
       <c r="N10" s="17"/>
     </row>
-    <row r="11" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>23</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
-      <c r="D11" s="21">
-        <v>6.920781345095918E-2</v>
-      </c>
-      <c r="E11" s="21">
-        <v>6.7837361699455062E-2</v>
-      </c>
-      <c r="F11" s="21">
-        <v>6.8159417861058516E-2</v>
-      </c>
-      <c r="G11" s="21">
-        <v>6.8926185616025107E-2</v>
-      </c>
-      <c r="H11" s="21">
-        <v>6.9465458380241984E-2</v>
-      </c>
-      <c r="I11" s="22">
-        <v>6.9913596102983824E-2</v>
+      <c r="D11" s="39">
+        <v>7.0633762738432901E-2</v>
+      </c>
+      <c r="E11" s="40">
+        <v>6.9235074367374846E-2</v>
+      </c>
+      <c r="F11" s="40">
+        <v>6.9563766134573476E-2</v>
+      </c>
+      <c r="G11" s="40">
+        <v>7.0346332278180476E-2</v>
+      </c>
+      <c r="H11" s="40">
+        <v>7.0896716152191813E-2</v>
+      </c>
+      <c r="I11" s="21">
+        <v>7.1354087249527798E-2</v>
       </c>
       <c r="J11" s="17"/>
       <c r="K11" s="17"/>
@@ -7888,29 +7944,29 @@
       <c r="N11" s="17"/>
       <c r="O11" s="9"/>
     </row>
-    <row r="12" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
         <v>24</v>
       </c>
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
-      <c r="D12" s="21">
-        <v>2.9241079982748872E-3</v>
-      </c>
-      <c r="E12" s="21">
-        <v>2.8965903895739344E-3</v>
-      </c>
-      <c r="F12" s="21">
-        <v>2.910638852963368E-3</v>
-      </c>
-      <c r="G12" s="21">
-        <v>2.970722827414301E-3</v>
-      </c>
-      <c r="H12" s="21">
-        <v>3.0037410612650541E-3</v>
-      </c>
-      <c r="I12" s="22">
-        <v>3.0378310335599499E-3</v>
+      <c r="D12" s="39">
+        <v>2.7985206463232572E-3</v>
+      </c>
+      <c r="E12" s="40">
+        <v>2.7721848898694976E-3</v>
+      </c>
+      <c r="F12" s="40">
+        <v>2.7856299865853629E-3</v>
+      </c>
+      <c r="G12" s="40">
+        <v>2.8431334177559265E-3</v>
+      </c>
+      <c r="H12" s="40">
+        <v>2.87473355331555E-3</v>
+      </c>
+      <c r="I12" s="21">
+        <v>2.9073593972844237E-3</v>
       </c>
       <c r="J12" s="17"/>
       <c r="K12" s="17"/>
@@ -7925,29 +7981,29 @@
       <c r="U12" s="12"/>
       <c r="V12" s="12"/>
     </row>
-    <row r="13" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>32</v>
       </c>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
-      <c r="D13" s="21">
-        <v>0.12109039692659479</v>
-      </c>
-      <c r="E13" s="21">
-        <v>0.12109039692659479</v>
-      </c>
-      <c r="F13" s="21">
-        <v>0.12290675288049369</v>
-      </c>
-      <c r="G13" s="21">
-        <v>0.12557074161287879</v>
-      </c>
-      <c r="H13" s="21">
-        <v>0.12787145915448409</v>
-      </c>
-      <c r="I13" s="22">
-        <v>0.13005108629916282</v>
+      <c r="D13" s="39">
+        <v>0.10642634683273512</v>
+      </c>
+      <c r="E13" s="40">
+        <v>0.10642634683273512</v>
+      </c>
+      <c r="F13" s="40">
+        <v>0.10802274203522612</v>
+      </c>
+      <c r="G13" s="40">
+        <v>0.11036412166554631</v>
+      </c>
+      <c r="H13" s="40">
+        <v>0.11238622225536828</v>
+      </c>
+      <c r="I13" s="21">
+        <v>0.11430189649835752</v>
       </c>
       <c r="J13" s="17"/>
       <c r="K13" s="17"/>
@@ -7962,28 +8018,28 @@
       <c r="U13" s="12"/>
       <c r="V13" s="12"/>
     </row>
-    <row r="14" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
         <v>25</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
-      <c r="D14" s="21">
+      <c r="D14" s="39">
         <v>0</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="40">
         <v>0</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="40">
         <v>0</v>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="40">
         <v>0</v>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="40">
         <v>0</v>
       </c>
-      <c r="I14" s="22">
+      <c r="I14" s="21">
         <v>0</v>
       </c>
       <c r="J14" s="17"/>
@@ -7999,29 +8055,29 @@
       <c r="U14" s="12"/>
       <c r="V14" s="12"/>
     </row>
-    <row r="15" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>26</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
-      <c r="D15" s="21">
-        <v>3.3228262999437804E-3</v>
-      </c>
-      <c r="E15" s="21">
-        <v>2.9825670282250779E-3</v>
-      </c>
-      <c r="F15" s="21">
-        <v>2.8597996954429551E-3</v>
-      </c>
-      <c r="G15" s="21">
-        <v>2.7439189076908137E-3</v>
-      </c>
-      <c r="H15" s="21">
-        <v>2.6571252863280799E-3</v>
-      </c>
-      <c r="I15" s="22">
-        <v>2.5331405247801591E-3</v>
+      <c r="D15" s="39">
+        <v>2.7588051253243828E-3</v>
+      </c>
+      <c r="E15" s="40">
+        <v>2.481565160976174E-3</v>
+      </c>
+      <c r="F15" s="40">
+        <v>2.382306501173403E-3</v>
+      </c>
+      <c r="G15" s="40">
+        <v>2.2890187203803572E-3</v>
+      </c>
+      <c r="H15" s="40">
+        <v>2.2192766863316877E-3</v>
+      </c>
+      <c r="I15" s="21">
+        <v>2.1191802725047232E-3</v>
       </c>
       <c r="J15" s="17"/>
       <c r="K15" s="17"/>
@@ -8036,29 +8092,29 @@
       <c r="U15" s="12"/>
       <c r="V15" s="12"/>
     </row>
-    <row r="16" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
         <v>33</v>
       </c>
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
-      <c r="D16" s="21">
-        <v>9.587496902639497E-3</v>
-      </c>
-      <c r="E16" s="21">
-        <v>1.6145530498270628E-2</v>
-      </c>
-      <c r="F16" s="21">
-        <v>2.4587460806713989E-2</v>
-      </c>
-      <c r="G16" s="21">
-        <v>3.3497866856667557E-2</v>
-      </c>
-      <c r="H16" s="21">
-        <v>3.8277819062444367E-2</v>
-      </c>
-      <c r="I16" s="22">
-        <v>4.5229385745225448E-2</v>
+      <c r="D16" s="39">
+        <v>8.0069774471775504E-3</v>
+      </c>
+      <c r="E16" s="40">
+        <v>1.3483905119883746E-2</v>
+      </c>
+      <c r="F16" s="40">
+        <v>2.0534165086251145E-2</v>
+      </c>
+      <c r="G16" s="40">
+        <v>2.7975671561995694E-2</v>
+      </c>
+      <c r="H16" s="40">
+        <v>3.1967638380749473E-2</v>
+      </c>
+      <c r="I16" s="21">
+        <v>3.7773224365998143E-2</v>
       </c>
       <c r="J16" s="17"/>
       <c r="K16" s="17"/>
@@ -8073,29 +8129,29 @@
       <c r="U16" s="12"/>
       <c r="V16" s="12"/>
     </row>
-    <row r="17" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
         <v>34</v>
       </c>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
-      <c r="D17" s="21">
-        <v>3.7138509474004613E-2</v>
-      </c>
-      <c r="E17" s="21">
-        <v>4.2090310737205226E-2</v>
-      </c>
-      <c r="F17" s="21">
-        <v>4.942310310779479E-2</v>
-      </c>
-      <c r="G17" s="21">
-        <v>5.177809725855196E-2</v>
-      </c>
-      <c r="H17" s="21">
-        <v>5.7280456292199425E-2</v>
-      </c>
-      <c r="I17" s="22">
-        <v>6.2356300177043231E-2</v>
+      <c r="D17" s="39">
+        <v>3.0477036651838436E-2</v>
+      </c>
+      <c r="E17" s="40">
+        <v>3.4540641538750222E-2</v>
+      </c>
+      <c r="F17" s="40">
+        <v>4.0558163108785433E-2</v>
+      </c>
+      <c r="G17" s="40">
+        <v>4.2490745866252566E-2</v>
+      </c>
+      <c r="H17" s="40">
+        <v>4.7006155889840827E-2</v>
+      </c>
+      <c r="I17" s="21">
+        <v>5.1171554079169755E-2</v>
       </c>
       <c r="J17" s="17"/>
       <c r="K17" s="17"/>
@@ -8110,29 +8166,29 @@
       <c r="U17" s="12"/>
       <c r="V17" s="12"/>
     </row>
-    <row r="18" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="18" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
-      <c r="D18" s="21">
-        <v>6.3072717788188676E-3</v>
-      </c>
-      <c r="E18" s="21">
-        <v>5.7432206251919055E-3</v>
-      </c>
-      <c r="F18" s="21">
-        <v>5.6523167152298355E-3</v>
-      </c>
-      <c r="G18" s="21">
-        <v>5.6053833301873005E-3</v>
-      </c>
-      <c r="H18" s="21">
-        <v>5.3607421640706442E-3</v>
-      </c>
-      <c r="I18" s="22">
-        <v>5.1877401630595604E-3</v>
+      <c r="D18" s="39">
+        <v>5.7601199861102917E-3</v>
+      </c>
+      <c r="E18" s="40">
+        <v>5.2449999092957708E-3</v>
+      </c>
+      <c r="F18" s="40">
+        <v>5.1619818553811604E-3</v>
+      </c>
+      <c r="G18" s="40">
+        <v>5.1191199114726735E-3</v>
+      </c>
+      <c r="H18" s="40">
+        <v>4.8957012100451953E-3</v>
+      </c>
+      <c r="I18" s="21">
+        <v>4.7377070219704887E-3</v>
       </c>
       <c r="J18" s="17"/>
       <c r="K18" s="17"/>
@@ -8147,29 +8203,29 @@
       <c r="U18" s="12"/>
       <c r="V18" s="12"/>
     </row>
-    <row r="19" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
         <v>28</v>
       </c>
       <c r="B19" s="20"/>
       <c r="C19" s="20"/>
-      <c r="D19" s="21">
-        <v>1.1278148329826531E-2</v>
-      </c>
-      <c r="E19" s="21">
-        <v>9.2275759062217053E-3</v>
-      </c>
-      <c r="F19" s="21">
-        <v>8.3253240398355813E-3</v>
-      </c>
-      <c r="G19" s="21">
-        <v>7.4425526114737083E-3</v>
-      </c>
-      <c r="H19" s="21">
-        <v>6.4962134379800774E-3</v>
-      </c>
-      <c r="I19" s="22">
-        <v>5.5057869573789508E-3</v>
+      <c r="D19" s="39">
+        <v>1.1705633110997409E-2</v>
+      </c>
+      <c r="E19" s="40">
+        <v>9.5773361817251493E-3</v>
+      </c>
+      <c r="F19" s="40">
+        <v>8.640885532845359E-3</v>
+      </c>
+      <c r="G19" s="40">
+        <v>7.7246537047936503E-3</v>
+      </c>
+      <c r="H19" s="40">
+        <v>6.7424446719345048E-3</v>
+      </c>
+      <c r="I19" s="21">
+        <v>5.7144772550960076E-3</v>
       </c>
       <c r="J19" s="17"/>
       <c r="K19" s="17"/>
@@ -8184,29 +8240,29 @@
       <c r="U19" s="12"/>
       <c r="V19" s="12"/>
     </row>
-    <row r="20" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
         <v>29</v>
       </c>
       <c r="B20" s="20"/>
       <c r="C20" s="20"/>
-      <c r="D20" s="21">
-        <v>2.5884151119027501E-2</v>
-      </c>
-      <c r="E20" s="21">
-        <v>2.1177941824658871E-2</v>
-      </c>
-      <c r="F20" s="21">
-        <v>1.9107209735136663E-2</v>
-      </c>
-      <c r="G20" s="21">
-        <v>1.7081186633910967E-2</v>
-      </c>
-      <c r="H20" s="21">
-        <v>1.4909271044559845E-2</v>
-      </c>
-      <c r="I20" s="22">
-        <v>1.2636171955379793E-2</v>
+      <c r="D20" s="39">
+        <v>2.0449348910822666E-2</v>
+      </c>
+      <c r="E20" s="40">
+        <v>1.673128547249127E-2</v>
+      </c>
+      <c r="F20" s="40">
+        <v>1.5095337559625459E-2</v>
+      </c>
+      <c r="G20" s="40">
+        <v>1.3494711249423792E-2</v>
+      </c>
+      <c r="H20" s="40">
+        <v>1.1778824972633854E-2</v>
+      </c>
+      <c r="I20" s="21">
+        <v>9.9830003319197891E-3</v>
       </c>
       <c r="J20" s="17"/>
       <c r="K20" s="17"/>
@@ -8221,33 +8277,33 @@
       <c r="U20" s="12"/>
       <c r="V20" s="12"/>
     </row>
-    <row r="21" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A21" s="24" t="s">
+    <row r="21" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="24">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="24">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="D21" s="26">
-        <v>3.7162299448854033E-2</v>
-      </c>
-      <c r="E21" s="26">
-        <v>3.0405517730880578E-2</v>
-      </c>
-      <c r="F21" s="26">
-        <v>2.7432533774972245E-2</v>
-      </c>
-      <c r="G21" s="26">
-        <v>2.4523739245384674E-2</v>
-      </c>
-      <c r="H21" s="26">
-        <v>2.1405484482539924E-2</v>
-      </c>
-      <c r="I21" s="27">
-        <v>1.8141958912758743E-2</v>
+      <c r="D21" s="41">
+        <v>3.2154982021820072E-2</v>
+      </c>
+      <c r="E21" s="25">
+        <v>2.6308621654216421E-2</v>
+      </c>
+      <c r="F21" s="25">
+        <v>2.3736223092470816E-2</v>
+      </c>
+      <c r="G21" s="25">
+        <v>2.1219364954217442E-2</v>
+      </c>
+      <c r="H21" s="25">
+        <v>1.8521269644568357E-2</v>
+      </c>
+      <c r="I21" s="26">
+        <v>1.5697477587015798E-2</v>
       </c>
       <c r="J21" s="17"/>
       <c r="K21" s="17"/>
@@ -8261,7 +8317,7 @@
       <c r="U21" s="12"/>
       <c r="V21" s="12"/>
     </row>
-    <row r="22" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
@@ -8283,7 +8339,7 @@
       <c r="U22" s="16"/>
       <c r="V22" s="16"/>
     </row>
-    <row r="23" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="17"/>
@@ -8305,7 +8361,7 @@
       <c r="U23" s="15"/>
       <c r="V23" s="15"/>
     </row>
-    <row r="24" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
@@ -8321,7 +8377,7 @@
       <c r="M24" s="17"/>
       <c r="N24" s="17"/>
     </row>
-    <row r="25" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="17"/>
@@ -8337,7 +8393,7 @@
       <c r="M25" s="17"/>
       <c r="N25" s="17"/>
     </row>
-    <row r="26" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -8353,7 +8409,7 @@
       <c r="M26" s="17"/>
       <c r="N26" s="17"/>
     </row>
-    <row r="27" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
@@ -8369,7 +8425,7 @@
       <c r="M27" s="17"/>
       <c r="N27" s="17"/>
     </row>
-    <row r="28" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -8392,7 +8448,7 @@
       <c r="V28" s="12"/>
       <c r="W28" s="12"/>
     </row>
-    <row r="29" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="17"/>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
@@ -8408,7 +8464,7 @@
       <c r="M29" s="17"/>
       <c r="N29" s="17"/>
     </row>
-    <row r="30" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="17"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -8424,7 +8480,7 @@
       <c r="M30" s="17"/>
       <c r="N30" s="17"/>
     </row>
-    <row r="31" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="17"/>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
@@ -8440,7 +8496,7 @@
       <c r="M31" s="17"/>
       <c r="N31" s="17"/>
     </row>
-    <row r="32" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="17"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -8456,7 +8512,7 @@
       <c r="M32" s="17"/>
       <c r="N32" s="17"/>
     </row>
-    <row r="33" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="17"/>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
@@ -8472,7 +8528,7 @@
       <c r="M33" s="17"/>
       <c r="N33" s="17"/>
     </row>
-    <row r="34" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="17"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
@@ -8488,7 +8544,7 @@
       <c r="M34" s="17"/>
       <c r="N34" s="17"/>
     </row>
-    <row r="35" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="17"/>
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
@@ -8504,7 +8560,7 @@
       <c r="M35" s="17"/>
       <c r="N35" s="17"/>
     </row>
-    <row r="36" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="17"/>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
@@ -8520,7 +8576,7 @@
       <c r="M36" s="17"/>
       <c r="N36" s="17"/>
     </row>
-    <row r="37" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="17"/>
       <c r="B37" s="17"/>
       <c r="C37" s="17"/>
@@ -8536,7 +8592,7 @@
       <c r="M37" s="17"/>
       <c r="N37" s="17"/>
     </row>
-    <row r="38" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="17"/>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
@@ -8552,7 +8608,7 @@
       <c r="M38" s="17"/>
       <c r="N38" s="17"/>
     </row>
-    <row r="39" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="17"/>
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>
@@ -8568,7 +8624,7 @@
       <c r="M39" s="17"/>
       <c r="N39" s="17"/>
     </row>
-    <row r="40" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="17"/>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
@@ -8584,7 +8640,7 @@
       <c r="M40" s="17"/>
       <c r="N40" s="17"/>
     </row>
-    <row r="41" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="17"/>
       <c r="B41" s="17"/>
       <c r="C41" s="17"/>
@@ -8600,7 +8656,7 @@
       <c r="M41" s="17"/>
       <c r="N41" s="17"/>
     </row>
-    <row r="42" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="17"/>
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
@@ -8616,7 +8672,7 @@
       <c r="M42" s="17"/>
       <c r="N42" s="17"/>
     </row>
-    <row r="43" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="17"/>
       <c r="B43" s="17"/>
       <c r="C43" s="17"/>
@@ -8632,7 +8688,7 @@
       <c r="M43" s="17"/>
       <c r="N43" s="17"/>
     </row>
-    <row r="44" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="17"/>
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
@@ -8648,7 +8704,7 @@
       <c r="M44" s="17"/>
       <c r="N44" s="17"/>
     </row>
-    <row r="45" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="17"/>
       <c r="B45" s="17"/>
       <c r="C45" s="17"/>
@@ -8664,7 +8720,7 @@
       <c r="M45" s="17"/>
       <c r="N45" s="17"/>
     </row>
-    <row r="46" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="17"/>
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
@@ -8680,7 +8736,7 @@
       <c r="M46" s="17"/>
       <c r="N46" s="17"/>
     </row>
-    <row r="47" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="17"/>
       <c r="B47" s="17"/>
       <c r="C47" s="17"/>
@@ -8696,7 +8752,7 @@
       <c r="M47" s="17"/>
       <c r="N47" s="17"/>
     </row>
-    <row r="48" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="17"/>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
@@ -8712,7 +8768,7 @@
       <c r="M48" s="17"/>
       <c r="N48" s="17"/>
     </row>
-    <row r="49" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="17"/>
       <c r="B49" s="17"/>
       <c r="C49" s="17"/>
@@ -8728,7 +8784,7 @@
       <c r="M49" s="17"/>
       <c r="N49" s="17"/>
     </row>
-    <row r="50" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="17"/>
       <c r="B50" s="17"/>
       <c r="C50" s="17"/>
@@ -8744,7 +8800,7 @@
       <c r="M50" s="17"/>
       <c r="N50" s="17"/>
     </row>
-    <row r="51" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="17"/>
       <c r="B51" s="17"/>
       <c r="C51" s="17"/>
@@ -8760,7 +8816,7 @@
       <c r="M51" s="17"/>
       <c r="N51" s="17"/>
     </row>
-    <row r="52" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="17"/>
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
@@ -8776,7 +8832,7 @@
       <c r="M52" s="17"/>
       <c r="N52" s="17"/>
     </row>
-    <row r="53" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="17"/>
       <c r="B53" s="17"/>
       <c r="C53" s="17"/>
@@ -8792,7 +8848,7 @@
       <c r="M53" s="17"/>
       <c r="N53" s="17"/>
     </row>
-    <row r="54" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="17"/>
       <c r="B54" s="17"/>
       <c r="C54" s="17"/>
@@ -8808,7 +8864,7 @@
       <c r="M54" s="17"/>
       <c r="N54" s="17"/>
     </row>
-    <row r="55" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="17"/>
       <c r="B55" s="17"/>
       <c r="C55" s="17"/>
@@ -8824,7 +8880,7 @@
       <c r="M55" s="17"/>
       <c r="N55" s="17"/>
     </row>
-    <row r="56" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="17"/>
       <c r="B56" s="17"/>
       <c r="C56" s="17"/>
@@ -8840,7 +8896,7 @@
       <c r="M56" s="17"/>
       <c r="N56" s="17"/>
     </row>
-    <row r="57" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="17"/>
       <c r="B57" s="17"/>
       <c r="C57" s="17"/>
@@ -8856,7 +8912,7 @@
       <c r="M57" s="17"/>
       <c r="N57" s="17"/>
     </row>
-    <row r="58" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="17"/>
       <c r="B58" s="17"/>
       <c r="C58" s="17"/>
@@ -8872,7 +8928,7 @@
       <c r="M58" s="17"/>
       <c r="N58" s="17"/>
     </row>
-    <row r="59" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="17"/>
       <c r="B59" s="17"/>
       <c r="C59" s="17"/>
@@ -8888,7 +8944,7 @@
       <c r="M59" s="17"/>
       <c r="N59" s="17"/>
     </row>
-    <row r="60" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="17"/>
       <c r="B60" s="17"/>
       <c r="C60" s="17"/>
@@ -8904,7 +8960,7 @@
       <c r="M60" s="17"/>
       <c r="N60" s="17"/>
     </row>
-    <row r="61" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="17"/>
       <c r="B61" s="17"/>
       <c r="C61" s="17"/>
@@ -8920,7 +8976,7 @@
       <c r="M61" s="17"/>
       <c r="N61" s="17"/>
     </row>
-    <row r="62" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="17"/>
       <c r="B62" s="17"/>
       <c r="C62" s="17"/>
@@ -8936,7 +8992,7 @@
       <c r="M62" s="17"/>
       <c r="N62" s="17"/>
     </row>
-    <row r="63" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="17"/>
       <c r="B63" s="17"/>
       <c r="C63" s="17"/>
@@ -8952,7 +9008,7 @@
       <c r="M63" s="17"/>
       <c r="N63" s="17"/>
     </row>
-    <row r="64" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="17"/>
       <c r="B64" s="17"/>
       <c r="C64" s="17"/>
@@ -8968,7 +9024,7 @@
       <c r="M64" s="17"/>
       <c r="N64" s="17"/>
     </row>
-    <row r="65" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="17"/>
       <c r="B65" s="17"/>
       <c r="C65" s="17"/>
@@ -8984,7 +9040,7 @@
       <c r="M65" s="17"/>
       <c r="N65" s="17"/>
     </row>
-    <row r="66" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="17"/>
       <c r="B66" s="17"/>
       <c r="C66" s="17"/>
@@ -9000,7 +9056,7 @@
       <c r="M66" s="17"/>
       <c r="N66" s="17"/>
     </row>
-    <row r="67" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="17"/>
       <c r="B67" s="17"/>
       <c r="C67" s="17"/>
@@ -9016,7 +9072,7 @@
       <c r="M67" s="17"/>
       <c r="N67" s="17"/>
     </row>
-    <row r="68" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="17"/>
       <c r="B68" s="17"/>
       <c r="C68" s="17"/>
@@ -9032,7 +9088,7 @@
       <c r="M68" s="17"/>
       <c r="N68" s="17"/>
     </row>
-    <row r="69" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="17"/>
       <c r="B69" s="17"/>
       <c r="C69" s="17"/>
@@ -9048,7 +9104,7 @@
       <c r="M69" s="17"/>
       <c r="N69" s="17"/>
     </row>
-    <row r="70" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="17"/>
       <c r="B70" s="17"/>
       <c r="C70" s="17"/>
@@ -9064,7 +9120,7 @@
       <c r="M70" s="17"/>
       <c r="N70" s="17"/>
     </row>
-    <row r="71" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="17"/>
       <c r="B71" s="17"/>
       <c r="C71" s="17"/>
@@ -9080,7 +9136,7 @@
       <c r="M71" s="17"/>
       <c r="N71" s="17"/>
     </row>
-    <row r="72" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="17"/>
       <c r="B72" s="17"/>
       <c r="C72" s="17"/>
@@ -9096,7 +9152,7 @@
       <c r="M72" s="17"/>
       <c r="N72" s="17"/>
     </row>
-    <row r="73" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="17"/>
       <c r="B73" s="17"/>
       <c r="C73" s="17"/>
@@ -9112,7 +9168,7 @@
       <c r="M73" s="17"/>
       <c r="N73" s="17"/>
     </row>
-    <row r="74" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="17"/>
       <c r="B74" s="17"/>
       <c r="C74" s="17"/>
@@ -9128,7 +9184,7 @@
       <c r="M74" s="17"/>
       <c r="N74" s="17"/>
     </row>
-    <row r="75" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="17"/>
       <c r="B75" s="17"/>
       <c r="C75" s="17"/>
@@ -9144,7 +9200,7 @@
       <c r="M75" s="17"/>
       <c r="N75" s="17"/>
     </row>
-    <row r="76" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="17"/>
       <c r="B76" s="17"/>
       <c r="C76" s="17"/>
@@ -9160,7 +9216,7 @@
       <c r="M76" s="17"/>
       <c r="N76" s="17"/>
     </row>
-    <row r="77" spans="1:14" ht="15" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="17"/>
       <c r="B77" s="17"/>
       <c r="C77" s="17"/>
@@ -9190,31 +9246,31 @@
     <tabColor rgb="FFD18316"/>
   </sheetPr>
   <dimension ref="A1:W92"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.5" style="6" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" style="6" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12" style="6" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" style="6" customWidth="1"/>
     <col min="9" max="9" width="17.6640625" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="6"/>
+    <col min="10" max="16384" width="10.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:23" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -9230,32 +9286,32 @@
       <c r="M4" s="17"/>
       <c r="N4" s="17"/>
     </row>
-    <row r="5" spans="1:23" ht="28" x14ac:dyDescent="0.2">
-      <c r="A5" s="29" t="s">
+    <row r="5" spans="1:23" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="28" t="s">
+      <c r="G5" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="28" t="s">
+      <c r="I5" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J5" s="17"/>
@@ -9271,7 +9327,7 @@
       <c r="V5" s="13"/>
       <c r="W5" s="13"/>
     </row>
-    <row r="6" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
         <v>18</v>
       </c>
@@ -9281,23 +9337,23 @@
       <c r="C6" s="20">
         <v>3.5</v>
       </c>
-      <c r="D6" s="21">
-        <v>2.7748305087648015</v>
-      </c>
-      <c r="E6" s="21">
-        <v>2.336545031392594</v>
-      </c>
-      <c r="F6" s="21">
-        <v>2.1558301627304131</v>
-      </c>
-      <c r="G6" s="21">
-        <v>1.9734488582279694</v>
-      </c>
-      <c r="H6" s="21">
-        <v>1.833050353028399</v>
-      </c>
-      <c r="I6" s="22">
-        <v>1.6855024853270757</v>
+      <c r="D6" s="36">
+        <v>2.8238828058630632</v>
+      </c>
+      <c r="E6" s="37">
+        <v>2.4153217420395152</v>
+      </c>
+      <c r="F6" s="37">
+        <v>2.2504215207559373</v>
+      </c>
+      <c r="G6" s="37">
+        <v>2.0856285652520286</v>
+      </c>
+      <c r="H6" s="37">
+        <v>1.9592594240377978</v>
+      </c>
+      <c r="I6" s="38">
+        <v>1.8238372543589922</v>
       </c>
       <c r="J6" s="17"/>
       <c r="K6" s="17"/>
@@ -9312,33 +9368,33 @@
       <c r="V6" s="14"/>
       <c r="W6" s="14"/>
     </row>
-    <row r="7" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="20">
         <v>95</v>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="22">
         <v>255.38399999999999</v>
       </c>
-      <c r="D7" s="21">
-        <v>164.020622983881</v>
-      </c>
-      <c r="E7" s="21">
-        <v>155.81959183468695</v>
-      </c>
-      <c r="F7" s="21">
-        <v>152.68679793569484</v>
-      </c>
-      <c r="G7" s="21">
-        <v>151.1365687333215</v>
-      </c>
-      <c r="H7" s="21">
-        <v>150.50179835858827</v>
-      </c>
-      <c r="I7" s="22">
-        <v>147.72761748239606</v>
+      <c r="D7" s="39">
+        <v>152.5395874996793</v>
+      </c>
+      <c r="E7" s="40">
+        <v>144.91260812469534</v>
+      </c>
+      <c r="F7" s="40">
+        <v>141.99910200345144</v>
+      </c>
+      <c r="G7" s="40">
+        <v>140.55738498788304</v>
+      </c>
+      <c r="H7" s="40">
+        <v>140.00570361377817</v>
+      </c>
+      <c r="I7" s="21">
+        <v>137.42499594277893</v>
       </c>
       <c r="J7" s="17"/>
       <c r="K7" s="17"/>
@@ -9346,7 +9402,7 @@
       <c r="M7" s="17"/>
       <c r="N7" s="17"/>
     </row>
-    <row r="8" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
         <v>20</v>
       </c>
@@ -9356,23 +9412,23 @@
       <c r="C8" s="20">
         <v>0.27300000000000002</v>
       </c>
-      <c r="D8" s="21">
-        <v>0.38140685328172108</v>
-      </c>
-      <c r="E8" s="21">
-        <v>0.33485623035723444</v>
-      </c>
-      <c r="F8" s="21">
-        <v>0.31696272219469923</v>
-      </c>
-      <c r="G8" s="21">
-        <v>0.29949905110364711</v>
-      </c>
-      <c r="H8" s="21">
-        <v>0.28623433381431385</v>
-      </c>
-      <c r="I8" s="22">
-        <v>0.26795471033809803</v>
+      <c r="D8" s="39">
+        <v>0.41558675459928401</v>
+      </c>
+      <c r="E8" s="40">
+        <v>0.36447804751194213</v>
+      </c>
+      <c r="F8" s="40">
+        <v>0.34478497269473002</v>
+      </c>
+      <c r="G8" s="40">
+        <v>0.32554165974510135</v>
+      </c>
+      <c r="H8" s="40">
+        <v>0.31091794698413894</v>
+      </c>
+      <c r="I8" s="21">
+        <v>0.29079145109282606</v>
       </c>
       <c r="J8" s="17"/>
       <c r="K8" s="17"/>
@@ -9380,7 +9436,7 @@
       <c r="M8" s="17"/>
       <c r="N8" s="17"/>
     </row>
-    <row r="9" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>21</v>
       </c>
@@ -9390,23 +9446,23 @@
       <c r="C9" s="20">
         <v>0.20300000000000001</v>
       </c>
-      <c r="D9" s="21">
-        <v>0.25075631658617614</v>
-      </c>
-      <c r="E9" s="21">
-        <v>0.21835195252164688</v>
-      </c>
-      <c r="F9" s="21">
-        <v>0.21164339180412159</v>
-      </c>
-      <c r="G9" s="21">
-        <v>0.20082981174309253</v>
-      </c>
-      <c r="H9" s="21">
-        <v>0.19235697961641432</v>
-      </c>
-      <c r="I9" s="22">
-        <v>0.18237848748474675</v>
+      <c r="D9" s="39">
+        <v>0.2530598799890717</v>
+      </c>
+      <c r="E9" s="40">
+        <v>0.22025625393688522</v>
+      </c>
+      <c r="F9" s="40">
+        <v>0.21338143733997098</v>
+      </c>
+      <c r="G9" s="40">
+        <v>0.20235871018810211</v>
+      </c>
+      <c r="H9" s="40">
+        <v>0.193694983586016</v>
+      </c>
+      <c r="I9" s="21">
+        <v>0.18350841313302682</v>
       </c>
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
@@ -9414,29 +9470,29 @@
       <c r="M9" s="17"/>
       <c r="N9" s="17"/>
     </row>
-    <row r="10" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>22</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
-      <c r="D10" s="21">
-        <v>1.77993245301295E-3</v>
-      </c>
-      <c r="E10" s="21">
-        <v>1.5109729049916059E-3</v>
-      </c>
-      <c r="F10" s="21">
-        <v>1.3971405279456467E-3</v>
-      </c>
-      <c r="G10" s="21">
-        <v>1.2879678511781595E-3</v>
-      </c>
-      <c r="H10" s="21">
-        <v>1.1695554636053252E-3</v>
-      </c>
-      <c r="I10" s="22">
-        <v>1.0450597908111356E-3</v>
+      <c r="D10" s="39">
+        <v>1.6363388078855746E-3</v>
+      </c>
+      <c r="E10" s="40">
+        <v>1.389077207910978E-3</v>
+      </c>
+      <c r="F10" s="40">
+        <v>1.2844281040425348E-3</v>
+      </c>
+      <c r="G10" s="40">
+        <v>1.1840627854300275E-3</v>
+      </c>
+      <c r="H10" s="40">
+        <v>1.0752031571942321E-3</v>
+      </c>
+      <c r="I10" s="21">
+        <v>9.6075100455095719E-4</v>
       </c>
       <c r="J10" s="17"/>
       <c r="K10" s="17"/>
@@ -9444,29 +9500,29 @@
       <c r="M10" s="17"/>
       <c r="N10" s="17"/>
     </row>
-    <row r="11" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>23</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
-      <c r="D11" s="21">
-        <v>6.8014614273917987E-2</v>
-      </c>
-      <c r="E11" s="21">
-        <v>6.6667790228889912E-2</v>
-      </c>
-      <c r="F11" s="21">
-        <v>6.6984293879471496E-2</v>
-      </c>
-      <c r="G11" s="21">
-        <v>6.7737841932664716E-2</v>
-      </c>
-      <c r="H11" s="21">
-        <v>6.8267817194383282E-2</v>
-      </c>
-      <c r="I11" s="22">
-        <v>6.8708228657107462E-2</v>
+      <c r="D11" s="39">
+        <v>6.7362378210684068E-2</v>
+      </c>
+      <c r="E11" s="40">
+        <v>6.6028469731264569E-2</v>
+      </c>
+      <c r="F11" s="40">
+        <v>6.6341938223928143E-2</v>
+      </c>
+      <c r="G11" s="40">
+        <v>6.7088260018163356E-2</v>
+      </c>
+      <c r="H11" s="40">
+        <v>6.7613153004814908E-2</v>
+      </c>
+      <c r="I11" s="21">
+        <v>6.804934107758509E-2</v>
       </c>
       <c r="J11" s="17"/>
       <c r="K11" s="17"/>
@@ -9475,29 +9531,29 @@
       <c r="N11" s="17"/>
       <c r="O11" s="9"/>
     </row>
-    <row r="12" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
         <v>24</v>
       </c>
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
-      <c r="D12" s="21">
-        <v>2.7539338128226994E-3</v>
-      </c>
-      <c r="E12" s="21">
-        <v>2.728017645193362E-3</v>
-      </c>
-      <c r="F12" s="21">
-        <v>2.74124853077255E-3</v>
-      </c>
-      <c r="G12" s="21">
-        <v>2.7978358007867961E-3</v>
-      </c>
-      <c r="H12" s="21">
-        <v>2.8289324739243556E-3</v>
-      </c>
-      <c r="I12" s="22">
-        <v>2.8610385135906359E-3</v>
+      <c r="D12" s="39">
+        <v>2.4128790617246034E-3</v>
+      </c>
+      <c r="E12" s="40">
+        <v>2.3901724236994573E-3</v>
+      </c>
+      <c r="F12" s="40">
+        <v>2.4017647599543996E-3</v>
+      </c>
+      <c r="G12" s="40">
+        <v>2.4513441065391979E-3</v>
+      </c>
+      <c r="H12" s="40">
+        <v>2.4785896819969492E-3</v>
+      </c>
+      <c r="I12" s="21">
+        <v>2.5067196212514675E-3</v>
       </c>
       <c r="J12" s="17"/>
       <c r="K12" s="17"/>
@@ -9512,29 +9568,29 @@
       <c r="U12" s="12"/>
       <c r="V12" s="12"/>
     </row>
-    <row r="13" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>32</v>
       </c>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
-      <c r="D13" s="21">
-        <v>9.7782170596117809E-2</v>
-      </c>
-      <c r="E13" s="21">
-        <v>9.7782170596117809E-2</v>
-      </c>
-      <c r="F13" s="21">
-        <v>9.9248903155059576E-2</v>
-      </c>
-      <c r="G13" s="21">
-        <v>0.10140011090817416</v>
-      </c>
-      <c r="H13" s="21">
-        <v>0.10325797214950042</v>
-      </c>
-      <c r="I13" s="22">
-        <v>0.10501805122023053</v>
+      <c r="D13" s="39">
+        <v>0.10758377258668514</v>
+      </c>
+      <c r="E13" s="40">
+        <v>0.10758377258668514</v>
+      </c>
+      <c r="F13" s="40">
+        <v>0.10919752917548542</v>
+      </c>
+      <c r="G13" s="40">
+        <v>0.11156437217239248</v>
+      </c>
+      <c r="H13" s="40">
+        <v>0.11360846385153951</v>
+      </c>
+      <c r="I13" s="21">
+        <v>0.11554497175809984</v>
       </c>
       <c r="J13" s="17"/>
       <c r="K13" s="17"/>
@@ -9549,28 +9605,28 @@
       <c r="U13" s="12"/>
       <c r="V13" s="12"/>
     </row>
-    <row r="14" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
         <v>25</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
-      <c r="D14" s="21">
+      <c r="D14" s="39">
         <v>0</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="40">
         <v>0</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="40">
         <v>0</v>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="40">
         <v>0</v>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="40">
         <v>0</v>
       </c>
-      <c r="I14" s="22">
+      <c r="I14" s="21">
         <v>0</v>
       </c>
       <c r="J14" s="17"/>
@@ -9586,29 +9642,29 @@
       <c r="U14" s="12"/>
       <c r="V14" s="12"/>
     </row>
-    <row r="15" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>26</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
-      <c r="D15" s="21">
-        <v>2.9889641460235949E-3</v>
-      </c>
-      <c r="E15" s="21">
-        <v>2.6891596140263614E-3</v>
-      </c>
-      <c r="F15" s="21">
-        <v>2.5819065864494542E-3</v>
-      </c>
-      <c r="G15" s="21">
-        <v>2.4811497464912484E-3</v>
-      </c>
-      <c r="H15" s="21">
-        <v>2.4058381827881149E-3</v>
-      </c>
-      <c r="I15" s="22">
-        <v>2.2976960757731296E-3</v>
+      <c r="D15" s="39">
+        <v>3.2222948352178156E-3</v>
+      </c>
+      <c r="E15" s="40">
+        <v>2.9064332699219211E-3</v>
+      </c>
+      <c r="F15" s="40">
+        <v>2.7945346490742666E-3</v>
+      </c>
+      <c r="G15" s="40">
+        <v>2.6899928679774282E-3</v>
+      </c>
+      <c r="H15" s="40">
+        <v>2.6120394297266779E-3</v>
+      </c>
+      <c r="I15" s="21">
+        <v>2.4994238520078516E-3</v>
       </c>
       <c r="J15" s="17"/>
       <c r="K15" s="17"/>
@@ -9623,29 +9679,29 @@
       <c r="U15" s="12"/>
       <c r="V15" s="12"/>
     </row>
-    <row r="16" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
         <v>33</v>
       </c>
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
-      <c r="D16" s="21">
-        <v>7.6924577973204507E-3</v>
-      </c>
-      <c r="E16" s="21">
-        <v>1.2954247937134079E-2</v>
-      </c>
-      <c r="F16" s="21">
-        <v>1.9727568782509558E-2</v>
-      </c>
-      <c r="G16" s="21">
-        <v>2.6876767701925784E-2</v>
-      </c>
-      <c r="H16" s="21">
-        <v>3.0711927284196316E-2</v>
-      </c>
-      <c r="I16" s="22">
-        <v>3.6289465809171528E-2</v>
+      <c r="D16" s="39">
+        <v>8.6246150353075091E-3</v>
+      </c>
+      <c r="E16" s="40">
+        <v>1.4524018782218817E-2</v>
+      </c>
+      <c r="F16" s="40">
+        <v>2.2118117617877808E-2</v>
+      </c>
+      <c r="G16" s="40">
+        <v>3.0133642709517485E-2</v>
+      </c>
+      <c r="H16" s="40">
+        <v>3.4433539552315345E-2</v>
+      </c>
+      <c r="I16" s="21">
+        <v>4.0686953466300607E-2</v>
       </c>
       <c r="J16" s="17"/>
       <c r="K16" s="17"/>
@@ -9660,29 +9716,29 @@
       <c r="U16" s="12"/>
       <c r="V16" s="12"/>
     </row>
-    <row r="17" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
         <v>34</v>
       </c>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
-      <c r="D17" s="21">
-        <v>2.9791288001910308E-2</v>
-      </c>
-      <c r="E17" s="21">
-        <v>3.3763459735498352E-2</v>
-      </c>
-      <c r="F17" s="21">
-        <v>3.9645584044319962E-2</v>
-      </c>
-      <c r="G17" s="21">
-        <v>4.1534682717952229E-2</v>
-      </c>
-      <c r="H17" s="21">
-        <v>4.5948493745453019E-2</v>
-      </c>
-      <c r="I17" s="22">
-        <v>5.0020168380967449E-2</v>
+      <c r="D17" s="39">
+        <v>3.3924728639687221E-2</v>
+      </c>
+      <c r="E17" s="40">
+        <v>3.8448025791645524E-2</v>
+      </c>
+      <c r="F17" s="40">
+        <v>4.5146274990837093E-2</v>
+      </c>
+      <c r="G17" s="40">
+        <v>4.729747972802259E-2</v>
+      </c>
+      <c r="H17" s="40">
+        <v>5.2323692134992779E-2</v>
+      </c>
+      <c r="I17" s="21">
+        <v>5.6960297880607642E-2</v>
       </c>
       <c r="J17" s="17"/>
       <c r="K17" s="17"/>
@@ -9697,29 +9753,29 @@
       <c r="U17" s="12"/>
       <c r="V17" s="12"/>
     </row>
-    <row r="18" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="18" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
-      <c r="D18" s="21">
-        <v>4.750374912104673E-3</v>
-      </c>
-      <c r="E18" s="21">
-        <v>4.325555030657454E-3</v>
-      </c>
-      <c r="F18" s="21">
-        <v>4.2570899845266992E-3</v>
-      </c>
-      <c r="G18" s="21">
-        <v>4.2217417099216755E-3</v>
-      </c>
-      <c r="H18" s="21">
-        <v>4.0374881532743625E-3</v>
-      </c>
-      <c r="I18" s="22">
-        <v>3.9071902377624899E-3</v>
+      <c r="D18" s="39">
+        <v>4.9181481563141671E-3</v>
+      </c>
+      <c r="E18" s="40">
+        <v>4.4783245307343589E-3</v>
+      </c>
+      <c r="F18" s="40">
+        <v>4.4074414432664789E-3</v>
+      </c>
+      <c r="G18" s="40">
+        <v>4.3708447419967354E-3</v>
+      </c>
+      <c r="H18" s="40">
+        <v>4.1800837375104965E-3</v>
+      </c>
+      <c r="I18" s="21">
+        <v>4.0451839738490265E-3</v>
       </c>
       <c r="J18" s="17"/>
       <c r="K18" s="17"/>
@@ -9734,29 +9790,29 @@
       <c r="U18" s="12"/>
       <c r="V18" s="12"/>
     </row>
-    <row r="19" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
         <v>28</v>
       </c>
       <c r="B19" s="20"/>
       <c r="C19" s="20"/>
-      <c r="D19" s="21">
-        <v>1.1170644044497956E-2</v>
-      </c>
-      <c r="E19" s="21">
-        <v>9.1396178545892354E-3</v>
-      </c>
-      <c r="F19" s="21">
-        <v>8.245966331029397E-3</v>
-      </c>
-      <c r="G19" s="21">
-        <v>7.3716095562736941E-3</v>
-      </c>
-      <c r="H19" s="21">
-        <v>6.4342909696308197E-3</v>
-      </c>
-      <c r="I19" s="22">
-        <v>5.453305319904911E-3</v>
+      <c r="D19" s="39">
+        <v>1.0897335866431119E-2</v>
+      </c>
+      <c r="E19" s="40">
+        <v>8.9160020725345523E-3</v>
+      </c>
+      <c r="F19" s="40">
+        <v>8.0442152032200592E-3</v>
+      </c>
+      <c r="G19" s="40">
+        <v>7.1912510049475875E-3</v>
+      </c>
+      <c r="H19" s="40">
+        <v>6.2768654590643225E-3</v>
+      </c>
+      <c r="I19" s="21">
+        <v>5.3198812366122812E-3</v>
       </c>
       <c r="J19" s="17"/>
       <c r="K19" s="17"/>
@@ -9771,29 +9827,29 @@
       <c r="U19" s="12"/>
       <c r="V19" s="12"/>
     </row>
-    <row r="20" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
         <v>29</v>
       </c>
       <c r="B20" s="20"/>
       <c r="C20" s="20"/>
-      <c r="D20" s="21">
-        <v>2.3548044710911473E-2</v>
-      </c>
-      <c r="E20" s="21">
-        <v>1.9266582036200294E-2</v>
-      </c>
-      <c r="F20" s="21">
-        <v>1.7382738459327376E-2</v>
-      </c>
-      <c r="G20" s="21">
-        <v>1.5539568777864211E-2</v>
-      </c>
-      <c r="H20" s="21">
-        <v>1.3563673753485005E-2</v>
-      </c>
-      <c r="I20" s="22">
-        <v>1.1495727281599503E-2</v>
+      <c r="D20" s="39">
+        <v>2.714897022636303E-2</v>
+      </c>
+      <c r="E20" s="40">
+        <v>2.2212793821569751E-2</v>
+      </c>
+      <c r="F20" s="40">
+        <v>2.0040876203460706E-2</v>
+      </c>
+      <c r="G20" s="40">
+        <v>1.7915852261197199E-2</v>
+      </c>
+      <c r="H20" s="40">
+        <v>1.5637806850385103E-2</v>
+      </c>
+      <c r="I20" s="21">
+        <v>1.3253633646869951E-2</v>
       </c>
       <c r="J20" s="17"/>
       <c r="K20" s="17"/>
@@ -9808,33 +9864,33 @@
       <c r="U20" s="12"/>
       <c r="V20" s="12"/>
     </row>
-    <row r="21" spans="1:23" ht="15" x14ac:dyDescent="0.2">
-      <c r="A21" s="24" t="s">
+    <row r="21" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="24">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="24">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="D21" s="26">
-        <v>3.4718688755409427E-2</v>
-      </c>
-      <c r="E21" s="26">
-        <v>2.8406199890789529E-2</v>
-      </c>
-      <c r="F21" s="26">
-        <v>2.5628704790356775E-2</v>
-      </c>
-      <c r="G21" s="26">
-        <v>2.2911178334137906E-2</v>
-      </c>
-      <c r="H21" s="26">
-        <v>1.9997964723115824E-2</v>
-      </c>
-      <c r="I21" s="27">
-        <v>1.6949032601504415E-2</v>
+      <c r="D21" s="41">
+        <v>3.8046306092794149E-2</v>
+      </c>
+      <c r="E21" s="25">
+        <v>3.1128795894104305E-2</v>
+      </c>
+      <c r="F21" s="25">
+        <v>2.8085091406680765E-2</v>
+      </c>
+      <c r="G21" s="25">
+        <v>2.5107103266144785E-2</v>
+      </c>
+      <c r="H21" s="25">
+        <v>2.1914672309449428E-2</v>
+      </c>
+      <c r="I21" s="26">
+        <v>1.8573514883482231E-2</v>
       </c>
       <c r="J21" s="17"/>
       <c r="K21" s="17"/>
@@ -9848,7 +9904,7 @@
       <c r="U21" s="12"/>
       <c r="V21" s="12"/>
     </row>
-    <row r="22" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
@@ -9870,7 +9926,7 @@
       <c r="U22" s="16"/>
       <c r="V22" s="16"/>
     </row>
-    <row r="23" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="17"/>
@@ -9892,7 +9948,7 @@
       <c r="U23" s="15"/>
       <c r="V23" s="15"/>
     </row>
-    <row r="24" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
@@ -9908,7 +9964,7 @@
       <c r="M24" s="17"/>
       <c r="N24" s="17"/>
     </row>
-    <row r="25" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="17"/>
@@ -9924,7 +9980,7 @@
       <c r="M25" s="17"/>
       <c r="N25" s="17"/>
     </row>
-    <row r="26" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -9940,7 +9996,7 @@
       <c r="M26" s="17"/>
       <c r="N26" s="17"/>
     </row>
-    <row r="27" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
@@ -9956,7 +10012,7 @@
       <c r="M27" s="17"/>
       <c r="N27" s="17"/>
     </row>
-    <row r="28" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -9979,7 +10035,7 @@
       <c r="V28" s="12"/>
       <c r="W28" s="12"/>
     </row>
-    <row r="29" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="17"/>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
@@ -9995,7 +10051,7 @@
       <c r="M29" s="17"/>
       <c r="N29" s="17"/>
     </row>
-    <row r="30" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="17"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -10011,7 +10067,7 @@
       <c r="M30" s="17"/>
       <c r="N30" s="17"/>
     </row>
-    <row r="31" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="17"/>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
@@ -10027,7 +10083,7 @@
       <c r="M31" s="17"/>
       <c r="N31" s="17"/>
     </row>
-    <row r="32" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="17"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -10043,7 +10099,7 @@
       <c r="M32" s="17"/>
       <c r="N32" s="17"/>
     </row>
-    <row r="33" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:23" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="17"/>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
@@ -10059,7 +10115,7 @@
       <c r="M33" s="17"/>
       <c r="N33" s="17"/>
     </row>
-    <row r="34" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="17"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
@@ -10075,7 +10131,7 @@
       <c r="M34" s="17"/>
       <c r="N34" s="17"/>
     </row>
-    <row r="35" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="17"/>
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
@@ -10098,7 +10154,7 @@
       <c r="V35" s="12"/>
       <c r="W35" s="12"/>
     </row>
-    <row r="36" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="17"/>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
@@ -10121,7 +10177,7 @@
       <c r="V36" s="12"/>
       <c r="W36" s="12"/>
     </row>
-    <row r="37" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="17"/>
       <c r="B37" s="17"/>
       <c r="C37" s="17"/>
@@ -10144,7 +10200,7 @@
       <c r="V37" s="12"/>
       <c r="W37" s="12"/>
     </row>
-    <row r="38" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="17"/>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
@@ -10167,7 +10223,7 @@
       <c r="V38" s="12"/>
       <c r="W38" s="12"/>
     </row>
-    <row r="39" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="17"/>
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>
@@ -10190,7 +10246,7 @@
       <c r="V39" s="12"/>
       <c r="W39" s="12"/>
     </row>
-    <row r="40" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="17"/>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
@@ -10213,7 +10269,7 @@
       <c r="V40" s="12"/>
       <c r="W40" s="12"/>
     </row>
-    <row r="41" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="17"/>
       <c r="B41" s="17"/>
       <c r="C41" s="17"/>
@@ -10236,7 +10292,7 @@
       <c r="V41" s="12"/>
       <c r="W41" s="12"/>
     </row>
-    <row r="42" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="17"/>
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
@@ -10259,7 +10315,7 @@
       <c r="V42" s="12"/>
       <c r="W42" s="12"/>
     </row>
-    <row r="43" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="17"/>
       <c r="B43" s="17"/>
       <c r="C43" s="17"/>
@@ -10282,7 +10338,7 @@
       <c r="V43" s="12"/>
       <c r="W43" s="12"/>
     </row>
-    <row r="44" spans="1:23" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:23" s="9" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="17"/>
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
@@ -10305,7 +10361,7 @@
       <c r="V44" s="12"/>
       <c r="W44" s="12"/>
     </row>
-    <row r="45" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="17"/>
       <c r="B45" s="17"/>
       <c r="C45" s="17"/>
@@ -10328,7 +10384,7 @@
       <c r="V45" s="12"/>
       <c r="W45" s="12"/>
     </row>
-    <row r="46" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="17"/>
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
@@ -10351,7 +10407,7 @@
       <c r="V46" s="12"/>
       <c r="W46" s="12"/>
     </row>
-    <row r="47" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="17"/>
       <c r="B47" s="17"/>
       <c r="C47" s="17"/>
@@ -10374,7 +10430,7 @@
       <c r="V47" s="12"/>
       <c r="W47" s="12"/>
     </row>
-    <row r="48" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="17"/>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
@@ -10397,7 +10453,7 @@
       <c r="V48" s="12"/>
       <c r="W48" s="12"/>
     </row>
-    <row r="49" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="17"/>
       <c r="B49" s="17"/>
       <c r="C49" s="17"/>
@@ -10420,7 +10476,7 @@
       <c r="V49" s="12"/>
       <c r="W49" s="12"/>
     </row>
-    <row r="50" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="17"/>
       <c r="B50" s="17"/>
       <c r="C50" s="17"/>
@@ -10443,7 +10499,7 @@
       <c r="V50" s="12"/>
       <c r="W50" s="12"/>
     </row>
-    <row r="51" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="17"/>
       <c r="B51" s="17"/>
       <c r="C51" s="17"/>
@@ -10466,7 +10522,7 @@
       <c r="V51" s="12"/>
       <c r="W51" s="12"/>
     </row>
-    <row r="52" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="17"/>
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
@@ -10489,7 +10545,7 @@
       <c r="V52" s="12"/>
       <c r="W52" s="12"/>
     </row>
-    <row r="53" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="17"/>
       <c r="B53" s="17"/>
       <c r="C53" s="17"/>
@@ -10512,7 +10568,7 @@
       <c r="V53" s="13"/>
       <c r="W53" s="13"/>
     </row>
-    <row r="54" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="17"/>
       <c r="B54" s="17"/>
       <c r="C54" s="17"/>
@@ -10535,7 +10591,7 @@
       <c r="V54" s="14"/>
       <c r="W54" s="14"/>
     </row>
-    <row r="55" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="17"/>
       <c r="B55" s="17"/>
       <c r="C55" s="17"/>
@@ -10551,7 +10607,7 @@
       <c r="M55" s="17"/>
       <c r="N55" s="17"/>
     </row>
-    <row r="56" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="17"/>
       <c r="B56" s="17"/>
       <c r="C56" s="17"/>
@@ -10567,7 +10623,7 @@
       <c r="M56" s="17"/>
       <c r="N56" s="17"/>
     </row>
-    <row r="57" spans="1:23" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:23" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="17"/>
       <c r="B57" s="17"/>
       <c r="C57" s="17"/>
@@ -10583,7 +10639,7 @@
       <c r="M57" s="17"/>
       <c r="N57" s="17"/>
     </row>
-    <row r="58" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="17"/>
       <c r="B58" s="17"/>
       <c r="C58" s="17"/>
@@ -10599,7 +10655,7 @@
       <c r="M58" s="17"/>
       <c r="N58" s="17"/>
     </row>
-    <row r="59" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="17"/>
       <c r="B59" s="17"/>
       <c r="C59" s="17"/>
@@ -10616,7 +10672,7 @@
       <c r="N59" s="17"/>
       <c r="O59" s="9"/>
     </row>
-    <row r="60" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="17"/>
       <c r="B60" s="17"/>
       <c r="C60" s="17"/>
@@ -10639,7 +10695,7 @@
       <c r="U60" s="12"/>
       <c r="V60" s="12"/>
     </row>
-    <row r="61" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="17"/>
       <c r="B61" s="17"/>
       <c r="C61" s="17"/>
@@ -10662,7 +10718,7 @@
       <c r="U61" s="12"/>
       <c r="V61" s="12"/>
     </row>
-    <row r="62" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="17"/>
       <c r="B62" s="17"/>
       <c r="C62" s="17"/>
@@ -10685,7 +10741,7 @@
       <c r="U62" s="12"/>
       <c r="V62" s="12"/>
     </row>
-    <row r="63" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="17"/>
       <c r="B63" s="17"/>
       <c r="C63" s="17"/>
@@ -10708,7 +10764,7 @@
       <c r="U63" s="12"/>
       <c r="V63" s="12"/>
     </row>
-    <row r="64" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="17"/>
       <c r="B64" s="17"/>
       <c r="C64" s="17"/>
@@ -10731,7 +10787,7 @@
       <c r="U64" s="12"/>
       <c r="V64" s="12"/>
     </row>
-    <row r="65" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="17"/>
       <c r="B65" s="17"/>
       <c r="C65" s="17"/>
@@ -10754,7 +10810,7 @@
       <c r="U65" s="12"/>
       <c r="V65" s="12"/>
     </row>
-    <row r="66" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="17"/>
       <c r="B66" s="17"/>
       <c r="C66" s="17"/>
@@ -10777,7 +10833,7 @@
       <c r="U66" s="12"/>
       <c r="V66" s="12"/>
     </row>
-    <row r="67" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="17"/>
       <c r="B67" s="17"/>
       <c r="C67" s="17"/>
@@ -10800,7 +10856,7 @@
       <c r="U67" s="12"/>
       <c r="V67" s="12"/>
     </row>
-    <row r="68" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="17"/>
       <c r="B68" s="17"/>
       <c r="C68" s="17"/>
@@ -10823,7 +10879,7 @@
       <c r="U68" s="12"/>
       <c r="V68" s="12"/>
     </row>
-    <row r="69" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="17"/>
       <c r="B69" s="17"/>
       <c r="C69" s="17"/>
@@ -10845,7 +10901,7 @@
       <c r="U69" s="12"/>
       <c r="V69" s="12"/>
     </row>
-    <row r="70" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="17"/>
       <c r="B70" s="17"/>
       <c r="C70" s="17"/>
@@ -10867,7 +10923,7 @@
       <c r="U70" s="16"/>
       <c r="V70" s="16"/>
     </row>
-    <row r="71" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="17"/>
       <c r="B71" s="17"/>
       <c r="C71" s="17"/>
@@ -10889,7 +10945,7 @@
       <c r="U71" s="15"/>
       <c r="V71" s="15"/>
     </row>
-    <row r="72" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="17"/>
       <c r="B72" s="17"/>
       <c r="C72" s="17"/>
@@ -10905,7 +10961,7 @@
       <c r="M72" s="17"/>
       <c r="N72" s="17"/>
     </row>
-    <row r="73" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="17"/>
       <c r="B73" s="17"/>
       <c r="C73" s="17"/>
@@ -10921,7 +10977,7 @@
       <c r="M73" s="17"/>
       <c r="N73" s="17"/>
     </row>
-    <row r="74" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="17"/>
       <c r="B74" s="17"/>
       <c r="C74" s="17"/>
@@ -10937,7 +10993,7 @@
       <c r="M74" s="17"/>
       <c r="N74" s="17"/>
     </row>
-    <row r="75" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="17"/>
       <c r="B75" s="17"/>
       <c r="C75" s="17"/>
@@ -10953,7 +11009,7 @@
       <c r="M75" s="17"/>
       <c r="N75" s="17"/>
     </row>
-    <row r="76" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="17"/>
       <c r="B76" s="17"/>
       <c r="C76" s="17"/>
@@ -10976,7 +11032,7 @@
       <c r="V76" s="12"/>
       <c r="W76" s="12"/>
     </row>
-    <row r="77" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="17"/>
       <c r="B77" s="17"/>
       <c r="C77" s="17"/>
@@ -10992,7 +11048,7 @@
       <c r="M77" s="17"/>
       <c r="N77" s="17"/>
     </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -11008,7 +11064,7 @@
       <c r="M78" s="1"/>
       <c r="N78" s="1"/>
     </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -11024,7 +11080,7 @@
       <c r="M79" s="1"/>
       <c r="N79" s="1"/>
     </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -11040,7 +11096,7 @@
       <c r="M80" s="1"/>
       <c r="N80" s="1"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -11056,7 +11112,7 @@
       <c r="M81" s="1"/>
       <c r="N81" s="1"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -11072,7 +11128,7 @@
       <c r="M82" s="1"/>
       <c r="N82" s="1"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -11088,7 +11144,7 @@
       <c r="M83" s="1"/>
       <c r="N83" s="1"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -11104,7 +11160,7 @@
       <c r="M84" s="1"/>
       <c r="N84" s="1"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -11120,7 +11176,7 @@
       <c r="M85" s="1"/>
       <c r="N85" s="1"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -11136,7 +11192,7 @@
       <c r="M86" s="1"/>
       <c r="N86" s="1"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -11152,7 +11208,7 @@
       <c r="M87" s="1"/>
       <c r="N87" s="1"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -11168,7 +11224,7 @@
       <c r="M88" s="1"/>
       <c r="N88" s="1"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -11184,7 +11240,7 @@
       <c r="M89" s="1"/>
       <c r="N89" s="1"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -11200,7 +11256,7 @@
       <c r="M90" s="1"/>
       <c r="N90" s="1"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -11216,7 +11272,7 @@
       <c r="M91" s="1"/>
       <c r="N91" s="1"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
